--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6986AA13-F934-D641-B691-BDD149AC8B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE58513-A150-F84E-A136-5592AE2DAD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -475,14 +475,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,40 +888,40 @@
       <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -932,40 +935,40 @@
       <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>15665</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>18368</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>21537</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>20433</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>19944</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>19145</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>19872</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>20641</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>21287</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>23518</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="5">
         <v>26771</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>28509</v>
       </c>
     </row>
@@ -979,40 +982,40 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="4">
         <v>227</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>267</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>314</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="4">
         <v>302</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>309</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="4">
         <v>319</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>323</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>331</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <v>339</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="5">
         <v>358</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="5">
         <v>398</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="5">
         <v>408</v>
       </c>
     </row>
@@ -1026,40 +1029,40 @@
       <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1073,40 +1076,40 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>106</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>106</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>106</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>106</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>106</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>106</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>106</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="5">
         <v>106</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="5">
         <v>106</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="5">
         <v>106</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="5">
         <v>106</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="5">
         <v>106</v>
       </c>
     </row>
@@ -1120,40 +1123,40 @@
       <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>35550</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>36638</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>37759</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>38048</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>39236</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <v>40115</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>41183</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>42067</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>43149</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>43872</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>44083</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>44891</v>
       </c>
     </row>
@@ -1167,40 +1170,40 @@
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>1858</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>1820</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>1783</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>1789</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>1725</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <v>2427</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>2463</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>2517</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>2604</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>2748</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>2883</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <v>2960</v>
       </c>
     </row>
@@ -1214,40 +1217,40 @@
       <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>5864</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>6486</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>7174</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>7150</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>7723</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <v>7920</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>8118</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>8397</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>8713</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>9026</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>9043</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>9368</v>
       </c>
     </row>
@@ -1261,40 +1264,40 @@
       <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>71964</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>70213</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>68505</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>73263</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>74778</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <v>78638</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>79842</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>81536</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>83127</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>84418</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>84623</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>82556</v>
       </c>
     </row>
@@ -1308,40 +1311,40 @@
       <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>232749</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>242993</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>253688</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>229817</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>232951</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1355,40 +1358,40 @@
       <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>75862</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>63740</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>53555</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>68500</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>98599</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>79484</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>81327</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>84612</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>88943</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1402,40 +1405,40 @@
       <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>120329</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>127681</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>135482</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>131019</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <v>132408</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="5" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1449,40 +1452,40 @@
       <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>33458</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>28690</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>24601</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>30975</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="4">
         <v>33624</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="4">
         <v>36455</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>37648</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>39982</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>42731</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>50184</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="5">
         <v>57210</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="5">
         <v>65597</v>
       </c>
     </row>
@@ -1496,40 +1499,40 @@
       <c r="C15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>245157</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>246726</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>248305</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>235711</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="4">
         <v>237839</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1543,40 +1546,40 @@
       <c r="C16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>96559</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>87884</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>79988</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>87364</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <v>91089</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1590,40 +1593,40 @@
       <c r="C17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>651237</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>671360</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>692105</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>676705</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="4">
         <v>673347</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="5" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1637,40 +1640,40 @@
       <c r="C18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>562535</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>602579</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <v>645474</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>567830</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <v>582701</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="5" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1684,40 +1687,40 @@
       <c r="C19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="4">
         <v>9702</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>11370</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="4">
         <v>13325</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>11939</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>11691</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="4">
         <v>11364</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <v>11487</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>11736</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>11892</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>12231</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="5">
         <v>9795</v>
       </c>
-      <c r="O19" s="6">
+      <c r="O19" s="5">
         <v>9153</v>
       </c>
     </row>
@@ -1731,40 +1734,40 @@
       <c r="C20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>1136</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>1297</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>1481</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>1391</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="4">
         <v>1411</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="4">
         <v>1442</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="5">
         <v>1446</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>1479</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>1503</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>1548</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="5">
         <v>1423</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="5">
         <v>1362</v>
       </c>
     </row>
@@ -1778,40 +1781,40 @@
       <c r="C21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>2169</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>2540</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>2974</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>2626</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="4">
         <v>2606</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="4">
         <v>2458</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>2487</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>2553</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>2612</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>2701</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="5">
         <v>2243</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="5">
         <v>2163</v>
       </c>
     </row>
@@ -1825,40 +1828,40 @@
       <c r="C22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="4" t="s">
+      <c r="D22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1872,40 +1875,40 @@
       <c r="C23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>15665</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>18368</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>21537</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>20433</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="4">
         <v>19944</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="4">
         <v>19145</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <v>19861</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>20628</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>21301</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>23506</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="5">
         <v>26771</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O23" s="5">
         <v>28509</v>
       </c>
     </row>
@@ -1919,40 +1922,40 @@
       <c r="C24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>138</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <v>164</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <v>195</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="4">
         <v>163</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <v>137</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="4">
         <v>130</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="5">
         <v>134</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="5">
         <v>138</v>
       </c>
-      <c r="L24" s="4">
+      <c r="L24" s="5">
         <v>141</v>
       </c>
-      <c r="M24" s="4">
+      <c r="M24" s="5">
         <v>143</v>
       </c>
-      <c r="N24" s="4">
+      <c r="N24" s="5">
         <v>144</v>
       </c>
-      <c r="O24" s="4">
+      <c r="O24" s="5">
         <v>137</v>
       </c>
     </row>
@@ -1966,40 +1969,40 @@
       <c r="C25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="4">
         <v>2679</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>3363</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <v>4222</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>4017</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>4237</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="4">
         <v>4457</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="5">
         <v>4486</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>4603</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>4712</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>4829</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="5">
         <v>4747</v>
       </c>
-      <c r="O25" s="6">
+      <c r="O25" s="5">
         <v>4653</v>
       </c>
     </row>
@@ -2013,40 +2016,40 @@
       <c r="C26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="4">
         <v>13941</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>13971</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <v>14001</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>13558</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>13365</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="4">
         <v>13602</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="5">
         <v>13684</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>13821</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>13907</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>14042</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="5">
         <v>13352</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O26" s="5">
         <v>13096</v>
       </c>
     </row>
@@ -2060,40 +2063,40 @@
       <c r="C27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="4">
         <v>59291</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>55057</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="4">
         <v>51125</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>57250</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>58525</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="4">
         <v>60392</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="5">
         <v>60874</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>62412</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>64083</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>65917</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="5">
         <v>57715</v>
       </c>
-      <c r="O27" s="6">
+      <c r="O27" s="5">
         <v>59112</v>
       </c>
     </row>
@@ -2107,40 +2110,40 @@
       <c r="C28" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="4">
         <v>6994</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>7529</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="4">
         <v>8105</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>7252</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>7021</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="I28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="5">
         <v>6782</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>6597</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>6318</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>6104</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="5">
         <v>5957</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="5">
         <v>5457</v>
       </c>
     </row>
@@ -2154,40 +2157,40 @@
       <c r="C29" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="4">
         <v>4071</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>2521</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="4">
         <v>1561</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>1664</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>1328</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="4">
         <v>955</v>
       </c>
-      <c r="J29" s="4">
+      <c r="J29" s="5">
         <v>912</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29" s="5">
         <v>847</v>
       </c>
-      <c r="L29" s="4">
+      <c r="L29" s="5">
         <v>803</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="5">
         <v>712</v>
       </c>
-      <c r="N29" s="4">
+      <c r="N29" s="5">
         <v>558</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="5">
         <v>506</v>
       </c>
     </row>
@@ -2201,40 +2204,40 @@
       <c r="C30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="4">
         <v>57899</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>65594</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="4">
         <v>74312</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>67826</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>62048</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="4">
         <v>58469</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="5">
         <v>57182</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>55394</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>53276</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>51987</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="5">
         <v>51978</v>
       </c>
-      <c r="O30" s="6">
+      <c r="O30" s="5">
         <v>50663</v>
       </c>
     </row>
@@ -2248,40 +2251,40 @@
       <c r="C31" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="4">
         <v>232065</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="4">
         <v>229222</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>214551</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="4">
         <v>220488</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="M31" s="4" t="s">
+      <c r="M31" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N31" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="O31" s="4" t="s">
+      <c r="O31" s="5" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2295,40 +2298,40 @@
       <c r="C32" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="4">
         <v>43955</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>43218</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="4">
         <v>42493</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>36165</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="4">
         <v>37051</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="4">
         <v>37453</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="5">
         <v>37842</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>38917</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>39884</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>41062</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="5">
         <v>37304</v>
       </c>
-      <c r="O32" s="6">
+      <c r="O32" s="5">
         <v>36486</v>
       </c>
     </row>
@@ -2342,40 +2345,40 @@
       <c r="C33" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="4">
         <v>1946</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>2220</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="4">
         <v>2533</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>2235</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="4">
         <v>2180</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="4">
         <v>2057</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="5">
         <v>2053</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>2041</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>2029</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>2018</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33" s="5">
         <v>2261</v>
       </c>
-      <c r="O33" s="6">
+      <c r="O33" s="5">
         <v>2276</v>
       </c>
     </row>
@@ -2389,40 +2392,40 @@
       <c r="C34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <v>128227</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="4">
         <v>139951</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>126867</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="4">
         <v>126785</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="M34" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="N34" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="O34" s="4" t="s">
+      <c r="O34" s="5" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2436,40 +2439,40 @@
       <c r="C35" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="4">
         <v>1226</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>1220</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="4">
         <v>1214</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <v>1038</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="4">
         <v>1004</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="4">
         <v>1028</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="5">
         <v>1032</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>1018</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>1009</v>
       </c>
-      <c r="M35" s="4">
+      <c r="M35" s="5">
         <v>998</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35" s="5">
         <v>1075</v>
       </c>
-      <c r="O35" s="6">
+      <c r="O35" s="5">
         <v>1068</v>
       </c>
     </row>
@@ -2483,40 +2486,40 @@
       <c r="C36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>205501</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="4">
         <v>184544</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>173828</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="4">
         <v>188628</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J36" s="4" t="s">
+      <c r="J36" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="L36" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="M36" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="4" t="s">
+      <c r="N36" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="O36" s="4" t="s">
+      <c r="O36" s="5" t="s">
         <v>124</v>
       </c>
     </row>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE58513-A150-F84E-A136-5592AE2DAD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596E7B4C-4B18-2E43-8539-7D3FE966FD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$36</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="127">
   <si>
     <t>Category</t>
   </si>
@@ -414,13 +414,23 @@
   </si>
   <si>
     <t>1,82,929</t>
+  </si>
+  <si>
+    <t>Mar26 W4</t>
+  </si>
+  <si>
+    <t>Apr26 W1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -454,6 +464,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -472,10 +489,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -486,8 +504,15 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -820,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -829,9 +854,10 @@
     <col min="4" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.5" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.83203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,8 +903,14 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -924,8 +956,14 @@
       <c r="O2" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -971,8 +1009,14 @@
       <c r="O3" s="5">
         <v>28509</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" s="9">
+        <v>30834</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>33159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1018,8 +1062,14 @@
       <c r="O4" s="5">
         <v>408</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P4" s="9">
+        <v>430</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -1065,8 +1115,14 @@
       <c r="O5" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1112,8 +1168,14 @@
       <c r="O6" s="5">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" s="9">
+        <v>106</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -1159,8 +1221,14 @@
       <c r="O7" s="5">
         <v>44891</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="9">
+        <v>45486</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1206,8 +1274,14 @@
       <c r="O8" s="5">
         <v>2960</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="9">
+        <v>3068</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1253,8 +1327,14 @@
       <c r="O9" s="5">
         <v>9368</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="9">
+        <v>9588</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>9808</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1300,8 +1380,14 @@
       <c r="O10" s="5">
         <v>82556</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="9">
+        <v>81806</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>81056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -1347,8 +1433,14 @@
       <c r="O11" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="9">
+        <v>295402</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>306716</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1394,8 +1486,14 @@
       <c r="O12" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="9">
+        <v>200858</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>229496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1441,8 +1539,14 @@
       <c r="O13" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="9">
+        <v>154289</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>157676</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1488,8 +1592,14 @@
       <c r="O14" s="5">
         <v>65597</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="9">
+        <v>73375</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>81153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1535,8 +1645,14 @@
       <c r="O15" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="9">
+        <v>296538</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>303714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1582,8 +1698,14 @@
       <c r="O16" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="9">
+        <v>145783</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>152795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1629,8 +1751,14 @@
       <c r="O17" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="9">
+        <v>648993</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>615137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1676,8 +1804,14 @@
       <c r="O18" s="5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="9">
+        <v>859755</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>912668</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -1723,8 +1857,14 @@
       <c r="O19" s="5">
         <v>9153</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="9">
+        <v>8076</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -1770,8 +1910,14 @@
       <c r="O20" s="5">
         <v>1362</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="9">
+        <v>1297</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -1817,8 +1963,14 @@
       <c r="O21" s="5">
         <v>2163</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="9">
+        <v>1985</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
@@ -1864,8 +2016,14 @@
       <c r="O22" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>82</v>
       </c>
@@ -1911,8 +2069,14 @@
       <c r="O23" s="5">
         <v>28509</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="9">
+        <v>30834</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>33159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>82</v>
       </c>
@@ -1958,8 +2122,14 @@
       <c r="O24" s="5">
         <v>137</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="9">
+        <v>134</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>82</v>
       </c>
@@ -2005,8 +2175,14 @@
       <c r="O25" s="5">
         <v>4653</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="9">
+        <v>4598</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>4543</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>82</v>
       </c>
@@ -2052,8 +2228,14 @@
       <c r="O26" s="5">
         <v>13096</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="9">
+        <v>12760</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>12424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
@@ -2099,8 +2281,14 @@
       <c r="O27" s="5">
         <v>59112</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="9">
+        <v>57382</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>55652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
@@ -2146,8 +2334,14 @@
       <c r="O28" s="5">
         <v>5457</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="9">
+        <v>5122</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>4787</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
@@ -2193,8 +2387,14 @@
       <c r="O29" s="5">
         <v>506</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="9">
+        <v>414</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
@@ -2240,8 +2440,14 @@
       <c r="O30" s="5">
         <v>50663</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="9">
+        <v>49788</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>48913</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>82</v>
       </c>
@@ -2287,8 +2493,14 @@
       <c r="O31" s="5" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="9">
+        <v>205647</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>196280</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
@@ -2334,8 +2546,14 @@
       <c r="O32" s="5">
         <v>36486</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="9">
+        <v>35021</v>
+      </c>
+      <c r="Q32" s="9">
+        <v>33556</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>82</v>
       </c>
@@ -2381,8 +2599,14 @@
       <c r="O33" s="5">
         <v>2276</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="9">
+        <v>2363</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>82</v>
       </c>
@@ -2428,8 +2652,14 @@
       <c r="O34" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="9">
+        <v>117790</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>114206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -2475,8 +2705,14 @@
       <c r="O35" s="5">
         <v>1068</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="9">
+        <v>1088</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>82</v>
       </c>
@@ -2521,6 +2757,12 @@
       </c>
       <c r="O36" s="5" t="s">
         <v>124</v>
+      </c>
+      <c r="P36" s="9">
+        <v>177176</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>171423</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596E7B4C-4B18-2E43-8539-7D3FE966FD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704EF064-7854-9146-A77C-94C23DDE0580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="139">
   <si>
     <t>Category</t>
   </si>
@@ -420,6 +420,42 @@
   </si>
   <si>
     <t>Apr26 W1</t>
+  </si>
+  <si>
+    <t>Apr26 W4</t>
+  </si>
+  <si>
+    <t>Apr26 W3</t>
+  </si>
+  <si>
+    <t>2,16,159</t>
+  </si>
+  <si>
+    <t>1,76,153</t>
+  </si>
+  <si>
+    <t>1,47,679</t>
+  </si>
+  <si>
+    <t>2,58,914</t>
+  </si>
+  <si>
+    <t>1,13,378</t>
+  </si>
+  <si>
+    <t>6,12,501</t>
+  </si>
+  <si>
+    <t>7,12,641</t>
+  </si>
+  <si>
+    <t>2,23,906</t>
+  </si>
+  <si>
+    <t>1,20,465</t>
+  </si>
+  <si>
+    <t>1,90,556</t>
   </si>
 </sst>
 </file>
@@ -428,9 +464,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -471,6 +507,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -493,7 +535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -504,12 +546,15 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -845,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -857,7 +902,7 @@
     <col min="16" max="17" width="11.83203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,8 +954,17 @@
       <c r="Q1" s="6" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -962,8 +1016,17 @@
       <c r="Q2" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1015,8 +1078,17 @@
       <c r="Q3" s="9">
         <v>33159</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R3">
+        <v>30941</v>
+      </c>
+      <c r="S3">
+        <v>25786</v>
+      </c>
+      <c r="T3" s="10">
+        <v>21006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1068,8 +1140,17 @@
       <c r="Q4" s="9">
         <v>452</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R4">
+        <v>427</v>
+      </c>
+      <c r="S4">
+        <v>403</v>
+      </c>
+      <c r="T4" s="10">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -1121,8 +1202,17 @@
       <c r="Q5" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1264,17 @@
       <c r="Q6" s="9">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R6">
+        <v>106</v>
+      </c>
+      <c r="S6">
+        <v>106</v>
+      </c>
+      <c r="T6" s="10">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -1227,8 +1326,17 @@
       <c r="Q7" s="9">
         <v>46081</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7">
+        <v>46355</v>
+      </c>
+      <c r="S7">
+        <v>48497</v>
+      </c>
+      <c r="T7" s="10">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1280,8 +1388,17 @@
       <c r="Q8" s="9">
         <v>3176</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8">
+        <v>3228</v>
+      </c>
+      <c r="S8">
+        <v>3413</v>
+      </c>
+      <c r="T8" s="10">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1333,8 +1450,17 @@
       <c r="Q9" s="9">
         <v>9808</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9">
+        <v>9862</v>
+      </c>
+      <c r="S9">
+        <v>10315</v>
+      </c>
+      <c r="T9" s="10">
+        <v>9679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1386,8 +1512,17 @@
       <c r="Q10" s="9">
         <v>81056</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10">
+        <v>81236</v>
+      </c>
+      <c r="S10">
+        <v>84677</v>
+      </c>
+      <c r="T10" s="10">
+        <v>83638</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -1439,8 +1574,17 @@
       <c r="Q11" s="9">
         <v>306716</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11">
+        <v>294711</v>
+      </c>
+      <c r="S11">
+        <v>294331</v>
+      </c>
+      <c r="T11" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1492,8 +1636,17 @@
       <c r="Q12" s="9">
         <v>229496</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12">
+        <v>241671</v>
+      </c>
+      <c r="S12">
+        <v>269912</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1545,8 +1698,17 @@
       <c r="Q13" s="9">
         <v>157676</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13">
+        <v>157087</v>
+      </c>
+      <c r="S13">
+        <v>162791</v>
+      </c>
+      <c r="T13" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1598,8 +1760,17 @@
       <c r="Q14" s="9">
         <v>81153</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14">
+        <v>84292</v>
+      </c>
+      <c r="S14">
+        <v>91544</v>
+      </c>
+      <c r="T14" s="10">
+        <v>74927</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1651,8 +1822,17 @@
       <c r="Q15" s="9">
         <v>303714</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15">
+        <v>297755</v>
+      </c>
+      <c r="S15">
+        <v>303545</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1704,8 +1884,17 @@
       <c r="Q16" s="9">
         <v>152795</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R16">
+        <v>148080</v>
+      </c>
+      <c r="S16">
+        <v>149270</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1757,8 +1946,17 @@
       <c r="Q17" s="9">
         <v>615137</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R17">
+        <v>601400</v>
+      </c>
+      <c r="S17">
+        <v>611907</v>
+      </c>
+      <c r="T17" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1810,8 +2008,17 @@
       <c r="Q18" s="9">
         <v>912668</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R18">
+        <v>902394</v>
+      </c>
+      <c r="S18">
+        <v>930324</v>
+      </c>
+      <c r="T18" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -1863,8 +2070,17 @@
       <c r="Q19" s="9">
         <v>7000</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R19">
+        <v>6913</v>
+      </c>
+      <c r="S19">
+        <v>6871</v>
+      </c>
+      <c r="T19" s="10">
+        <v>8349</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -1916,8 +2132,17 @@
       <c r="Q20" s="9">
         <v>1232</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R20">
+        <v>1228</v>
+      </c>
+      <c r="S20">
+        <v>1226</v>
+      </c>
+      <c r="T20" s="10">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -1969,8 +2194,17 @@
       <c r="Q21" s="9">
         <v>1807</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R21">
+        <v>1767</v>
+      </c>
+      <c r="S21">
+        <v>1734</v>
+      </c>
+      <c r="T21" s="10">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
@@ -2022,8 +2256,17 @@
       <c r="Q22" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>82</v>
       </c>
@@ -2075,8 +2318,17 @@
       <c r="Q23" s="9">
         <v>33159</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R23">
+        <v>30941</v>
+      </c>
+      <c r="S23">
+        <v>27786</v>
+      </c>
+      <c r="T23" s="10">
+        <v>21006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>82</v>
       </c>
@@ -2128,8 +2380,17 @@
       <c r="Q24" s="9">
         <v>131</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R24">
+        <v>134</v>
+      </c>
+      <c r="S24">
+        <v>136</v>
+      </c>
+      <c r="T24" s="10">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>82</v>
       </c>
@@ -2181,8 +2442,17 @@
       <c r="Q25" s="9">
         <v>4543</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R25">
+        <v>4637</v>
+      </c>
+      <c r="S25">
+        <v>4731</v>
+      </c>
+      <c r="T25" s="10">
+        <v>5158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>82</v>
       </c>
@@ -2234,8 +2504,17 @@
       <c r="Q26" s="9">
         <v>12424</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R26">
+        <v>12621</v>
+      </c>
+      <c r="S26">
+        <v>12822</v>
+      </c>
+      <c r="T26" s="10">
+        <v>14185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
@@ -2287,8 +2566,17 @@
       <c r="Q27" s="9">
         <v>55652</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R27">
+        <v>58952</v>
+      </c>
+      <c r="S27">
+        <v>62294</v>
+      </c>
+      <c r="T27" s="10">
+        <v>76957</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
@@ -2340,8 +2628,17 @@
       <c r="Q28" s="9">
         <v>4787</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R28">
+        <v>5120</v>
+      </c>
+      <c r="S28">
+        <v>5460</v>
+      </c>
+      <c r="T28" s="10">
+        <v>6994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
@@ -2393,8 +2690,17 @@
       <c r="Q29" s="9">
         <v>322</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R29">
+        <v>326</v>
+      </c>
+      <c r="S29">
+        <v>334</v>
+      </c>
+      <c r="T29" s="10">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
@@ -2446,8 +2752,17 @@
       <c r="Q30" s="9">
         <v>48913</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R30">
+        <v>50486</v>
+      </c>
+      <c r="S30">
+        <v>52062</v>
+      </c>
+      <c r="T30" s="10">
+        <v>58170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>82</v>
       </c>
@@ -2499,8 +2814,17 @@
       <c r="Q31" s="9">
         <v>196280</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R31">
+        <v>197409</v>
+      </c>
+      <c r="S31">
+        <v>198784</v>
+      </c>
+      <c r="T31" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
@@ -2552,8 +2876,17 @@
       <c r="Q32" s="9">
         <v>33556</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R32">
+        <v>33371</v>
+      </c>
+      <c r="S32">
+        <v>33222</v>
+      </c>
+      <c r="T32" s="10">
+        <v>36068</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>82</v>
       </c>
@@ -2605,8 +2938,17 @@
       <c r="Q33" s="9">
         <v>2450</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R33">
+        <v>2437</v>
+      </c>
+      <c r="S33">
+        <v>2427</v>
+      </c>
+      <c r="T33" s="10">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>82</v>
       </c>
@@ -2658,8 +3000,17 @@
       <c r="Q34" s="9">
         <v>114206</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R34">
+        <v>113754</v>
+      </c>
+      <c r="S34">
+        <v>113366</v>
+      </c>
+      <c r="T34" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -2711,8 +3062,17 @@
       <c r="Q35" s="9">
         <v>1108</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R35">
+        <v>1107</v>
+      </c>
+      <c r="S35">
+        <v>1106</v>
+      </c>
+      <c r="T35" s="10">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>82</v>
       </c>
@@ -2763,6 +3123,15 @@
       </c>
       <c r="Q36" s="9">
         <v>171423</v>
+      </c>
+      <c r="R36">
+        <v>172527</v>
+      </c>
+      <c r="S36">
+        <v>173740</v>
+      </c>
+      <c r="T36" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704EF064-7854-9146-A77C-94C23DDE0580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5CA229-902D-484D-AFFF-6E7E31F99834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advikholalu/Desktop/SOV Brand Comparison/data_raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5CA229-902D-484D-AFFF-6E7E31F99834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4B9438-5A0C-D14C-BE19-1A5D3C116D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15680" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="163">
   <si>
     <t>Category</t>
   </si>
@@ -456,6 +456,78 @@
   </si>
   <si>
     <t>1,90,556</t>
+  </si>
+  <si>
+    <t>May26 W1</t>
+  </si>
+  <si>
+    <t>May26 W2</t>
+  </si>
+  <si>
+    <t>2,13,743</t>
+  </si>
+  <si>
+    <t>1,82,395</t>
+  </si>
+  <si>
+    <t>1,50,892</t>
+  </si>
+  <si>
+    <t>2,71,617</t>
+  </si>
+  <si>
+    <t>1,19,337</t>
+  </si>
+  <si>
+    <t>6,48,673</t>
+  </si>
+  <si>
+    <t>7,41,381</t>
+  </si>
+  <si>
+    <t>2,25,377</t>
+  </si>
+  <si>
+    <t>1,20,581</t>
+  </si>
+  <si>
+    <t>2,01,863</t>
+  </si>
+  <si>
+    <t>2,08,441</t>
+  </si>
+  <si>
+    <t>1,79,338</t>
+  </si>
+  <si>
+    <t>1,45,904</t>
+  </si>
+  <si>
+    <t>2,63,228</t>
+  </si>
+  <si>
+    <t>1,16,482</t>
+  </si>
+  <si>
+    <t>6,31,447</t>
+  </si>
+  <si>
+    <t>7,28,904</t>
+  </si>
+  <si>
+    <t>2,28,992</t>
+  </si>
+  <si>
+    <t>1,22,348</t>
+  </si>
+  <si>
+    <t>2,06,417</t>
+  </si>
+  <si>
+    <t>May26 W3</t>
+  </si>
+  <si>
+    <t>Apr26 W2</t>
   </si>
 </sst>
 </file>
@@ -466,7 +538,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -513,6 +585,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -535,7 +615,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -555,6 +635,15 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -890,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -900,9 +989,10 @@
     <col min="9" max="12" width="11.5" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.83203125" style="7" customWidth="1"/>
+    <col min="23" max="23" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -955,7 +1045,7 @@
         <v>126</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="S1" s="6" t="s">
         <v>128</v>
@@ -963,8 +1053,21 @@
       <c r="T1" s="6" t="s">
         <v>127</v>
       </c>
+      <c r="U1" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -1025,8 +1128,17 @@
       <c r="T2" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="U2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1087,8 +1199,18 @@
       <c r="T3" s="10">
         <v>21006</v>
       </c>
+      <c r="U3" s="14">
+        <v>23487</v>
+      </c>
+      <c r="V3" s="14">
+        <v>22116</v>
+      </c>
+      <c r="W3" s="15">
+        <v>19589</v>
+      </c>
+      <c r="AB3" s="12"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1149,8 +1271,17 @@
       <c r="T4" s="10">
         <v>270</v>
       </c>
+      <c r="U4" s="13">
+        <v>291</v>
+      </c>
+      <c r="V4" s="13">
+        <v>274</v>
+      </c>
+      <c r="W4" s="15">
+        <v>237</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -1211,8 +1342,17 @@
       <c r="T5" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="U5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1273,8 +1413,17 @@
       <c r="T6" s="10">
         <v>106</v>
       </c>
+      <c r="U6" s="13">
+        <v>106</v>
+      </c>
+      <c r="V6" s="13">
+        <v>106</v>
+      </c>
+      <c r="W6" s="15">
+        <v>106</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -1335,8 +1484,18 @@
       <c r="T7" s="10">
         <v>46334</v>
       </c>
+      <c r="U7" s="14">
+        <v>47012</v>
+      </c>
+      <c r="V7" s="14">
+        <v>48206</v>
+      </c>
+      <c r="W7" s="15">
+        <v>47748</v>
+      </c>
+      <c r="AB7" s="12"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -1397,8 +1556,18 @@
       <c r="T8" s="10">
         <v>3198</v>
       </c>
+      <c r="U8" s="14">
+        <v>3104</v>
+      </c>
+      <c r="V8" s="14">
+        <v>3157</v>
+      </c>
+      <c r="W8" s="15">
+        <v>3148</v>
+      </c>
+      <c r="AB8" s="12"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1459,8 +1628,18 @@
       <c r="T9" s="10">
         <v>9679</v>
       </c>
+      <c r="U9" s="14">
+        <v>9112</v>
+      </c>
+      <c r="V9" s="14">
+        <v>9305</v>
+      </c>
+      <c r="W9" s="15">
+        <v>9230</v>
+      </c>
+      <c r="AB9" s="12"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1521,8 +1700,18 @@
       <c r="T10" s="10">
         <v>83638</v>
       </c>
+      <c r="U10" s="14">
+        <v>79884</v>
+      </c>
+      <c r="V10" s="14">
+        <v>81093</v>
+      </c>
+      <c r="W10" s="15">
+        <v>81479</v>
+      </c>
+      <c r="AB10" s="12"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -1583,8 +1772,17 @@
       <c r="T11" s="10" t="s">
         <v>129</v>
       </c>
+      <c r="U11" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="V11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="W11" s="15">
+        <v>190412</v>
+      </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1645,8 +1843,17 @@
       <c r="T12" s="10" t="s">
         <v>130</v>
       </c>
+      <c r="U12" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="W12" s="15">
+        <v>168639</v>
+      </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1707,8 +1914,17 @@
       <c r="T13" s="10" t="s">
         <v>131</v>
       </c>
+      <c r="U13" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="V13" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="W13" s="15">
+        <v>146511</v>
+      </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1769,8 +1985,18 @@
       <c r="T14" s="10">
         <v>74927</v>
       </c>
+      <c r="U14" s="14">
+        <v>73982</v>
+      </c>
+      <c r="V14" s="14">
+        <v>76417</v>
+      </c>
+      <c r="W14" s="15">
+        <v>74001</v>
+      </c>
+      <c r="AB14" s="12"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1831,8 +2057,17 @@
       <c r="T15" s="10" t="s">
         <v>132</v>
       </c>
+      <c r="U15" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="V15" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="W15" s="15">
+        <v>257190</v>
+      </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1893,8 +2128,17 @@
       <c r="T16" s="10" t="s">
         <v>133</v>
       </c>
+      <c r="U16" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="W16" s="15">
+        <v>108615</v>
+      </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1955,8 +2199,17 @@
       <c r="T17" s="10" t="s">
         <v>134</v>
       </c>
+      <c r="U17" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="W17" s="15">
+        <v>639961</v>
+      </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -2017,8 +2270,17 @@
       <c r="T18" s="10" t="s">
         <v>135</v>
       </c>
+      <c r="U18" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="V18" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="W18" s="15">
+        <v>688213</v>
+      </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -2079,8 +2341,18 @@
       <c r="T19" s="10">
         <v>8349</v>
       </c>
+      <c r="U19" s="14">
+        <v>7614</v>
+      </c>
+      <c r="V19" s="14">
+        <v>7929</v>
+      </c>
+      <c r="W19" s="15">
+        <v>8147</v>
+      </c>
+      <c r="AB19" s="12"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -2141,8 +2413,18 @@
       <c r="T20" s="10">
         <v>1354</v>
       </c>
+      <c r="U20" s="14">
+        <v>1221</v>
+      </c>
+      <c r="V20" s="14">
+        <v>1247</v>
+      </c>
+      <c r="W20" s="15">
+        <v>1271</v>
+      </c>
+      <c r="AB20" s="12"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2203,8 +2485,18 @@
       <c r="T21" s="10">
         <v>1955</v>
       </c>
+      <c r="U21" s="14">
+        <v>1861</v>
+      </c>
+      <c r="V21" s="14">
+        <v>1905</v>
+      </c>
+      <c r="W21" s="15">
+        <v>1925</v>
+      </c>
+      <c r="AB21" s="12"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
@@ -2265,8 +2557,17 @@
       <c r="T22" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="U22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>82</v>
       </c>
@@ -2327,8 +2628,18 @@
       <c r="T23" s="10">
         <v>21006</v>
       </c>
+      <c r="U23" s="14">
+        <v>23487</v>
+      </c>
+      <c r="V23" s="14">
+        <v>22116</v>
+      </c>
+      <c r="W23" s="15">
+        <v>19669</v>
+      </c>
+      <c r="AB23" s="12"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>82</v>
       </c>
@@ -2389,8 +2700,17 @@
       <c r="T24" s="10">
         <v>150</v>
       </c>
+      <c r="U24" s="13">
+        <v>171</v>
+      </c>
+      <c r="V24" s="13">
+        <v>165</v>
+      </c>
+      <c r="W24" s="15">
+        <v>171</v>
+      </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>82</v>
       </c>
@@ -2451,8 +2771,18 @@
       <c r="T25" s="10">
         <v>5158</v>
       </c>
+      <c r="U25" s="14">
+        <v>5386</v>
+      </c>
+      <c r="V25" s="14">
+        <v>5258</v>
+      </c>
+      <c r="W25" s="15">
+        <v>5453</v>
+      </c>
+      <c r="AB25" s="12"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>82</v>
       </c>
@@ -2513,8 +2843,18 @@
       <c r="T26" s="10">
         <v>14185</v>
       </c>
+      <c r="U26" s="14">
+        <v>14884</v>
+      </c>
+      <c r="V26" s="14">
+        <v>14530</v>
+      </c>
+      <c r="W26" s="15">
+        <v>15081</v>
+      </c>
+      <c r="AB26" s="12"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>82</v>
       </c>
@@ -2575,8 +2915,18 @@
       <c r="T27" s="10">
         <v>76957</v>
       </c>
+      <c r="U27" s="14">
+        <v>85406</v>
+      </c>
+      <c r="V27" s="14">
+        <v>82691</v>
+      </c>
+      <c r="W27" s="15">
+        <v>88622</v>
+      </c>
+      <c r="AB27" s="12"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
@@ -2637,8 +2987,18 @@
       <c r="T28" s="10">
         <v>6994</v>
       </c>
+      <c r="U28" s="14">
+        <v>8644</v>
+      </c>
+      <c r="V28" s="14">
+        <v>8255</v>
+      </c>
+      <c r="W28" s="15">
+        <v>8878</v>
+      </c>
+      <c r="AB28" s="12"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
@@ -2699,8 +3059,17 @@
       <c r="T29" s="10">
         <v>448</v>
       </c>
+      <c r="U29" s="13">
+        <v>417</v>
+      </c>
+      <c r="V29" s="13">
+        <v>428</v>
+      </c>
+      <c r="W29" s="15">
+        <v>455</v>
+      </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
@@ -2761,8 +3130,18 @@
       <c r="T30" s="10">
         <v>58170</v>
       </c>
+      <c r="U30" s="14">
+        <v>59824</v>
+      </c>
+      <c r="V30" s="14">
+        <v>58797</v>
+      </c>
+      <c r="W30" s="15">
+        <v>61410</v>
+      </c>
+      <c r="AB30" s="12"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>82</v>
       </c>
@@ -2823,8 +3202,17 @@
       <c r="T31" s="10" t="s">
         <v>136</v>
       </c>
+      <c r="U31" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="V31" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="W31" s="15">
+        <v>233433</v>
+      </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
@@ -2885,8 +3273,18 @@
       <c r="T32" s="10">
         <v>36068</v>
       </c>
+      <c r="U32" s="14">
+        <v>38102</v>
+      </c>
+      <c r="V32" s="14">
+        <v>37420</v>
+      </c>
+      <c r="W32" s="15">
+        <v>38234</v>
+      </c>
+      <c r="AB32" s="12"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>82</v>
       </c>
@@ -2947,8 +3345,18 @@
       <c r="T33" s="10">
         <v>2116</v>
       </c>
+      <c r="U33" s="14">
+        <v>1947</v>
+      </c>
+      <c r="V33" s="14">
+        <v>2003</v>
+      </c>
+      <c r="W33" s="15">
+        <v>1906</v>
+      </c>
+      <c r="AB33" s="12"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>82</v>
       </c>
@@ -3009,8 +3417,17 @@
       <c r="T34" s="10" t="s">
         <v>137</v>
       </c>
+      <c r="U34" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="V34" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="W34" s="15">
+        <v>122810</v>
+      </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>82</v>
       </c>
@@ -3071,8 +3488,18 @@
       <c r="T35" s="10">
         <v>1035</v>
       </c>
+      <c r="U35" s="14">
+        <v>1074</v>
+      </c>
+      <c r="V35" s="14">
+        <v>1058</v>
+      </c>
+      <c r="W35" s="15">
+        <v>1046</v>
+      </c>
+      <c r="AB35" s="12"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>82</v>
       </c>
@@ -3132,6 +3559,15 @@
       </c>
       <c r="T36" s="10" t="s">
         <v>138</v>
+      </c>
+      <c r="U36" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="V36" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="W36" s="15">
+        <v>207739</v>
       </c>
     </row>
   </sheetData>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4B9438-5A0C-D14C-BE19-1A5D3C116D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAF2891-0C62-7043-9C3E-9830FF0C2A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="176">
   <si>
     <t>Category</t>
   </si>
@@ -528,6 +528,45 @@
   </si>
   <si>
     <t>Apr26 W2</t>
+  </si>
+  <si>
+    <t>May26 W4</t>
+  </si>
+  <si>
+    <t>Jun26 W1</t>
+  </si>
+  <si>
+    <t>Jun26 W2</t>
+  </si>
+  <si>
+    <t>2,48,183</t>
+  </si>
+  <si>
+    <t>1,87,475</t>
+  </si>
+  <si>
+    <t>1,58,049</t>
+  </si>
+  <si>
+    <t>2,74,609</t>
+  </si>
+  <si>
+    <t>1,32,304</t>
+  </si>
+  <si>
+    <t>7,13,994</t>
+  </si>
+  <si>
+    <t>7,38,421</t>
+  </si>
+  <si>
+    <t>2,43,094</t>
+  </si>
+  <si>
+    <t>1,37,019</t>
+  </si>
+  <si>
+    <t>2,24,375</t>
   </si>
 </sst>
 </file>
@@ -538,39 +577,13 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -582,16 +595,20 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -602,7 +619,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -610,40 +627,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -979,2596 +1010,2985 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11.83203125" style="7" customWidth="1"/>
-    <col min="23" max="23" width="11.33203125" customWidth="1"/>
+    <col min="18" max="22" width="10.83203125" style="1"/>
+    <col min="23" max="23" width="11.33203125" style="1" customWidth="1"/>
+    <col min="24" max="25" width="10.83203125" style="1"/>
+    <col min="26" max="26" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
+      <c r="X1" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="15" t="s">
+      <c r="D2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="10">
         <v>15665</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="10">
         <v>18368</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="10">
         <v>21537</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="10">
         <v>20433</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="10">
         <v>19944</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="10">
         <v>19145</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="10">
         <v>19872</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="10">
         <v>20641</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="10">
         <v>21287</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="10">
         <v>23518</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="10">
         <v>26771</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="10">
         <v>28509</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="2">
         <v>30834</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="Q3" s="2">
         <v>33159</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="3">
         <v>30941</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="3">
         <v>25786</v>
       </c>
-      <c r="T3" s="10">
+      <c r="T3" s="2">
         <v>21006</v>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="5">
         <v>23487</v>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="5">
         <v>22116</v>
       </c>
-      <c r="W3" s="15">
+      <c r="W3" s="4">
         <v>19589</v>
       </c>
-      <c r="AB3" s="12"/>
+      <c r="X3" s="12">
+        <v>19584</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>19580</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>20511</v>
+      </c>
+      <c r="AB3" s="6"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="10">
         <v>227</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="10">
         <v>267</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="10">
         <v>314</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="10">
         <v>302</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="10">
         <v>309</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="10">
         <v>319</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="10">
         <v>323</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="10">
         <v>331</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="10">
         <v>339</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="10">
         <v>358</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="10">
         <v>398</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="10">
         <v>408</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="2">
         <v>430</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="Q4" s="2">
         <v>452</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="3">
         <v>427</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="3">
         <v>403</v>
       </c>
-      <c r="T4" s="10">
+      <c r="T4" s="2">
         <v>270</v>
       </c>
-      <c r="U4" s="13">
+      <c r="U4" s="3">
         <v>291</v>
       </c>
-      <c r="V4" s="13">
+      <c r="V4" s="3">
         <v>274</v>
       </c>
-      <c r="W4" s="15">
+      <c r="W4" s="4">
         <v>237</v>
       </c>
+      <c r="X4" s="12">
+        <v>253</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>268</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>337</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="T5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="V5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="W5" s="15" t="s">
+      <c r="D5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="10">
         <v>106</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="10">
         <v>106</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="10">
         <v>106</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="10">
         <v>106</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="10">
         <v>106</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="10">
         <v>106</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="10">
         <v>106</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="10">
         <v>106</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="10">
         <v>106</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="10">
         <v>106</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="10">
         <v>106</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="10">
         <v>106</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="2">
         <v>106</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Q6" s="2">
         <v>106</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="3">
         <v>106</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="3">
         <v>106</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="2">
         <v>106</v>
       </c>
-      <c r="U6" s="13">
+      <c r="U6" s="3">
         <v>106</v>
       </c>
-      <c r="V6" s="13">
+      <c r="V6" s="3">
         <v>106</v>
       </c>
-      <c r="W6" s="15">
+      <c r="W6" s="4">
         <v>106</v>
       </c>
+      <c r="X6" s="12">
+        <v>106</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>106</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>106</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="10">
         <v>35550</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="10">
         <v>36638</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="10">
         <v>37759</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="10">
         <v>38048</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="10">
         <v>39236</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="10">
         <v>40115</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="10">
         <v>41183</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="10">
         <v>42067</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="10">
         <v>43149</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="10">
         <v>43872</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="10">
         <v>44083</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="10">
         <v>44891</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="2">
         <v>45486</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Q7" s="2">
         <v>46081</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="3">
         <v>46355</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="3">
         <v>48497</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="2">
         <v>46334</v>
       </c>
-      <c r="U7" s="14">
+      <c r="U7" s="5">
         <v>47012</v>
       </c>
-      <c r="V7" s="14">
+      <c r="V7" s="5">
         <v>48206</v>
       </c>
-      <c r="W7" s="15">
+      <c r="W7" s="4">
         <v>47748</v>
       </c>
-      <c r="AB7" s="12"/>
+      <c r="X7" s="12">
+        <v>48609</v>
+      </c>
+      <c r="Y7" s="12">
+        <v>49470</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>51110</v>
+      </c>
+      <c r="AB7" s="6"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="10">
         <v>1858</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="10">
         <v>1820</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="10">
         <v>1783</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="10">
         <v>1789</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="10">
         <v>1725</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="10">
         <v>2427</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="10">
         <v>2463</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="10">
         <v>2517</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="10">
         <v>2604</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="10">
         <v>2748</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="10">
         <v>2883</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="10">
         <v>2960</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="2">
         <v>3068</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="2">
         <v>3176</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="3">
         <v>3228</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="3">
         <v>3413</v>
       </c>
-      <c r="T8" s="10">
+      <c r="T8" s="2">
         <v>3198</v>
       </c>
-      <c r="U8" s="14">
+      <c r="U8" s="5">
         <v>3104</v>
       </c>
-      <c r="V8" s="14">
+      <c r="V8" s="5">
         <v>3157</v>
       </c>
-      <c r="W8" s="15">
+      <c r="W8" s="4">
         <v>3148</v>
       </c>
-      <c r="AB8" s="12"/>
+      <c r="X8" s="12">
+        <v>3123</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>3098</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>3057</v>
+      </c>
+      <c r="AB8" s="6"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="10">
         <v>5864</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="10">
         <v>6486</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="10">
         <v>7174</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="10">
         <v>7150</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="10">
         <v>7723</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="10">
         <v>7920</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="10">
         <v>8118</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="10">
         <v>8397</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="10">
         <v>8713</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="10">
         <v>9026</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="10">
         <v>9043</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="10">
         <v>9368</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="2">
         <v>9588</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="2">
         <v>9808</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="3">
         <v>9862</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="3">
         <v>10315</v>
       </c>
-      <c r="T9" s="10">
+      <c r="T9" s="2">
         <v>9679</v>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="5">
         <v>9112</v>
       </c>
-      <c r="V9" s="14">
+      <c r="V9" s="5">
         <v>9305</v>
       </c>
-      <c r="W9" s="15">
+      <c r="W9" s="4">
         <v>9230</v>
       </c>
-      <c r="AB9" s="12"/>
+      <c r="X9" s="12">
+        <v>9178</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>9125</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>9268</v>
+      </c>
+      <c r="AB9" s="6"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="10">
         <v>71964</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="10">
         <v>70213</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="10">
         <v>68505</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="10">
         <v>73263</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="10">
         <v>74778</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="10">
         <v>78638</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="10">
         <v>79842</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="10">
         <v>81536</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="10">
         <v>83127</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="10">
         <v>84418</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="10">
         <v>84623</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="10">
         <v>82556</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="2">
         <v>81806</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="2">
         <v>81056</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="3">
         <v>81236</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="3">
         <v>84677</v>
       </c>
-      <c r="T10" s="10">
+      <c r="T10" s="2">
         <v>83638</v>
       </c>
-      <c r="U10" s="14">
+      <c r="U10" s="5">
         <v>79884</v>
       </c>
-      <c r="V10" s="14">
+      <c r="V10" s="5">
         <v>81093</v>
       </c>
-      <c r="W10" s="15">
+      <c r="W10" s="4">
         <v>81479</v>
       </c>
-      <c r="AB10" s="12"/>
+      <c r="X10" s="12">
+        <v>80893</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>80306</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>79986</v>
+      </c>
+      <c r="AB10" s="6"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="10">
         <v>232749</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="10">
         <v>242993</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="10">
         <v>253688</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="10">
         <v>229817</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="10">
         <v>232951</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="2">
         <v>295402</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="2">
         <v>306716</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="3">
         <v>294711</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="3">
         <v>294331</v>
       </c>
-      <c r="T11" s="10" t="s">
+      <c r="T11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="U11" s="13" t="s">
+      <c r="U11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="V11" s="13" t="s">
+      <c r="V11" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="W11" s="15">
+      <c r="W11" s="4">
         <v>190412</v>
       </c>
+      <c r="X11" s="12">
+        <v>198533</v>
+      </c>
+      <c r="Y11" s="12">
+        <v>206655</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="10">
         <v>75862</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="10">
         <v>63740</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="10">
         <v>53555</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="10">
         <v>68500</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="10">
         <v>98599</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="10">
         <v>79484</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="10">
         <v>81327</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="10">
         <v>84612</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="10">
         <v>88943</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="N12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="2">
         <v>200858</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="2">
         <v>229496</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="3">
         <v>241671</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="3">
         <v>269912</v>
       </c>
-      <c r="T12" s="10" t="s">
+      <c r="T12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="U12" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="V12" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="W12" s="15">
+      <c r="W12" s="4">
         <v>168639</v>
       </c>
+      <c r="X12" s="12">
+        <v>171404</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>174170</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="10">
         <v>120329</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="10">
         <v>127681</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="10">
         <v>135482</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="10">
         <v>131019</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="10">
         <v>132408</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="5" t="s">
+      <c r="L13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="5" t="s">
+      <c r="O13" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="2">
         <v>154289</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="2">
         <v>157676</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="3">
         <v>157087</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="3">
         <v>162791</v>
       </c>
-      <c r="T13" s="10" t="s">
+      <c r="T13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="U13" s="13" t="s">
+      <c r="U13" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="V13" s="13" t="s">
+      <c r="V13" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="W13" s="15">
+      <c r="W13" s="4">
         <v>146511</v>
       </c>
+      <c r="X13" s="12">
+        <v>148663</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>150815</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="10">
         <v>33458</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="10">
         <v>28690</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="10">
         <v>24601</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="10">
         <v>30975</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="10">
         <v>33624</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="10">
         <v>36455</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="10">
         <v>37648</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="10">
         <v>39982</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="10">
         <v>42731</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="10">
         <v>50184</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="10">
         <v>57210</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="10">
         <v>65597</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="2">
         <v>73375</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="2">
         <v>81153</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="3">
         <v>84292</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="3">
         <v>91544</v>
       </c>
-      <c r="T14" s="10">
+      <c r="T14" s="2">
         <v>74927</v>
       </c>
-      <c r="U14" s="14">
+      <c r="U14" s="5">
         <v>73982</v>
       </c>
-      <c r="V14" s="14">
+      <c r="V14" s="5">
         <v>76417</v>
       </c>
-      <c r="W14" s="15">
+      <c r="W14" s="4">
         <v>74001</v>
       </c>
-      <c r="AB14" s="12"/>
+      <c r="X14" s="12">
+        <v>76698</v>
+      </c>
+      <c r="Y14" s="12">
+        <v>79396</v>
+      </c>
+      <c r="Z14" s="5">
+        <v>88105</v>
+      </c>
+      <c r="AB14" s="6"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="10">
         <v>245157</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="10">
         <v>246726</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="10">
         <v>248305</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="10">
         <v>235711</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="10">
         <v>237839</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="5" t="s">
+      <c r="O15" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="2">
         <v>296538</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="Q15" s="2">
         <v>303714</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="3">
         <v>297755</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="3">
         <v>303545</v>
       </c>
-      <c r="T15" s="10" t="s">
+      <c r="T15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="U15" s="13" t="s">
+      <c r="U15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="V15" s="13" t="s">
+      <c r="V15" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="W15" s="15">
+      <c r="W15" s="4">
         <v>257190</v>
       </c>
+      <c r="X15" s="12">
+        <v>260444</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>263698</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="10">
         <v>96559</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="10">
         <v>87884</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="10">
         <v>79988</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="10">
         <v>87364</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="10">
         <v>91089</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L16" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="N16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="2">
         <v>145783</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="2">
         <v>152795</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="3">
         <v>148080</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="3">
         <v>149270</v>
       </c>
-      <c r="T16" s="10" t="s">
+      <c r="T16" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="U16" s="13" t="s">
+      <c r="U16" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="V16" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="W16" s="15">
+      <c r="W16" s="4">
         <v>108615</v>
       </c>
+      <c r="X16" s="12">
+        <v>112718</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>116820</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="10">
         <v>651237</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="10">
         <v>671360</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="10">
         <v>692105</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="10">
         <v>676705</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="10">
         <v>673347</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="5" t="s">
+      <c r="L17" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="N17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="O17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="2">
         <v>648993</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="2">
         <v>615137</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="3">
         <v>601400</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="3">
         <v>611907</v>
       </c>
-      <c r="T17" s="10" t="s">
+      <c r="T17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="V17" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="W17" s="15">
+      <c r="W17" s="4">
         <v>639961</v>
       </c>
+      <c r="X17" s="12">
+        <v>658429</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>676897</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="10">
         <v>562535</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="10">
         <v>602579</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="10">
         <v>645474</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="10">
         <v>567830</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="10">
         <v>582701</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="L18" s="5" t="s">
+      <c r="L18" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="5" t="s">
+      <c r="N18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="O18" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="2">
         <v>859755</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="Q18" s="2">
         <v>912668</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="3">
         <v>902394</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="3">
         <v>930324</v>
       </c>
-      <c r="T18" s="10" t="s">
+      <c r="T18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="V18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="W18" s="15">
+      <c r="W18" s="4">
         <v>688213</v>
       </c>
+      <c r="X18" s="12">
+        <v>694998</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>701782</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="10">
         <v>9702</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="10">
         <v>11370</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="10">
         <v>13325</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="10">
         <v>11939</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="10">
         <v>11691</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="10">
         <v>11364</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="10">
         <v>11487</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="10">
         <v>11736</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="10">
         <v>11892</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="10">
         <v>12231</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="10">
         <v>9795</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="10">
         <v>9153</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="2">
         <v>8076</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="Q19" s="2">
         <v>7000</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="3">
         <v>6913</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="3">
         <v>6871</v>
       </c>
-      <c r="T19" s="10">
+      <c r="T19" s="2">
         <v>8349</v>
       </c>
-      <c r="U19" s="14">
+      <c r="U19" s="5">
         <v>7614</v>
       </c>
-      <c r="V19" s="14">
+      <c r="V19" s="5">
         <v>7929</v>
       </c>
-      <c r="W19" s="15">
+      <c r="W19" s="4">
         <v>8147</v>
       </c>
-      <c r="AB19" s="12"/>
+      <c r="X19" s="12">
+        <v>8076</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>8006</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>7929</v>
+      </c>
+      <c r="AB19" s="6"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="10">
         <v>1136</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="10">
         <v>1297</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="10">
         <v>1481</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="10">
         <v>1391</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="10">
         <v>1411</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="10">
         <v>1442</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="10">
         <v>1446</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="10">
         <v>1479</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="10">
         <v>1503</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="10">
         <v>1548</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="10">
         <v>1423</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="10">
         <v>1362</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="2">
         <v>1297</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="Q20" s="2">
         <v>1232</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="3">
         <v>1228</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="3">
         <v>1226</v>
       </c>
-      <c r="T20" s="10">
+      <c r="T20" s="2">
         <v>1354</v>
       </c>
-      <c r="U20" s="14">
+      <c r="U20" s="5">
         <v>1221</v>
       </c>
-      <c r="V20" s="14">
+      <c r="V20" s="5">
         <v>1247</v>
       </c>
-      <c r="W20" s="15">
+      <c r="W20" s="4">
         <v>1271</v>
       </c>
-      <c r="AB20" s="12"/>
+      <c r="X20" s="12">
+        <v>1286</v>
+      </c>
+      <c r="Y20" s="12">
+        <v>1300</v>
+      </c>
+      <c r="Z20" s="5">
+        <v>1400</v>
+      </c>
+      <c r="AB20" s="6"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="10">
         <v>2169</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="10">
         <v>2540</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="10">
         <v>2974</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="10">
         <v>2626</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="10">
         <v>2606</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="10">
         <v>2458</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="10">
         <v>2487</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="10">
         <v>2553</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="10">
         <v>2612</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="10">
         <v>2701</v>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" s="10">
         <v>2243</v>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="10">
         <v>2163</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="2">
         <v>1985</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="Q21" s="2">
         <v>1807</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="3">
         <v>1767</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="3">
         <v>1734</v>
       </c>
-      <c r="T21" s="10">
+      <c r="T21" s="2">
         <v>1955</v>
       </c>
-      <c r="U21" s="14">
+      <c r="U21" s="5">
         <v>1861</v>
       </c>
-      <c r="V21" s="14">
+      <c r="V21" s="5">
         <v>1905</v>
       </c>
-      <c r="W21" s="15">
+      <c r="W21" s="4">
         <v>1925</v>
       </c>
-      <c r="AB21" s="12"/>
+      <c r="X21" s="12">
+        <v>1945</v>
+      </c>
+      <c r="Y21" s="12">
+        <v>1965</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>2046</v>
+      </c>
+      <c r="AB21" s="6"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="T22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="U22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="V22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="W22" s="15" t="s">
+      <c r="D22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z22" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="10">
         <v>15665</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="10">
         <v>18368</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="10">
         <v>21537</v>
       </c>
-      <c r="G23" s="4">
+      <c r="G23" s="10">
         <v>20433</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="10">
         <v>19944</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="10">
         <v>19145</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="10">
         <v>19861</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="10">
         <v>20628</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="10">
         <v>21301</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="10">
         <v>23506</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="10">
         <v>26771</v>
       </c>
-      <c r="O23" s="5">
+      <c r="O23" s="10">
         <v>28509</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="2">
         <v>30834</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="Q23" s="2">
         <v>33159</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="3">
         <v>30941</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="3">
         <v>27786</v>
       </c>
-      <c r="T23" s="10">
+      <c r="T23" s="2">
         <v>21006</v>
       </c>
-      <c r="U23" s="14">
+      <c r="U23" s="5">
         <v>23487</v>
       </c>
-      <c r="V23" s="14">
+      <c r="V23" s="5">
         <v>22116</v>
       </c>
-      <c r="W23" s="15">
+      <c r="W23" s="4">
         <v>19669</v>
       </c>
-      <c r="AB23" s="12"/>
+      <c r="X23" s="12">
+        <v>19659</v>
+      </c>
+      <c r="Y23" s="12">
+        <v>19649</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>20511</v>
+      </c>
+      <c r="AB23" s="6"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="10">
         <v>138</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="10">
         <v>164</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="10">
         <v>195</v>
       </c>
-      <c r="G24" s="4">
+      <c r="G24" s="10">
         <v>163</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="10">
         <v>137</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="10">
         <v>130</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="10">
         <v>134</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="10">
         <v>138</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="10">
         <v>141</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="10">
         <v>143</v>
       </c>
-      <c r="N24" s="5">
+      <c r="N24" s="10">
         <v>144</v>
       </c>
-      <c r="O24" s="5">
+      <c r="O24" s="10">
         <v>137</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="2">
         <v>134</v>
       </c>
-      <c r="Q24" s="9">
+      <c r="Q24" s="2">
         <v>131</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="3">
         <v>134</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="3">
         <v>136</v>
       </c>
-      <c r="T24" s="10">
+      <c r="T24" s="2">
         <v>150</v>
       </c>
-      <c r="U24" s="13">
+      <c r="U24" s="3">
         <v>171</v>
       </c>
-      <c r="V24" s="13">
+      <c r="V24" s="3">
         <v>165</v>
       </c>
-      <c r="W24" s="15">
+      <c r="W24" s="4">
         <v>171</v>
       </c>
+      <c r="X24" s="12">
+        <v>178</v>
+      </c>
+      <c r="Y24" s="12">
+        <v>185</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>191</v>
+      </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="10">
         <v>2679</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="10">
         <v>3363</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="10">
         <v>4222</v>
       </c>
-      <c r="G25" s="4">
+      <c r="G25" s="10">
         <v>4017</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="10">
         <v>4237</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="10">
         <v>4457</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="10">
         <v>4486</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="10">
         <v>4603</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="10">
         <v>4712</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="10">
         <v>4829</v>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" s="10">
         <v>4747</v>
       </c>
-      <c r="O25" s="5">
+      <c r="O25" s="10">
         <v>4653</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="2">
         <v>4598</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="Q25" s="2">
         <v>4543</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="3">
         <v>4637</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="3">
         <v>4731</v>
       </c>
-      <c r="T25" s="10">
+      <c r="T25" s="2">
         <v>5158</v>
       </c>
-      <c r="U25" s="14">
+      <c r="U25" s="5">
         <v>5386</v>
       </c>
-      <c r="V25" s="14">
+      <c r="V25" s="5">
         <v>5258</v>
       </c>
-      <c r="W25" s="15">
+      <c r="W25" s="4">
         <v>5453</v>
       </c>
-      <c r="AB25" s="12"/>
+      <c r="X25" s="12">
+        <v>5391</v>
+      </c>
+      <c r="Y25" s="12">
+        <v>5330</v>
+      </c>
+      <c r="Z25" s="5">
+        <v>4948</v>
+      </c>
+      <c r="AB25" s="6"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="10">
         <v>13941</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="10">
         <v>13971</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="10">
         <v>14001</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="10">
         <v>13558</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="10">
         <v>13365</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="10">
         <v>13602</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J26" s="10">
         <v>13684</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="10">
         <v>13821</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="10">
         <v>13907</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26" s="10">
         <v>14042</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="10">
         <v>13352</v>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="10">
         <v>13096</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="2">
         <v>12760</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q26" s="2">
         <v>12424</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="3">
         <v>12621</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="3">
         <v>12822</v>
       </c>
-      <c r="T26" s="10">
+      <c r="T26" s="2">
         <v>14185</v>
       </c>
-      <c r="U26" s="14">
+      <c r="U26" s="5">
         <v>14884</v>
       </c>
-      <c r="V26" s="14">
+      <c r="V26" s="5">
         <v>14530</v>
       </c>
-      <c r="W26" s="15">
+      <c r="W26" s="4">
         <v>15081</v>
       </c>
-      <c r="AB26" s="12"/>
+      <c r="X26" s="12">
+        <v>15271</v>
+      </c>
+      <c r="Y26" s="12">
+        <v>15462</v>
+      </c>
+      <c r="Z26" s="5">
+        <v>15435</v>
+      </c>
+      <c r="AB26" s="6"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="10">
         <v>59291</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="10">
         <v>55057</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="10">
         <v>51125</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="10">
         <v>57250</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="10">
         <v>58525</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="10">
         <v>60392</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="10">
         <v>60874</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="10">
         <v>62412</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="10">
         <v>64083</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="10">
         <v>65917</v>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="10">
         <v>57715</v>
       </c>
-      <c r="O27" s="5">
+      <c r="O27" s="10">
         <v>59112</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="2">
         <v>57382</v>
       </c>
-      <c r="Q27" s="9">
+      <c r="Q27" s="2">
         <v>55652</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="3">
         <v>58952</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="3">
         <v>62294</v>
       </c>
-      <c r="T27" s="10">
+      <c r="T27" s="2">
         <v>76957</v>
       </c>
-      <c r="U27" s="14">
+      <c r="U27" s="5">
         <v>85406</v>
       </c>
-      <c r="V27" s="14">
+      <c r="V27" s="5">
         <v>82691</v>
       </c>
-      <c r="W27" s="15">
+      <c r="W27" s="4">
         <v>88622</v>
       </c>
-      <c r="AB27" s="12"/>
+      <c r="X27" s="12">
+        <v>91624</v>
+      </c>
+      <c r="Y27" s="12">
+        <v>94626</v>
+      </c>
+      <c r="Z27" s="5">
+        <v>95855</v>
+      </c>
+      <c r="AB27" s="6"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="10">
         <v>6994</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="10">
         <v>7529</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="10">
         <v>8105</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="10">
         <v>7252</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="10">
         <v>7021</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="5">
+      <c r="I28" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="10">
         <v>6782</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="10">
         <v>6597</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="10">
         <v>6318</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="10">
         <v>6104</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="10">
         <v>5957</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="10">
         <v>5457</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="2">
         <v>5122</v>
       </c>
-      <c r="Q28" s="9">
+      <c r="Q28" s="2">
         <v>4787</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="3">
         <v>5120</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="3">
         <v>5460</v>
       </c>
-      <c r="T28" s="10">
+      <c r="T28" s="2">
         <v>6994</v>
       </c>
-      <c r="U28" s="14">
+      <c r="U28" s="5">
         <v>8644</v>
       </c>
-      <c r="V28" s="14">
+      <c r="V28" s="5">
         <v>8255</v>
       </c>
-      <c r="W28" s="15">
+      <c r="W28" s="4">
         <v>8878</v>
       </c>
-      <c r="AB28" s="12"/>
+      <c r="X28" s="12">
+        <v>9076</v>
+      </c>
+      <c r="Y28" s="12">
+        <v>9275</v>
+      </c>
+      <c r="Z28" s="5">
+        <v>8614</v>
+      </c>
+      <c r="AB28" s="6"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="10">
         <v>4071</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="10">
         <v>2521</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="10">
         <v>1561</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="10">
         <v>1664</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="10">
         <v>1328</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="10">
         <v>955</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="10">
         <v>912</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="10">
         <v>847</v>
       </c>
-      <c r="L29" s="5">
+      <c r="L29" s="10">
         <v>803</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29" s="10">
         <v>712</v>
       </c>
-      <c r="N29" s="5">
+      <c r="N29" s="10">
         <v>558</v>
       </c>
-      <c r="O29" s="5">
+      <c r="O29" s="10">
         <v>506</v>
       </c>
-      <c r="P29" s="9">
+      <c r="P29" s="2">
         <v>414</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="Q29" s="2">
         <v>322</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="3">
         <v>326</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="3">
         <v>334</v>
       </c>
-      <c r="T29" s="10">
+      <c r="T29" s="2">
         <v>448</v>
       </c>
-      <c r="U29" s="13">
+      <c r="U29" s="3">
         <v>417</v>
       </c>
-      <c r="V29" s="13">
+      <c r="V29" s="3">
         <v>428</v>
       </c>
-      <c r="W29" s="15">
+      <c r="W29" s="4">
         <v>455</v>
       </c>
+      <c r="X29" s="12">
+        <v>1477</v>
+      </c>
+      <c r="Y29" s="12">
+        <v>2499</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>5560</v>
+      </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="10">
         <v>57899</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="10">
         <v>65594</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="10">
         <v>74312</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="10">
         <v>67826</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="10">
         <v>62048</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="10">
         <v>58469</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="10">
         <v>57182</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="10">
         <v>55394</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30" s="10">
         <v>53276</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30" s="10">
         <v>51987</v>
       </c>
-      <c r="N30" s="5">
+      <c r="N30" s="10">
         <v>51978</v>
       </c>
-      <c r="O30" s="5">
+      <c r="O30" s="10">
         <v>50663</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="2">
         <v>49788</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="Q30" s="2">
         <v>48913</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="3">
         <v>50486</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="3">
         <v>52062</v>
       </c>
-      <c r="T30" s="10">
+      <c r="T30" s="2">
         <v>58170</v>
       </c>
-      <c r="U30" s="14">
+      <c r="U30" s="5">
         <v>59824</v>
       </c>
-      <c r="V30" s="14">
+      <c r="V30" s="5">
         <v>58797</v>
       </c>
-      <c r="W30" s="15">
+      <c r="W30" s="4">
         <v>61410</v>
       </c>
-      <c r="AB30" s="12"/>
+      <c r="X30" s="12">
+        <v>61591</v>
+      </c>
+      <c r="Y30" s="12">
+        <v>61772</v>
+      </c>
+      <c r="Z30" s="5">
+        <v>60156</v>
+      </c>
+      <c r="AB30" s="6"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="10">
         <v>232065</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="10">
         <v>229222</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="10">
         <v>214551</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="10">
         <v>220488</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K31" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="L31" s="5" t="s">
+      <c r="L31" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="M31" s="5" t="s">
+      <c r="M31" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="N31" s="5" t="s">
+      <c r="N31" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="O31" s="5" t="s">
+      <c r="O31" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="P31" s="9">
+      <c r="P31" s="2">
         <v>205647</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="Q31" s="2">
         <v>196280</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="3">
         <v>197409</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="3">
         <v>198784</v>
       </c>
-      <c r="T31" s="10" t="s">
+      <c r="T31" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="U31" s="13" t="s">
+      <c r="U31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="V31" s="13" t="s">
+      <c r="V31" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="W31" s="15">
+      <c r="W31" s="4">
         <v>233433</v>
       </c>
+      <c r="X31" s="12">
+        <v>236635</v>
+      </c>
+      <c r="Y31" s="12">
+        <v>239838</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="10">
         <v>43955</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="10">
         <v>43218</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="10">
         <v>42493</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="10">
         <v>36165</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="10">
         <v>37051</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="10">
         <v>37453</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="10">
         <v>37842</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="10">
         <v>38917</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32" s="10">
         <v>39884</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32" s="10">
         <v>41062</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N32" s="10">
         <v>37304</v>
       </c>
-      <c r="O32" s="5">
+      <c r="O32" s="10">
         <v>36486</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="2">
         <v>35021</v>
       </c>
-      <c r="Q32" s="9">
+      <c r="Q32" s="2">
         <v>33556</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="3">
         <v>33371</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="3">
         <v>33222</v>
       </c>
-      <c r="T32" s="10">
+      <c r="T32" s="2">
         <v>36068</v>
       </c>
-      <c r="U32" s="14">
+      <c r="U32" s="5">
         <v>38102</v>
       </c>
-      <c r="V32" s="14">
+      <c r="V32" s="5">
         <v>37420</v>
       </c>
-      <c r="W32" s="15">
+      <c r="W32" s="4">
         <v>38234</v>
       </c>
-      <c r="AB32" s="12"/>
+      <c r="X32" s="12">
+        <v>38596</v>
+      </c>
+      <c r="Y32" s="12">
+        <v>38958</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>38599</v>
+      </c>
+      <c r="AB32" s="6"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="10">
         <v>1946</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="10">
         <v>2220</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="10">
         <v>2533</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="10">
         <v>2235</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="10">
         <v>2180</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="10">
         <v>2057</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="10">
         <v>2053</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="10">
         <v>2041</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33" s="10">
         <v>2029</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33" s="10">
         <v>2018</v>
       </c>
-      <c r="N33" s="5">
+      <c r="N33" s="10">
         <v>2261</v>
       </c>
-      <c r="O33" s="5">
+      <c r="O33" s="10">
         <v>2276</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="2">
         <v>2363</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="Q33" s="2">
         <v>2450</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="3">
         <v>2437</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="3">
         <v>2427</v>
       </c>
-      <c r="T33" s="10">
+      <c r="T33" s="2">
         <v>2116</v>
       </c>
-      <c r="U33" s="14">
+      <c r="U33" s="5">
         <v>1947</v>
       </c>
-      <c r="V33" s="14">
+      <c r="V33" s="5">
         <v>2003</v>
       </c>
-      <c r="W33" s="15">
+      <c r="W33" s="4">
         <v>1906</v>
       </c>
-      <c r="AB33" s="12"/>
+      <c r="X33" s="12">
+        <v>1936</v>
+      </c>
+      <c r="Y33" s="12">
+        <v>1966</v>
+      </c>
+      <c r="Z33" s="5">
+        <v>2196</v>
+      </c>
+      <c r="AB33" s="6"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="10">
         <v>128227</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="10">
         <v>139951</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="10">
         <v>126867</v>
       </c>
-      <c r="H34" s="4">
+      <c r="H34" s="10">
         <v>126785</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="K34" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="L34" s="5" t="s">
+      <c r="L34" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="M34" s="5" t="s">
+      <c r="M34" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="N34" s="5" t="s">
+      <c r="N34" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="O34" s="5" t="s">
+      <c r="O34" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="P34" s="9">
+      <c r="P34" s="2">
         <v>117790</v>
       </c>
-      <c r="Q34" s="9">
+      <c r="Q34" s="2">
         <v>114206</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="3">
         <v>113754</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="3">
         <v>113366</v>
       </c>
-      <c r="T34" s="10" t="s">
+      <c r="T34" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="U34" s="13" t="s">
+      <c r="U34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="V34" s="13" t="s">
+      <c r="V34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="W34" s="15">
+      <c r="W34" s="4">
         <v>122810</v>
       </c>
+      <c r="X34" s="12">
+        <v>125964</v>
+      </c>
+      <c r="Y34" s="12">
+        <v>129119</v>
+      </c>
+      <c r="Z34" s="3" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="10">
         <v>1226</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="10">
         <v>1220</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="10">
         <v>1214</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G35" s="10">
         <v>1038</v>
       </c>
-      <c r="H35" s="4">
+      <c r="H35" s="10">
         <v>1004</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="10">
         <v>1028</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="10">
         <v>1032</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="10">
         <v>1018</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35" s="10">
         <v>1009</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35" s="10">
         <v>998</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" s="10">
         <v>1075</v>
       </c>
-      <c r="O35" s="5">
+      <c r="O35" s="10">
         <v>1068</v>
       </c>
-      <c r="P35" s="9">
+      <c r="P35" s="2">
         <v>1088</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="Q35" s="2">
         <v>1108</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="3">
         <v>1107</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="3">
         <v>1106</v>
       </c>
-      <c r="T35" s="10">
+      <c r="T35" s="2">
         <v>1035</v>
       </c>
-      <c r="U35" s="14">
+      <c r="U35" s="5">
         <v>1074</v>
       </c>
-      <c r="V35" s="14">
+      <c r="V35" s="5">
         <v>1058</v>
       </c>
-      <c r="W35" s="15">
+      <c r="W35" s="4">
         <v>1046</v>
       </c>
-      <c r="AB35" s="12"/>
+      <c r="X35" s="12">
+        <v>1061</v>
+      </c>
+      <c r="Y35" s="12">
+        <v>1076</v>
+      </c>
+      <c r="Z35" s="5">
+        <v>1114</v>
+      </c>
+      <c r="AB35" s="6"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="10">
         <v>205501</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="10">
         <v>184544</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="10">
         <v>173828</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="10">
         <v>188628</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="K36" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L36" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="M36" s="5" t="s">
+      <c r="M36" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="5" t="s">
+      <c r="N36" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="O36" s="5" t="s">
+      <c r="O36" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="P36" s="9">
+      <c r="P36" s="2">
         <v>177176</v>
       </c>
-      <c r="Q36" s="9">
+      <c r="Q36" s="2">
         <v>171423</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="3">
         <v>172527</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="3">
         <v>173740</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="T36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="U36" s="13" t="s">
+      <c r="U36" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="V36" s="13" t="s">
+      <c r="V36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="W36" s="15">
+      <c r="W36" s="4">
         <v>207739</v>
       </c>
+      <c r="X36" s="12">
+        <v>213357</v>
+      </c>
+      <c r="Y36" s="12">
+        <v>218976</v>
+      </c>
+      <c r="Z36" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="U40" s="8"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="X42" s="6"/>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="X46" s="6"/>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="X47" s="6"/>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="X48" s="6"/>
+    </row>
+    <row r="49" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X49" s="6"/>
+    </row>
+    <row r="53" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X53" s="6"/>
+    </row>
+    <row r="58" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X58" s="6"/>
+    </row>
+    <row r="59" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X59" s="6"/>
+    </row>
+    <row r="60" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X60" s="6"/>
+    </row>
+    <row r="62" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X62" s="6"/>
+    </row>
+    <row r="64" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X64" s="6"/>
+    </row>
+    <row r="65" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X65" s="6"/>
+    </row>
+    <row r="66" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X66" s="6"/>
+    </row>
+    <row r="67" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X67" s="6"/>
+    </row>
+    <row r="68" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X68" s="6"/>
+    </row>
+    <row r="69" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X69" s="6"/>
+    </row>
+    <row r="71" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X71" s="6"/>
+    </row>
+    <row r="72" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X72" s="6"/>
+    </row>
+    <row r="74" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X74" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O36" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}"/>

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAF2891-0C62-7043-9C3E-9830FF0C2A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC9F9D4-04D6-7341-B3EA-5CEEC2E91E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="178">
   <si>
     <t>Category</t>
   </si>
@@ -567,6 +567,12 @@
   </si>
   <si>
     <t>2,24,375</t>
+  </si>
+  <si>
+    <t>Jun26 W3</t>
+  </si>
+  <si>
+    <t>Jun26 W4</t>
   </si>
 </sst>
 </file>
@@ -669,10 +675,10 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1106,8 +1112,12 @@
       <c r="Z1" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
+      <c r="AA1" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1188,6 +1198,12 @@
       <c r="Z2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AA2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1268,7 +1284,12 @@
       <c r="Z3" s="5">
         <v>20511</v>
       </c>
-      <c r="AB3" s="6"/>
+      <c r="AA3" s="5">
+        <v>19597</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>19386</v>
+      </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1349,6 +1370,12 @@
       <c r="Z4" s="3">
         <v>337</v>
       </c>
+      <c r="AA4" s="3">
+        <v>306</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>306</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1429,6 +1456,12 @@
       <c r="Z5" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AA5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1509,6 +1542,12 @@
       <c r="Z6" s="3">
         <v>106</v>
       </c>
+      <c r="AA6" s="3">
+        <v>106</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>106</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1589,7 +1628,12 @@
       <c r="Z7" s="5">
         <v>51110</v>
       </c>
-      <c r="AB7" s="6"/>
+      <c r="AA7" s="5">
+        <v>50804</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>51139</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1670,7 +1714,12 @@
       <c r="Z8" s="5">
         <v>3057</v>
       </c>
-      <c r="AB8" s="6"/>
+      <c r="AA8" s="5">
+        <v>3064</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>3054</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1751,7 +1800,12 @@
       <c r="Z9" s="5">
         <v>9268</v>
       </c>
-      <c r="AB9" s="6"/>
+      <c r="AA9" s="5">
+        <v>9229</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>9230</v>
+      </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -1832,7 +1886,12 @@
       <c r="Z10" s="5">
         <v>79986</v>
       </c>
-      <c r="AB10" s="6"/>
+      <c r="AA10" s="5">
+        <v>79958</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>79806</v>
+      </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -1913,6 +1972,12 @@
       <c r="Z11" s="3" t="s">
         <v>166</v>
       </c>
+      <c r="AA11" s="3">
+        <v>229539</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>229619</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1993,6 +2058,12 @@
       <c r="Z12" s="3" t="s">
         <v>167</v>
       </c>
+      <c r="AA12" s="3">
+        <v>179991</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>179909</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -2073,6 +2144,12 @@
       <c r="Z13" s="3" t="s">
         <v>168</v>
       </c>
+      <c r="AA13" s="3">
+        <v>155085</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>155321</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2153,7 +2230,12 @@
       <c r="Z14" s="5">
         <v>88105</v>
       </c>
-      <c r="AB14" s="6"/>
+      <c r="AA14" s="5">
+        <v>85353</v>
+      </c>
+      <c r="AB14" s="5">
+        <v>86391</v>
+      </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -2234,6 +2316,12 @@
       <c r="Z15" s="3" t="s">
         <v>169</v>
       </c>
+      <c r="AA15" s="3">
+        <v>269169</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>269558</v>
+      </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2314,6 +2402,12 @@
       <c r="Z16" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="AA16" s="3">
+        <v>125689</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>126703</v>
+      </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -2394,6 +2488,12 @@
       <c r="Z17" s="3" t="s">
         <v>171</v>
       </c>
+      <c r="AA17" s="3">
+        <v>705930</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>713077</v>
+      </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2474,6 +2574,12 @@
       <c r="Z18" s="3" t="s">
         <v>172</v>
       </c>
+      <c r="AA18" s="3">
+        <v>721744</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>721187</v>
+      </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
@@ -2554,7 +2660,12 @@
       <c r="Z19" s="5">
         <v>7929</v>
       </c>
-      <c r="AB19" s="6"/>
+      <c r="AA19" s="5">
+        <v>7989</v>
+      </c>
+      <c r="AB19" s="5">
+        <v>7993</v>
+      </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2635,7 +2746,12 @@
       <c r="Z20" s="5">
         <v>1400</v>
       </c>
-      <c r="AB20" s="6"/>
+      <c r="AA20" s="5">
+        <v>1372</v>
+      </c>
+      <c r="AB20" s="5">
+        <v>1384</v>
+      </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -2716,7 +2832,12 @@
       <c r="Z21" s="5">
         <v>2046</v>
       </c>
-      <c r="AB21" s="6"/>
+      <c r="AA21" s="5">
+        <v>2028</v>
+      </c>
+      <c r="AB21" s="5">
+        <v>2041</v>
+      </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2797,6 +2918,12 @@
       <c r="Z22" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="AA22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
@@ -2877,7 +3004,12 @@
       <c r="Z23" s="5">
         <v>20511</v>
       </c>
-      <c r="AB23" s="6"/>
+      <c r="AA23" s="5">
+        <v>19591</v>
+      </c>
+      <c r="AB23" s="5">
+        <v>19364</v>
+      </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -2958,6 +3090,12 @@
       <c r="Z24" s="3">
         <v>191</v>
       </c>
+      <c r="AA24" s="3">
+        <v>192</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>195</v>
+      </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
@@ -3038,7 +3176,12 @@
       <c r="Z25" s="5">
         <v>4948</v>
       </c>
-      <c r="AB25" s="6"/>
+      <c r="AA25" s="5">
+        <v>5108</v>
+      </c>
+      <c r="AB25" s="5">
+        <v>5086</v>
+      </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -3119,7 +3262,12 @@
       <c r="Z26" s="5">
         <v>15435</v>
       </c>
-      <c r="AB26" s="6"/>
+      <c r="AA26" s="5">
+        <v>15612</v>
+      </c>
+      <c r="AB26" s="5">
+        <v>15710</v>
+      </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
@@ -3200,7 +3348,12 @@
       <c r="Z27" s="5">
         <v>95855</v>
       </c>
-      <c r="AB27" s="6"/>
+      <c r="AA27" s="5">
+        <v>97691</v>
+      </c>
+      <c r="AB27" s="5">
+        <v>99168</v>
+      </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -3281,7 +3434,12 @@
       <c r="Z28" s="5">
         <v>8614</v>
       </c>
-      <c r="AB28" s="6"/>
+      <c r="AA28" s="5">
+        <v>9070</v>
+      </c>
+      <c r="AB28" s="5">
+        <v>9151</v>
+      </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
@@ -3362,6 +3520,12 @@
       <c r="Z29" s="5">
         <v>5560</v>
       </c>
+      <c r="AA29" s="5">
+        <v>1980</v>
+      </c>
+      <c r="AB29" s="5">
+        <v>760</v>
+      </c>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -3442,7 +3606,12 @@
       <c r="Z30" s="5">
         <v>60156</v>
       </c>
-      <c r="AB30" s="6"/>
+      <c r="AA30" s="5">
+        <v>61343</v>
+      </c>
+      <c r="AB30" s="5">
+        <v>61537</v>
+      </c>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -3523,6 +3692,12 @@
       <c r="Z31" s="3" t="s">
         <v>173</v>
       </c>
+      <c r="AA31" s="3">
+        <v>241915</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>242484</v>
+      </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -3603,7 +3778,12 @@
       <c r="Z32" s="5">
         <v>38599</v>
       </c>
-      <c r="AB32" s="6"/>
+      <c r="AA32" s="5">
+        <v>38730</v>
+      </c>
+      <c r="AB32" s="5">
+        <v>38775</v>
+      </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
@@ -3684,7 +3864,12 @@
       <c r="Z33" s="5">
         <v>2196</v>
       </c>
-      <c r="AB33" s="6"/>
+      <c r="AA33" s="5">
+        <v>2098</v>
+      </c>
+      <c r="AB33" s="5">
+        <v>2110</v>
+      </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -3765,6 +3950,12 @@
       <c r="Z34" s="3" t="s">
         <v>174</v>
       </c>
+      <c r="AA34" s="3">
+        <v>135429</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>136909</v>
+      </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
@@ -3845,7 +4036,12 @@
       <c r="Z35" s="5">
         <v>1114</v>
       </c>
-      <c r="AB35" s="6"/>
+      <c r="AA35" s="5">
+        <v>1097</v>
+      </c>
+      <c r="AB35" s="5">
+        <v>1098</v>
+      </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -3925,6 +4121,12 @@
       </c>
       <c r="Z36" s="3" t="s">
         <v>175</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>225458</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>227879</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC9F9D4-04D6-7341-B3EA-5CEEC2E91E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFE029D-24E5-AE41-ABE0-A3F35CDBAFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="180">
   <si>
     <t>Category</t>
   </si>
@@ -573,6 +573,12 @@
   </si>
   <si>
     <t>Jun26 W4</t>
+  </si>
+  <si>
+    <t>Jul26 W1</t>
+  </si>
+  <si>
+    <t>Jul26 W2</t>
   </si>
 </sst>
 </file>
@@ -653,7 +659,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -680,6 +686,12 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1016,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AF74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1033,7 +1045,7 @@
     <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1118,8 +1130,16 @@
       <c r="AB1" s="9" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC1" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1204,8 +1224,15 @@
       <c r="AB2" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC2" s="13" t="str">
+        <f t="shared" ref="AC2:AC36" si="0">IF($AD2="-","-",ROUND($AB2+SUMIFS($AH$4:$AH$9,$AF$4:$AF$9,$A2,$AG$4:$AG$9,$B2)*($AD2-$AB2),0))</f>
+        <v>-</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1290,8 +1317,15 @@
       <c r="AB3" s="5">
         <v>19386</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC3" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>19386</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>18054</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1376,8 +1410,15 @@
       <c r="AB4" s="3">
         <v>306</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC4" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>306</v>
+      </c>
+      <c r="AD4" s="13">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1462,8 +1503,15 @@
       <c r="AB5" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC5" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="AD5" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1548,8 +1596,15 @@
       <c r="AB6" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC6" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>106</v>
+      </c>
+      <c r="AD6" s="13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1634,8 +1689,15 @@
       <c r="AB7" s="5">
         <v>51139</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>51139</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>49782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1720,8 +1782,15 @@
       <c r="AB8" s="5">
         <v>3054</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>3054</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1806,8 +1875,15 @@
       <c r="AB9" s="5">
         <v>9230</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>9230</v>
+      </c>
+      <c r="AD9" s="13">
+        <v>11738</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1892,8 +1968,15 @@
       <c r="AB10" s="5">
         <v>79806</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>79806</v>
+      </c>
+      <c r="AD10" s="13">
+        <v>84843</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1978,8 +2061,15 @@
       <c r="AB11" s="3">
         <v>229619</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>229619</v>
+      </c>
+      <c r="AD11" s="13">
+        <v>238024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2064,8 +2154,15 @@
       <c r="AB12" s="3">
         <v>179909</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>179909</v>
+      </c>
+      <c r="AD12" s="13">
+        <v>173515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -2150,8 +2247,15 @@
       <c r="AB13" s="3">
         <v>155321</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>155321</v>
+      </c>
+      <c r="AD13" s="13">
+        <v>162351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2236,8 +2340,15 @@
       <c r="AB14" s="5">
         <v>86391</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>86391</v>
+      </c>
+      <c r="AD14" s="13">
+        <v>91784</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -2322,8 +2433,15 @@
       <c r="AB15" s="3">
         <v>269558</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>269558</v>
+      </c>
+      <c r="AD15" s="13">
+        <v>311607</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2408,8 +2526,15 @@
       <c r="AB16" s="3">
         <v>126703</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>126703</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>136274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2494,8 +2619,15 @@
       <c r="AB17" s="3">
         <v>713077</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>713077</v>
+      </c>
+      <c r="AD17" s="13">
+        <v>811831</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2580,8 +2712,15 @@
       <c r="AB18" s="3">
         <v>721187</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>721187</v>
+      </c>
+      <c r="AD18" s="13">
+        <v>773824</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -2666,8 +2805,15 @@
       <c r="AB19" s="5">
         <v>7993</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>7993</v>
+      </c>
+      <c r="AD19" s="13">
+        <v>7759</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -2752,8 +2898,15 @@
       <c r="AB20" s="5">
         <v>1384</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>1384</v>
+      </c>
+      <c r="AD20" s="13">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -2838,8 +2991,15 @@
       <c r="AB21" s="5">
         <v>2041</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>2041</v>
+      </c>
+      <c r="AD21" s="13">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -2924,8 +3084,15 @@
       <c r="AB22" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>-</v>
+      </c>
+      <c r="AD22" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -3010,8 +3177,15 @@
       <c r="AB23" s="5">
         <v>19364</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>19364</v>
+      </c>
+      <c r="AD23" s="13">
+        <v>18054</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3096,8 +3270,15 @@
       <c r="AB24" s="3">
         <v>195</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="AD24" s="13">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3182,8 +3363,15 @@
       <c r="AB25" s="5">
         <v>5086</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>5086</v>
+      </c>
+      <c r="AD25" s="13">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -3268,8 +3456,15 @@
       <c r="AB26" s="5">
         <v>15710</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>15710</v>
+      </c>
+      <c r="AD26" s="13">
+        <v>15346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -3354,8 +3549,15 @@
       <c r="AB27" s="5">
         <v>99168</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>99168</v>
+      </c>
+      <c r="AD27" s="13">
+        <v>99365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -3440,8 +3642,15 @@
       <c r="AB28" s="5">
         <v>9151</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>9151</v>
+      </c>
+      <c r="AD28" s="13">
+        <v>9174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -3526,8 +3735,15 @@
       <c r="AB29" s="5">
         <v>760</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="AD29" s="13">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3612,8 +3828,15 @@
       <c r="AB30" s="5">
         <v>61537</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>61537</v>
+      </c>
+      <c r="AD30" s="13">
+        <v>66523</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,8 +3921,15 @@
       <c r="AB31" s="3">
         <v>242484</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>242484</v>
+      </c>
+      <c r="AD31" s="13">
+        <v>245897</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -3784,8 +4014,15 @@
       <c r="AB32" s="5">
         <v>38775</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>38775</v>
+      </c>
+      <c r="AD32" s="13">
+        <v>39782</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -3870,8 +4107,15 @@
       <c r="AB33" s="5">
         <v>2110</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>2110</v>
+      </c>
+      <c r="AD33" s="13">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -3956,8 +4200,15 @@
       <c r="AB34" s="3">
         <v>136909</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>136909</v>
+      </c>
+      <c r="AD34" s="13">
+        <v>132948</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -4042,8 +4293,15 @@
       <c r="AB35" s="5">
         <v>1098</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>1098</v>
+      </c>
+      <c r="AD35" s="13">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4128,23 +4386,30 @@
       <c r="AB36" s="3">
         <v>227879</v>
       </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC36" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>227879</v>
+      </c>
+      <c r="AD36" s="13">
+        <v>242948</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
       <c r="X42" s="6"/>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="X46" s="6"/>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="X48" s="6"/>
     </row>
     <row r="49" spans="24:24" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFE029D-24E5-AE41-ABE0-A3F35CDBAFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC67D52-576F-6142-B0B3-2446D53990E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="181">
   <si>
     <t>Category</t>
   </si>
@@ -579,6 +579,9 @@
   </si>
   <si>
     <t>Jul26 W2</t>
+  </si>
+  <si>
+    <t>Jul26 W3</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1139,9 @@
       <c r="AD1" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" s="9"/>
+      <c r="AE1" s="9" t="s">
+        <v>180</v>
+      </c>
       <c r="AF1" s="9"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
@@ -1231,6 +1236,9 @@
       <c r="AD2" s="14" t="s">
         <v>18</v>
       </c>
+      <c r="AE2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1324,6 +1332,9 @@
       <c r="AD3" s="13">
         <v>18054</v>
       </c>
+      <c r="AE3" s="1">
+        <v>17926</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1417,6 +1428,9 @@
       <c r="AD4" s="13">
         <v>283</v>
       </c>
+      <c r="AE4" s="1">
+        <v>281</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -1510,6 +1524,9 @@
       <c r="AD5" s="14" t="s">
         <v>18</v>
       </c>
+      <c r="AE5" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1603,6 +1620,9 @@
       <c r="AD6" s="13">
         <v>106</v>
       </c>
+      <c r="AE6" s="1">
+        <v>106</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1696,6 +1716,9 @@
       <c r="AD7" s="13">
         <v>49782</v>
       </c>
+      <c r="AE7" s="1">
+        <v>49648</v>
+      </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1789,6 +1812,9 @@
       <c r="AD8" s="13">
         <v>2883</v>
       </c>
+      <c r="AE8" s="1">
+        <v>2866</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1882,6 +1908,9 @@
       <c r="AD9" s="13">
         <v>11738</v>
       </c>
+      <c r="AE9" s="1">
+        <v>12024</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -1975,6 +2004,9 @@
       <c r="AD10" s="13">
         <v>84843</v>
       </c>
+      <c r="AE10" s="1">
+        <v>85364</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -2068,6 +2100,9 @@
       <c r="AD11" s="13">
         <v>238024</v>
       </c>
+      <c r="AE11" s="1">
+        <v>238881</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -2161,6 +2196,9 @@
       <c r="AD12" s="13">
         <v>173515</v>
       </c>
+      <c r="AE12" s="1">
+        <v>172888</v>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -2254,6 +2292,9 @@
       <c r="AD13" s="13">
         <v>162351</v>
       </c>
+      <c r="AE13" s="1">
+        <v>163071</v>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2347,6 +2388,9 @@
       <c r="AD14" s="13">
         <v>91784</v>
       </c>
+      <c r="AE14" s="1">
+        <v>92341</v>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
@@ -2440,6 +2484,9 @@
       <c r="AD15" s="13">
         <v>311607</v>
       </c>
+      <c r="AE15" s="1">
+        <v>316157</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2533,8 +2580,11 @@
       <c r="AD16" s="13">
         <v>136274</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="1">
+        <v>137270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2626,8 +2676,11 @@
       <c r="AD17" s="13">
         <v>811831</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="1">
+        <v>822429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2719,8 +2772,11 @@
       <c r="AD18" s="13">
         <v>773824</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="1">
+        <v>779295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -2812,8 +2868,11 @@
       <c r="AD19" s="13">
         <v>7759</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="1">
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -2905,8 +2964,11 @@
       <c r="AD20" s="13">
         <v>1405</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="1">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -2998,8 +3060,11 @@
       <c r="AD21" s="13">
         <v>2048</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="1">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -3091,8 +3156,11 @@
       <c r="AD22" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -3184,8 +3252,11 @@
       <c r="AD23" s="13">
         <v>18054</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="1">
+        <v>17928</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3277,8 +3348,11 @@
       <c r="AD24" s="13">
         <v>178</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3370,8 +3444,11 @@
       <c r="AD25" s="13">
         <v>5104</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="1">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -3463,8 +3540,11 @@
       <c r="AD26" s="13">
         <v>15346</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="1">
+        <v>15310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -3556,8 +3636,11 @@
       <c r="AD27" s="13">
         <v>99365</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="1">
+        <v>99385</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -3649,8 +3732,11 @@
       <c r="AD28" s="13">
         <v>9174</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="1">
+        <v>9176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -3742,8 +3828,11 @@
       <c r="AD29" s="13">
         <v>1253</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="1">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3835,8 +3924,11 @@
       <c r="AD30" s="13">
         <v>66523</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="1">
+        <v>67043</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,8 +4020,11 @@
       <c r="AD31" s="13">
         <v>245897</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="1">
+        <v>246241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -4021,8 +4116,11 @@
       <c r="AD32" s="13">
         <v>39782</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="1">
+        <v>39884</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -4114,8 +4212,11 @@
       <c r="AD33" s="13">
         <v>2129</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="1">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -4207,8 +4308,11 @@
       <c r="AD34" s="13">
         <v>132948</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="1">
+        <v>132558</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -4300,8 +4404,11 @@
       <c r="AD35" s="13">
         <v>1110</v>
       </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4393,23 +4500,26 @@
       <c r="AD36" s="13">
         <v>242948</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE36" s="1">
+        <v>244509</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="X42" s="6"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="X46" s="6"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="X48" s="6"/>
     </row>
     <row r="49" spans="24:24" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC67D52-576F-6142-B0B3-2446D53990E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8A6A1E-7DBB-094D-8733-CFC2DB6BC99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="185">
   <si>
     <t>Category</t>
   </si>
@@ -582,6 +582,18 @@
   </si>
   <si>
     <t>Jul26 W3</t>
+  </si>
+  <si>
+    <t>Snacks</t>
+  </si>
+  <si>
+    <t>Let's try</t>
+  </si>
+  <si>
+    <t>Lets try</t>
+  </si>
+  <si>
+    <t>Jul26 W4</t>
   </si>
 </sst>
 </file>
@@ -662,7 +674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -680,12 +692,8 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -695,6 +703,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1045,7 +1062,9 @@
     <col min="23" max="23" width="11.33203125" style="1" customWidth="1"/>
     <col min="24" max="25" width="10.83203125" style="1"/>
     <col min="26" max="26" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="10.83203125" style="1"/>
+    <col min="27" max="30" width="10.83203125" style="1"/>
+    <col min="31" max="31" width="10.83203125" style="3"/>
+    <col min="32" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
@@ -1058,91 +1077,93 @@
       <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AE1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="AF1" s="9"/>
+      <c r="AF1" s="13" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1154,40 +1175,40 @@
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="10" t="s">
+      <c r="D2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="P2" s="2" t="s">
@@ -1214,10 +1235,10 @@
       <c r="W2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="X2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2" s="11" t="s">
+      <c r="X2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y2" s="15" t="s">
         <v>18</v>
       </c>
       <c r="Z2" s="3" t="s">
@@ -1229,14 +1250,16 @@
       <c r="AB2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" s="13" t="str">
-        <f t="shared" ref="AC2:AC36" si="0">IF($AD2="-","-",ROUND($AB2+SUMIFS($AH$4:$AH$9,$AF$4:$AF$9,$A2,$AG$4:$AG$9,$B2)*($AD2-$AB2),0))</f>
-        <v>-</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AC2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1250,40 +1273,40 @@
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>15665</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>18368</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>21537</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>20433</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>19944</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>19145</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>19872</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>20641</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>21287</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>23518</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>26771</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>28509</v>
       </c>
       <c r="P3" s="2">
@@ -1310,10 +1333,10 @@
       <c r="W3" s="4">
         <v>19589</v>
       </c>
-      <c r="X3" s="12">
+      <c r="X3" s="10">
         <v>19584</v>
       </c>
-      <c r="Y3" s="12">
+      <c r="Y3" s="10">
         <v>19580</v>
       </c>
       <c r="Z3" s="5">
@@ -1325,15 +1348,17 @@
       <c r="AB3" s="5">
         <v>19386</v>
       </c>
-      <c r="AC3" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC3" s="11">
         <v>19386</v>
       </c>
-      <c r="AD3" s="13">
+      <c r="AD3" s="11">
         <v>18054</v>
       </c>
-      <c r="AE3" s="1">
+      <c r="AE3" s="3">
         <v>17926</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>20489</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
@@ -1346,40 +1371,40 @@
       <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>227</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>267</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>314</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>302</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>309</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>319</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>323</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>331</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>339</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>358</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>398</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>408</v>
       </c>
       <c r="P4" s="2">
@@ -1406,10 +1431,10 @@
       <c r="W4" s="4">
         <v>237</v>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="10">
         <v>253</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="10">
         <v>268</v>
       </c>
       <c r="Z4" s="3">
@@ -1421,15 +1446,17 @@
       <c r="AB4" s="3">
         <v>306</v>
       </c>
-      <c r="AC4" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC4" s="11">
         <v>306</v>
       </c>
-      <c r="AD4" s="13">
+      <c r="AD4" s="11">
         <v>283</v>
       </c>
-      <c r="AE4" s="1">
+      <c r="AE4" s="3">
         <v>281</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
@@ -1442,40 +1469,40 @@
       <c r="C5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="P5" s="2" t="s">
@@ -1502,10 +1529,10 @@
       <c r="W5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="X5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y5" s="11" t="s">
+      <c r="X5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y5" s="15" t="s">
         <v>18</v>
       </c>
       <c r="Z5" s="3" t="s">
@@ -1517,14 +1544,16 @@
       <c r="AB5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AC5" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="AD5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AC5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1538,40 +1567,40 @@
       <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>106</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>106</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>106</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>106</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>106</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>106</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>106</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>106</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>106</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>106</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>106</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="9">
         <v>106</v>
       </c>
       <c r="P6" s="2">
@@ -1598,10 +1627,10 @@
       <c r="W6" s="4">
         <v>106</v>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="10">
         <v>106</v>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="10">
         <v>106</v>
       </c>
       <c r="Z6" s="3">
@@ -1613,14 +1642,16 @@
       <c r="AB6" s="3">
         <v>106</v>
       </c>
-      <c r="AC6" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC6" s="11">
         <v>106</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="11">
         <v>106</v>
       </c>
-      <c r="AE6" s="1">
+      <c r="AE6" s="3">
+        <v>106</v>
+      </c>
+      <c r="AF6" s="3">
         <v>106</v>
       </c>
     </row>
@@ -1634,40 +1665,40 @@
       <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>35550</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>36638</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>37759</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>38048</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>39236</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>40115</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>41183</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>42067</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>43149</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <v>43872</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <v>44083</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <v>44891</v>
       </c>
       <c r="P7" s="2">
@@ -1694,10 +1725,10 @@
       <c r="W7" s="4">
         <v>47748</v>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="10">
         <v>48609</v>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="10">
         <v>49470</v>
       </c>
       <c r="Z7" s="5">
@@ -1709,15 +1740,17 @@
       <c r="AB7" s="5">
         <v>51139</v>
       </c>
-      <c r="AC7" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC7" s="11">
         <v>51139</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AD7" s="11">
         <v>49782</v>
       </c>
-      <c r="AE7" s="1">
+      <c r="AE7" s="3">
         <v>49648</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>50940</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
@@ -1730,40 +1763,40 @@
       <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>1858</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>1820</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>1783</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>1789</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>1725</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>2427</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="9">
         <v>2463</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <v>2517</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>2604</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <v>2748</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>2883</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>2960</v>
       </c>
       <c r="P8" s="2">
@@ -1790,10 +1823,10 @@
       <c r="W8" s="4">
         <v>3148</v>
       </c>
-      <c r="X8" s="12">
+      <c r="X8" s="10">
         <v>3123</v>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="10">
         <v>3098</v>
       </c>
       <c r="Z8" s="5">
@@ -1805,15 +1838,17 @@
       <c r="AB8" s="5">
         <v>3054</v>
       </c>
-      <c r="AC8" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC8" s="11">
         <v>3054</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AD8" s="11">
         <v>2883</v>
       </c>
-      <c r="AE8" s="1">
+      <c r="AE8" s="3">
         <v>2866</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>2953</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
@@ -1826,40 +1861,40 @@
       <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>5864</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>6486</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>7174</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>7150</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>7723</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>7920</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>8118</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>8397</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>8713</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>9026</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <v>9043</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="9">
         <v>9368</v>
       </c>
       <c r="P9" s="2">
@@ -1886,10 +1921,10 @@
       <c r="W9" s="4">
         <v>9230</v>
       </c>
-      <c r="X9" s="12">
+      <c r="X9" s="10">
         <v>9178</v>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="10">
         <v>9125</v>
       </c>
       <c r="Z9" s="5">
@@ -1901,15 +1936,17 @@
       <c r="AB9" s="5">
         <v>9230</v>
       </c>
-      <c r="AC9" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC9" s="11">
         <v>9230</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AD9" s="11">
         <v>11738</v>
       </c>
-      <c r="AE9" s="1">
+      <c r="AE9" s="3">
         <v>12024</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>13652</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
@@ -1922,40 +1959,40 @@
       <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>71964</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>70213</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>68505</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>73263</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>74778</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>78638</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>79842</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>81536</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>83127</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>84418</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>84623</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="9">
         <v>82556</v>
       </c>
       <c r="P10" s="2">
@@ -1982,10 +2019,10 @@
       <c r="W10" s="4">
         <v>81479</v>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="10">
         <v>80893</v>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="10">
         <v>80306</v>
       </c>
       <c r="Z10" s="5">
@@ -1997,15 +2034,17 @@
       <c r="AB10" s="5">
         <v>79806</v>
       </c>
-      <c r="AC10" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC10" s="11">
         <v>79806</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AD10" s="11">
         <v>84843</v>
       </c>
-      <c r="AE10" s="1">
+      <c r="AE10" s="3">
         <v>85364</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>92830</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
@@ -2018,40 +2057,40 @@
       <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>232749</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>242993</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>253688</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>229817</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>232951</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>35</v>
       </c>
       <c r="P11" s="2">
@@ -2078,10 +2117,10 @@
       <c r="W11" s="4">
         <v>190412</v>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="10">
         <v>198533</v>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="10">
         <v>206655</v>
       </c>
       <c r="Z11" s="3" t="s">
@@ -2093,15 +2132,17 @@
       <c r="AB11" s="3">
         <v>229619</v>
       </c>
-      <c r="AC11" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC11" s="11">
         <v>229619</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AD11" s="11">
         <v>238024</v>
       </c>
-      <c r="AE11" s="1">
+      <c r="AE11" s="3">
         <v>238881</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>260076</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
@@ -2114,40 +2155,40 @@
       <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>75862</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>63740</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>53555</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>68500</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>98599</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>79484</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="9">
         <v>81327</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="9">
         <v>84612</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>88943</v>
       </c>
-      <c r="M12" s="10" t="s">
+      <c r="M12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>39</v>
       </c>
       <c r="P12" s="2">
@@ -2174,10 +2215,10 @@
       <c r="W12" s="4">
         <v>168639</v>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="10">
         <v>171404</v>
       </c>
-      <c r="Y12" s="12">
+      <c r="Y12" s="10">
         <v>174170</v>
       </c>
       <c r="Z12" s="3" t="s">
@@ -2189,15 +2230,17 @@
       <c r="AB12" s="3">
         <v>179909</v>
       </c>
-      <c r="AC12" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC12" s="11">
         <v>179909</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AD12" s="11">
         <v>173515</v>
       </c>
-      <c r="AE12" s="1">
+      <c r="AE12" s="3">
         <v>172888</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>179901</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
@@ -2210,40 +2253,40 @@
       <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>120329</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>127681</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>135482</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>131019</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <v>132408</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M13" s="10" t="s">
+      <c r="M13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="N13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="9" t="s">
         <v>47</v>
       </c>
       <c r="P13" s="2">
@@ -2270,10 +2313,10 @@
       <c r="W13" s="4">
         <v>146511</v>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="10">
         <v>148663</v>
       </c>
-      <c r="Y13" s="12">
+      <c r="Y13" s="10">
         <v>150815</v>
       </c>
       <c r="Z13" s="3" t="s">
@@ -2285,15 +2328,17 @@
       <c r="AB13" s="3">
         <v>155321</v>
       </c>
-      <c r="AC13" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC13" s="11">
         <v>155321</v>
       </c>
-      <c r="AD13" s="13">
+      <c r="AD13" s="11">
         <v>162351</v>
       </c>
-      <c r="AE13" s="1">
+      <c r="AE13" s="3">
         <v>163071</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>171760</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
@@ -2306,40 +2351,40 @@
       <c r="C14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>33458</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>28690</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>24601</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>30975</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <v>33624</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>36455</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <v>37648</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
         <v>39982</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>42731</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <v>50184</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>57210</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>65597</v>
       </c>
       <c r="P14" s="2">
@@ -2366,10 +2411,10 @@
       <c r="W14" s="4">
         <v>74001</v>
       </c>
-      <c r="X14" s="12">
+      <c r="X14" s="10">
         <v>76698</v>
       </c>
-      <c r="Y14" s="12">
+      <c r="Y14" s="10">
         <v>79396</v>
       </c>
       <c r="Z14" s="5">
@@ -2381,15 +2426,17 @@
       <c r="AB14" s="5">
         <v>86391</v>
       </c>
-      <c r="AC14" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC14" s="11">
         <v>86391</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AD14" s="11">
         <v>91784</v>
       </c>
-      <c r="AE14" s="1">
+      <c r="AE14" s="3">
         <v>92341</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>97772</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
@@ -2402,40 +2449,40 @@
       <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>245157</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>246726</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>248305</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>235711</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="9">
         <v>237839</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="10" t="s">
+      <c r="M15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="10" t="s">
+      <c r="N15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="10" t="s">
+      <c r="O15" s="9" t="s">
         <v>57</v>
       </c>
       <c r="P15" s="2">
@@ -2462,10 +2509,10 @@
       <c r="W15" s="4">
         <v>257190</v>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="10">
         <v>260444</v>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y15" s="10">
         <v>263698</v>
       </c>
       <c r="Z15" s="3" t="s">
@@ -2477,15 +2524,17 @@
       <c r="AB15" s="3">
         <v>269558</v>
       </c>
-      <c r="AC15" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC15" s="11">
         <v>269558</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AD15" s="11">
         <v>311607</v>
       </c>
-      <c r="AE15" s="1">
+      <c r="AE15" s="3">
         <v>316157</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>358778</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
@@ -2498,40 +2547,40 @@
       <c r="C16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>96559</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>87884</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>79988</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>87364</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="9">
         <v>91089</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="N16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P16" s="2">
@@ -2558,10 +2607,10 @@
       <c r="W16" s="4">
         <v>108615</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="10">
         <v>112718</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="10">
         <v>116820</v>
       </c>
       <c r="Z16" s="3" t="s">
@@ -2573,18 +2622,20 @@
       <c r="AB16" s="3">
         <v>126703</v>
       </c>
-      <c r="AC16" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC16" s="11">
         <v>126703</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AD16" s="11">
         <v>136274</v>
       </c>
-      <c r="AE16" s="1">
+      <c r="AE16" s="3">
         <v>137270</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3">
+        <v>159166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2594,40 +2645,40 @@
       <c r="C17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>651237</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>671360</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>692105</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>676705</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <v>673347</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="M17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="N17" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="P17" s="2">
@@ -2654,10 +2705,10 @@
       <c r="W17" s="4">
         <v>639961</v>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="10">
         <v>658429</v>
       </c>
-      <c r="Y17" s="12">
+      <c r="Y17" s="10">
         <v>676897</v>
       </c>
       <c r="Z17" s="3" t="s">
@@ -2669,18 +2720,20 @@
       <c r="AB17" s="3">
         <v>713077</v>
       </c>
-      <c r="AC17" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC17" s="11">
         <v>713077</v>
       </c>
-      <c r="AD17" s="13">
+      <c r="AD17" s="11">
         <v>811831</v>
       </c>
-      <c r="AE17" s="1">
+      <c r="AE17" s="3">
         <v>822429</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>949630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2690,40 +2743,40 @@
       <c r="C18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>562535</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>602579</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>645474</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>567830</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>582701</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="M18" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="N18" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="O18" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P18" s="2">
@@ -2750,10 +2803,10 @@
       <c r="W18" s="4">
         <v>688213</v>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="10">
         <v>694998</v>
       </c>
-      <c r="Y18" s="12">
+      <c r="Y18" s="10">
         <v>701782</v>
       </c>
       <c r="Z18" s="3" t="s">
@@ -2765,18 +2818,20 @@
       <c r="AB18" s="3">
         <v>721187</v>
       </c>
-      <c r="AC18" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC18" s="11">
         <v>721187</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AD18" s="11">
         <v>773824</v>
       </c>
-      <c r="AE18" s="1">
+      <c r="AE18" s="3">
         <v>779295</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>850631</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -2786,40 +2841,40 @@
       <c r="C19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>9702</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>11370</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>13325</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>11939</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <v>11691</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>11364</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>11487</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="9">
         <v>11736</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>11892</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>12231</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>9795</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>9153</v>
       </c>
       <c r="P19" s="2">
@@ -2846,10 +2901,10 @@
       <c r="W19" s="4">
         <v>8147</v>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="10">
         <v>8076</v>
       </c>
-      <c r="Y19" s="12">
+      <c r="Y19" s="10">
         <v>8006</v>
       </c>
       <c r="Z19" s="5">
@@ -2861,18 +2916,20 @@
       <c r="AB19" s="5">
         <v>7993</v>
       </c>
-      <c r="AC19" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC19" s="11">
         <v>7993</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="11">
         <v>7759</v>
       </c>
-      <c r="AE19" s="1">
+      <c r="AE19" s="3">
         <v>7736</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3">
+        <v>8608</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -2882,40 +2939,40 @@
       <c r="C20" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>1136</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>1297</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>1481</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>1391</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="9">
         <v>1411</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>1442</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <v>1446</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="9">
         <v>1479</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>1503</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="9">
         <v>1548</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>1423</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>1362</v>
       </c>
       <c r="P20" s="2">
@@ -2942,10 +2999,10 @@
       <c r="W20" s="4">
         <v>1271</v>
       </c>
-      <c r="X20" s="12">
+      <c r="X20" s="10">
         <v>1286</v>
       </c>
-      <c r="Y20" s="12">
+      <c r="Y20" s="10">
         <v>1300</v>
       </c>
       <c r="Z20" s="5">
@@ -2957,18 +3014,20 @@
       <c r="AB20" s="5">
         <v>1384</v>
       </c>
-      <c r="AC20" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC20" s="11">
         <v>1384</v>
       </c>
-      <c r="AD20" s="13">
+      <c r="AD20" s="11">
         <v>1405</v>
       </c>
-      <c r="AE20" s="1">
+      <c r="AE20" s="3">
         <v>1407</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -2978,40 +3037,40 @@
       <c r="C21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>2169</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>2540</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>2974</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>2626</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="9">
         <v>2606</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>2458</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <v>2487</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="9">
         <v>2553</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <v>2612</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="9">
         <v>2701</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="9">
         <v>2243</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="9">
         <v>2163</v>
       </c>
       <c r="P21" s="2">
@@ -3038,10 +3097,10 @@
       <c r="W21" s="4">
         <v>1925</v>
       </c>
-      <c r="X21" s="12">
+      <c r="X21" s="10">
         <v>1945</v>
       </c>
-      <c r="Y21" s="12">
+      <c r="Y21" s="10">
         <v>1965</v>
       </c>
       <c r="Z21" s="5">
@@ -3053,18 +3112,20 @@
       <c r="AB21" s="5">
         <v>2041</v>
       </c>
-      <c r="AC21" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC21" s="11">
         <v>2041</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AD21" s="11">
         <v>2048</v>
       </c>
-      <c r="AE21" s="1">
+      <c r="AE21" s="3">
         <v>2049</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -3074,40 +3135,40 @@
       <c r="C22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="10" t="s">
+      <c r="D22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="9" t="s">
         <v>18</v>
       </c>
       <c r="P22" s="2" t="s">
@@ -3134,10 +3195,10 @@
       <c r="W22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="X22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y22" s="11" t="s">
+      <c r="X22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y22" s="15" t="s">
         <v>18</v>
       </c>
       <c r="Z22" s="3" t="s">
@@ -3149,18 +3210,20 @@
       <c r="AB22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AC22" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>-</v>
-      </c>
-      <c r="AD22" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AC22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -3170,40 +3233,40 @@
       <c r="C23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>15665</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>18368</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>21537</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>20433</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="9">
         <v>19944</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="9">
         <v>19145</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <v>19861</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="9">
         <v>20628</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="9">
         <v>21301</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="9">
         <v>23506</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="9">
         <v>26771</v>
       </c>
-      <c r="O23" s="10">
+      <c r="O23" s="9">
         <v>28509</v>
       </c>
       <c r="P23" s="2">
@@ -3230,10 +3293,10 @@
       <c r="W23" s="4">
         <v>19669</v>
       </c>
-      <c r="X23" s="12">
+      <c r="X23" s="10">
         <v>19659</v>
       </c>
-      <c r="Y23" s="12">
+      <c r="Y23" s="10">
         <v>19649</v>
       </c>
       <c r="Z23" s="5">
@@ -3245,18 +3308,20 @@
       <c r="AB23" s="5">
         <v>19364</v>
       </c>
-      <c r="AC23" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC23" s="11">
         <v>19364</v>
       </c>
-      <c r="AD23" s="13">
+      <c r="AD23" s="11">
         <v>18054</v>
       </c>
-      <c r="AE23" s="1">
+      <c r="AE23" s="3">
         <v>17928</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>20489</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3266,40 +3331,40 @@
       <c r="C24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>138</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>164</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="9">
         <v>195</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>163</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="9">
         <v>137</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="9">
         <v>130</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="9">
         <v>134</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="9">
         <v>138</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="9">
         <v>141</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="9">
         <v>143</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="9">
         <v>144</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="9">
         <v>137</v>
       </c>
       <c r="P24" s="2">
@@ -3326,10 +3391,10 @@
       <c r="W24" s="4">
         <v>171</v>
       </c>
-      <c r="X24" s="12">
+      <c r="X24" s="10">
         <v>178</v>
       </c>
-      <c r="Y24" s="12">
+      <c r="Y24" s="10">
         <v>185</v>
       </c>
       <c r="Z24" s="3">
@@ -3341,18 +3406,20 @@
       <c r="AB24" s="3">
         <v>195</v>
       </c>
-      <c r="AC24" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC24" s="11">
         <v>195</v>
       </c>
-      <c r="AD24" s="13">
+      <c r="AD24" s="11">
         <v>178</v>
       </c>
-      <c r="AE24" s="1">
+      <c r="AE24" s="3">
         <v>176</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3362,40 +3429,40 @@
       <c r="C25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>2679</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>3363</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>4222</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>4017</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="9">
         <v>4237</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="9">
         <v>4457</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="9">
         <v>4486</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="9">
         <v>4603</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="9">
         <v>4712</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="9">
         <v>4829</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="9">
         <v>4747</v>
       </c>
-      <c r="O25" s="10">
+      <c r="O25" s="9">
         <v>4653</v>
       </c>
       <c r="P25" s="2">
@@ -3422,10 +3489,10 @@
       <c r="W25" s="4">
         <v>5453</v>
       </c>
-      <c r="X25" s="12">
+      <c r="X25" s="10">
         <v>5391</v>
       </c>
-      <c r="Y25" s="12">
+      <c r="Y25" s="10">
         <v>5330</v>
       </c>
       <c r="Z25" s="5">
@@ -3437,18 +3504,20 @@
       <c r="AB25" s="5">
         <v>5086</v>
       </c>
-      <c r="AC25" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC25" s="11">
         <v>5086</v>
       </c>
-      <c r="AD25" s="13">
+      <c r="AD25" s="11">
         <v>5104</v>
       </c>
-      <c r="AE25" s="1">
+      <c r="AE25" s="3">
         <v>5106</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>5685</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -3458,40 +3527,40 @@
       <c r="C26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>13941</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>13971</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <v>14001</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>13558</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="9">
         <v>13365</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="9">
         <v>13602</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="9">
         <v>13684</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="9">
         <v>13821</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="9">
         <v>13907</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="9">
         <v>14042</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="9">
         <v>13352</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="9">
         <v>13096</v>
       </c>
       <c r="P26" s="2">
@@ -3518,10 +3587,10 @@
       <c r="W26" s="4">
         <v>15081</v>
       </c>
-      <c r="X26" s="12">
+      <c r="X26" s="10">
         <v>15271</v>
       </c>
-      <c r="Y26" s="12">
+      <c r="Y26" s="10">
         <v>15462</v>
       </c>
       <c r="Z26" s="5">
@@ -3533,18 +3602,20 @@
       <c r="AB26" s="5">
         <v>15710</v>
       </c>
-      <c r="AC26" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC26" s="11">
         <v>15710</v>
       </c>
-      <c r="AD26" s="13">
+      <c r="AD26" s="11">
         <v>15346</v>
       </c>
-      <c r="AE26" s="1">
+      <c r="AE26" s="3">
         <v>15310</v>
       </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>17234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -3554,40 +3625,40 @@
       <c r="C27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>59291</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>55057</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>51125</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>57250</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="9">
         <v>58525</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="9">
         <v>60392</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="9">
         <v>60874</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="9">
         <v>62412</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="9">
         <v>64083</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="9">
         <v>65917</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="9">
         <v>57715</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="9">
         <v>59112</v>
       </c>
       <c r="P27" s="2">
@@ -3614,10 +3685,10 @@
       <c r="W27" s="4">
         <v>88622</v>
       </c>
-      <c r="X27" s="12">
+      <c r="X27" s="10">
         <v>91624</v>
       </c>
-      <c r="Y27" s="12">
+      <c r="Y27" s="10">
         <v>94626</v>
       </c>
       <c r="Z27" s="5">
@@ -3629,18 +3700,20 @@
       <c r="AB27" s="5">
         <v>99168</v>
       </c>
-      <c r="AC27" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC27" s="11">
         <v>99168</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="AD27" s="11">
         <v>99365</v>
       </c>
-      <c r="AE27" s="1">
+      <c r="AE27" s="3">
         <v>99385</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>109652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -3650,40 +3723,40 @@
       <c r="C28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>6994</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>7529</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>8105</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>7252</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="9">
         <v>7021</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="10">
+      <c r="I28" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="9">
         <v>6782</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="9">
         <v>6597</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="9">
         <v>6318</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="9">
         <v>6104</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="9">
         <v>5957</v>
       </c>
-      <c r="O28" s="10">
+      <c r="O28" s="9">
         <v>5457</v>
       </c>
       <c r="P28" s="2">
@@ -3710,10 +3783,10 @@
       <c r="W28" s="4">
         <v>8878</v>
       </c>
-      <c r="X28" s="12">
+      <c r="X28" s="10">
         <v>9076</v>
       </c>
-      <c r="Y28" s="12">
+      <c r="Y28" s="10">
         <v>9275</v>
       </c>
       <c r="Z28" s="5">
@@ -3725,18 +3798,20 @@
       <c r="AB28" s="5">
         <v>9151</v>
       </c>
-      <c r="AC28" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC28" s="11">
         <v>9151</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AD28" s="11">
         <v>9174</v>
       </c>
-      <c r="AE28" s="1">
+      <c r="AE28" s="3">
         <v>9176</v>
       </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>9110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -3746,40 +3821,40 @@
       <c r="C29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>4071</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>2521</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>1561</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>1664</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="9">
         <v>1328</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="9">
         <v>955</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="9">
         <v>912</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="9">
         <v>847</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="9">
         <v>803</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="9">
         <v>712</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="9">
         <v>558</v>
       </c>
-      <c r="O29" s="10">
+      <c r="O29" s="9">
         <v>506</v>
       </c>
       <c r="P29" s="2">
@@ -3806,10 +3881,10 @@
       <c r="W29" s="4">
         <v>455</v>
       </c>
-      <c r="X29" s="12">
+      <c r="X29" s="10">
         <v>1477</v>
       </c>
-      <c r="Y29" s="12">
+      <c r="Y29" s="10">
         <v>2499</v>
       </c>
       <c r="Z29" s="5">
@@ -3821,18 +3896,20 @@
       <c r="AB29" s="5">
         <v>760</v>
       </c>
-      <c r="AC29" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC29" s="11">
         <v>760</v>
       </c>
-      <c r="AD29" s="13">
+      <c r="AD29" s="11">
         <v>1253</v>
       </c>
-      <c r="AE29" s="1">
+      <c r="AE29" s="3">
         <v>1291</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -3842,40 +3919,40 @@
       <c r="C30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>57899</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <v>65594</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>74312</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>67826</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="9">
         <v>62048</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="9">
         <v>58469</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="9">
         <v>57182</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="9">
         <v>55394</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="9">
         <v>53276</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="9">
         <v>51987</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="9">
         <v>51978</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="9">
         <v>50663</v>
       </c>
       <c r="P30" s="2">
@@ -3902,10 +3979,10 @@
       <c r="W30" s="4">
         <v>61410</v>
       </c>
-      <c r="X30" s="12">
+      <c r="X30" s="10">
         <v>61591</v>
       </c>
-      <c r="Y30" s="12">
+      <c r="Y30" s="10">
         <v>61772</v>
       </c>
       <c r="Z30" s="5">
@@ -3917,18 +3994,20 @@
       <c r="AB30" s="5">
         <v>61537</v>
       </c>
-      <c r="AC30" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC30" s="11">
         <v>61537</v>
       </c>
-      <c r="AD30" s="13">
+      <c r="AD30" s="11">
         <v>66523</v>
       </c>
-      <c r="AE30" s="1">
+      <c r="AE30" s="3">
         <v>67043</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>69929</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -3938,40 +4017,40 @@
       <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>232065</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>229222</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>214551</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <v>220488</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="L31" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="M31" s="10" t="s">
+      <c r="M31" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="N31" s="10" t="s">
+      <c r="N31" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="O31" s="10" t="s">
+      <c r="O31" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P31" s="2">
@@ -3998,10 +4077,10 @@
       <c r="W31" s="4">
         <v>233433</v>
       </c>
-      <c r="X31" s="12">
+      <c r="X31" s="10">
         <v>236635</v>
       </c>
-      <c r="Y31" s="12">
+      <c r="Y31" s="10">
         <v>239838</v>
       </c>
       <c r="Z31" s="3" t="s">
@@ -4013,18 +4092,20 @@
       <c r="AB31" s="3">
         <v>242484</v>
       </c>
-      <c r="AC31" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC31" s="11">
         <v>242484</v>
       </c>
-      <c r="AD31" s="13">
+      <c r="AD31" s="11">
         <v>245897</v>
       </c>
-      <c r="AE31" s="1">
+      <c r="AE31" s="3">
         <v>246241</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>276760</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -4034,40 +4115,40 @@
       <c r="C32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>43955</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>43218</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>42493</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>36165</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="9">
         <v>37051</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="9">
         <v>37453</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="9">
         <v>37842</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="9">
         <v>38917</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="9">
         <v>39884</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M32" s="9">
         <v>41062</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="9">
         <v>37304</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O32" s="9">
         <v>36486</v>
       </c>
       <c r="P32" s="2">
@@ -4094,10 +4175,10 @@
       <c r="W32" s="4">
         <v>38234</v>
       </c>
-      <c r="X32" s="12">
+      <c r="X32" s="10">
         <v>38596</v>
       </c>
-      <c r="Y32" s="12">
+      <c r="Y32" s="10">
         <v>38958</v>
       </c>
       <c r="Z32" s="5">
@@ -4109,18 +4190,20 @@
       <c r="AB32" s="5">
         <v>38775</v>
       </c>
-      <c r="AC32" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC32" s="11">
         <v>38775</v>
       </c>
-      <c r="AD32" s="13">
+      <c r="AD32" s="11">
         <v>39782</v>
       </c>
-      <c r="AE32" s="1">
+      <c r="AE32" s="3">
         <v>39884</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>43699</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -4130,40 +4213,40 @@
       <c r="C33" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>1946</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>2220</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>2533</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>2235</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="9">
         <v>2180</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="9">
         <v>2057</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="9">
         <v>2053</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="9">
         <v>2041</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="9">
         <v>2029</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="9">
         <v>2018</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="9">
         <v>2261</v>
       </c>
-      <c r="O33" s="10">
+      <c r="O33" s="9">
         <v>2276</v>
       </c>
       <c r="P33" s="2">
@@ -4190,10 +4273,10 @@
       <c r="W33" s="4">
         <v>1906</v>
       </c>
-      <c r="X33" s="12">
+      <c r="X33" s="10">
         <v>1936</v>
       </c>
-      <c r="Y33" s="12">
+      <c r="Y33" s="10">
         <v>1966</v>
       </c>
       <c r="Z33" s="5">
@@ -4205,18 +4288,20 @@
       <c r="AB33" s="5">
         <v>2110</v>
       </c>
-      <c r="AC33" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC33" s="11">
         <v>2110</v>
       </c>
-      <c r="AD33" s="13">
+      <c r="AD33" s="11">
         <v>2129</v>
       </c>
-      <c r="AE33" s="1">
+      <c r="AE33" s="3">
         <v>2131</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -4226,40 +4311,40 @@
       <c r="C34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>128227</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <v>139951</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <v>126867</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="9">
         <v>126785</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="J34" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="L34" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="M34" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="N34" s="10" t="s">
+      <c r="N34" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="O34" s="10" t="s">
+      <c r="O34" s="9" t="s">
         <v>114</v>
       </c>
       <c r="P34" s="2">
@@ -4286,10 +4371,10 @@
       <c r="W34" s="4">
         <v>122810</v>
       </c>
-      <c r="X34" s="12">
+      <c r="X34" s="10">
         <v>125964</v>
       </c>
-      <c r="Y34" s="12">
+      <c r="Y34" s="10">
         <v>129119</v>
       </c>
       <c r="Z34" s="3" t="s">
@@ -4301,18 +4386,20 @@
       <c r="AB34" s="3">
         <v>136909</v>
       </c>
-      <c r="AC34" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC34" s="11">
         <v>136909</v>
       </c>
-      <c r="AD34" s="13">
+      <c r="AD34" s="11">
         <v>132948</v>
       </c>
-      <c r="AE34" s="1">
+      <c r="AE34" s="3">
         <v>132558</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>142234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -4322,40 +4409,40 @@
       <c r="C35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>1226</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>1220</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>1214</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>1038</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="9">
         <v>1004</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="9">
         <v>1028</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="9">
         <v>1032</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="9">
         <v>1018</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="9">
         <v>1009</v>
       </c>
-      <c r="M35" s="10">
+      <c r="M35" s="9">
         <v>998</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="9">
         <v>1075</v>
       </c>
-      <c r="O35" s="10">
+      <c r="O35" s="9">
         <v>1068</v>
       </c>
       <c r="P35" s="2">
@@ -4382,10 +4469,10 @@
       <c r="W35" s="4">
         <v>1046</v>
       </c>
-      <c r="X35" s="12">
+      <c r="X35" s="10">
         <v>1061</v>
       </c>
-      <c r="Y35" s="12">
+      <c r="Y35" s="10">
         <v>1076</v>
       </c>
       <c r="Z35" s="5">
@@ -4397,18 +4484,20 @@
       <c r="AB35" s="5">
         <v>1098</v>
       </c>
-      <c r="AC35" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC35" s="11">
         <v>1098</v>
       </c>
-      <c r="AD35" s="13">
+      <c r="AD35" s="11">
         <v>1110</v>
       </c>
-      <c r="AE35" s="1">
+      <c r="AE35" s="3">
         <v>1111</v>
       </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4418,40 +4507,40 @@
       <c r="C36" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>205501</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="9">
         <v>184544</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <v>173828</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="9">
         <v>188628</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="L36" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="M36" s="10" t="s">
+      <c r="M36" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="N36" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="O36" s="10" t="s">
+      <c r="O36" s="9" t="s">
         <v>124</v>
       </c>
       <c r="P36" s="2">
@@ -4478,10 +4567,10 @@
       <c r="W36" s="4">
         <v>207739</v>
       </c>
-      <c r="X36" s="12">
+      <c r="X36" s="10">
         <v>213357</v>
       </c>
-      <c r="Y36" s="12">
+      <c r="Y36" s="10">
         <v>218976</v>
       </c>
       <c r="Z36" s="3" t="s">
@@ -4493,33 +4582,231 @@
       <c r="AB36" s="3">
         <v>227879</v>
       </c>
-      <c r="AC36" s="13">
-        <f t="shared" ca="1" si="0"/>
+      <c r="AC36" s="11">
         <v>227879</v>
       </c>
-      <c r="AD36" s="13">
+      <c r="AD36" s="11">
         <v>242948</v>
       </c>
-      <c r="AE36" s="1">
+      <c r="AE36" s="3">
         <v>244509</v>
       </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF36" s="3">
+        <v>292657</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X37" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y37" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC37" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF37" s="3">
+        <v>99570</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X38" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y38" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC38" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD38" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF38" s="3">
+        <v>67914</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="X42" s="6"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="X46" s="6"/>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="X48" s="6"/>
     </row>
     <row r="49" spans="24:24" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8A6A1E-7DBB-094D-8733-CFC2DB6BC99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2407E8-DF85-C146-BAE7-0945E1584ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="186">
   <si>
     <t>Category</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>Jul26 W4</t>
+  </si>
+  <si>
+    <t>Aug26 W1</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AF74"/>
+  <dimension ref="A1:AG74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1067,7 +1070,7 @@
     <col min="32" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1164,8 +1167,11 @@
       <c r="AF1" s="13" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG1" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1262,8 +1268,11 @@
       <c r="AF2" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1360,8 +1369,11 @@
       <c r="AF3" s="3">
         <v>20489</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG3" s="1">
+        <v>21008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1458,8 +1470,11 @@
       <c r="AF4" s="3">
         <v>372</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG4" s="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,8 +1571,11 @@
       <c r="AF5" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1654,8 +1672,11 @@
       <c r="AF6" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG6" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1752,8 +1773,11 @@
       <c r="AF7" s="3">
         <v>50940</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="1">
+        <v>50981</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1850,8 +1874,11 @@
       <c r="AF8" s="3">
         <v>2953</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="1">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1948,8 +1975,11 @@
       <c r="AF9" s="3">
         <v>13652</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="1">
+        <v>13660</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -2046,8 +2076,11 @@
       <c r="AF10" s="3">
         <v>92830</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="1">
+        <v>93670</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -2144,8 +2177,11 @@
       <c r="AF11" s="3">
         <v>260076</v>
       </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="1">
+        <v>261335</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2242,8 +2278,11 @@
       <c r="AF12" s="3">
         <v>179901</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="1">
+        <v>179178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -2340,8 +2379,11 @@
       <c r="AF13" s="3">
         <v>171760</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="1">
+        <v>172153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2438,8 +2480,11 @@
       <c r="AF14" s="3">
         <v>97772</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="1">
+        <v>98441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -2536,8 +2581,11 @@
       <c r="AF15" s="3">
         <v>358778</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="1">
+        <v>373963</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2634,8 +2682,11 @@
       <c r="AF16" s="3">
         <v>159166</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="1">
+        <v>170952</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2732,8 +2783,11 @@
       <c r="AF17" s="3">
         <v>949630</v>
       </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="1">
+        <v>969210</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2830,8 +2884,11 @@
       <c r="AF18" s="3">
         <v>850631</v>
       </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="1">
+        <v>861488</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -2928,8 +2985,11 @@
       <c r="AF19" s="3">
         <v>8608</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="1">
+        <v>8772</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -3026,8 +3086,11 @@
       <c r="AF20" s="3">
         <v>1360</v>
       </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="1">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -3124,8 +3187,11 @@
       <c r="AF21" s="3">
         <v>2202</v>
       </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="1">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -3222,8 +3288,11 @@
       <c r="AF22" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -3320,8 +3389,11 @@
       <c r="AF23" s="3">
         <v>20489</v>
       </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="1">
+        <v>21008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3418,8 +3490,11 @@
       <c r="AF24" s="3">
         <v>231</v>
       </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3516,8 +3591,11 @@
       <c r="AF25" s="3">
         <v>5685</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="1">
+        <v>5859</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -3614,8 +3692,11 @@
       <c r="AF26" s="3">
         <v>17234</v>
       </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="1">
+        <v>18090</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -3712,8 +3793,11 @@
       <c r="AF27" s="3">
         <v>109652</v>
       </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="1">
+        <v>111742</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -3810,8 +3894,11 @@
       <c r="AF28" s="3">
         <v>9110</v>
       </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="1">
+        <v>9112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -3908,8 +3995,11 @@
       <c r="AF29" s="3">
         <v>730</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="1">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -4006,8 +4096,11 @@
       <c r="AF30" s="3">
         <v>69929</v>
       </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="1">
+        <v>70753</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -4104,8 +4197,11 @@
       <c r="AF31" s="3">
         <v>276760</v>
       </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="1">
+        <v>283936</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -4202,8 +4298,11 @@
       <c r="AF32" s="3">
         <v>43699</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="1">
+        <v>44802</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -4300,8 +4399,11 @@
       <c r="AF33" s="3">
         <v>2438</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="1">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -4398,8 +4500,11 @@
       <c r="AF34" s="3">
         <v>142234</v>
       </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="1">
+        <v>142641</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -4496,8 +4601,11 @@
       <c r="AF35" s="3">
         <v>1248</v>
       </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="1">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4594,8 +4702,11 @@
       <c r="AF36" s="3">
         <v>292657</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG36" s="1">
+        <v>302625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>181</v>
       </c>
@@ -4692,8 +4803,11 @@
       <c r="AF37" s="3">
         <v>99570</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG37" s="1">
+        <v>99469</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>181</v>
       </c>
@@ -4790,23 +4904,26 @@
       <c r="AF38" s="3">
         <v>67914</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="1">
+        <v>68080</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="U40" s="8"/>
       <c r="V40" s="8"/>
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
       <c r="X42" s="6"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="X46" s="6"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="X48" s="6"/>
     </row>
     <row r="49" spans="24:24" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2407E8-DF85-C146-BAE7-0945E1584ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7284D4A2-48D9-CF40-8E94-8CA1451F71FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="193">
   <si>
     <t>Category</t>
   </si>
@@ -597,6 +597,27 @@
   </si>
   <si>
     <t>Aug26 W1</t>
+  </si>
+  <si>
+    <t>go desi indian sweets</t>
+  </si>
+  <si>
+    <t>go desi classic kaju katli</t>
+  </si>
+  <si>
+    <t>go desi besan laddu</t>
+  </si>
+  <si>
+    <t>go desi mithai</t>
+  </si>
+  <si>
+    <t>go desi bhel</t>
+  </si>
+  <si>
+    <t>go desi snacks</t>
+  </si>
+  <si>
+    <t>Aug26 W2</t>
   </si>
 </sst>
 </file>
@@ -607,7 +628,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -637,6 +658,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -677,7 +704,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -716,6 +743,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1051,12 +1079,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AG74"/>
+  <dimension ref="A1:AH79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -1067,10 +1095,12 @@
     <col min="26" max="26" width="12.5" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="30" width="10.83203125" style="1"/>
     <col min="31" max="31" width="10.83203125" style="3"/>
-    <col min="32" max="16384" width="10.83203125" style="1"/>
+    <col min="32" max="32" width="10.83203125" style="1"/>
+    <col min="33" max="33" width="10.83203125" style="3"/>
+    <col min="34" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1170,8 +1200,11 @@
       <c r="AG1" s="13" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH1" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1268,11 +1301,14 @@
       <c r="AF2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AG2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1369,11 +1405,14 @@
       <c r="AF3" s="3">
         <v>20489</v>
       </c>
-      <c r="AG3" s="1">
+      <c r="AG3" s="3">
         <v>21008</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH3" s="3">
+        <v>22063</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1470,11 +1509,14 @@
       <c r="AF4" s="3">
         <v>372</v>
       </c>
-      <c r="AG4" s="1">
+      <c r="AG4" s="3">
         <v>394</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH4" s="3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1571,11 +1613,14 @@
       <c r="AF5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AG5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1672,516 +1717,534 @@
       <c r="AF6" s="3">
         <v>106</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AG6" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH6" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="9">
-        <v>35550</v>
-      </c>
-      <c r="E7" s="9">
-        <v>36638</v>
-      </c>
-      <c r="F7" s="9">
-        <v>37759</v>
-      </c>
-      <c r="G7" s="9">
-        <v>38048</v>
-      </c>
-      <c r="H7" s="9">
-        <v>39236</v>
-      </c>
-      <c r="I7" s="9">
-        <v>40115</v>
-      </c>
-      <c r="J7" s="9">
-        <v>41183</v>
-      </c>
-      <c r="K7" s="9">
-        <v>42067</v>
-      </c>
-      <c r="L7" s="9">
-        <v>43149</v>
-      </c>
-      <c r="M7" s="9">
-        <v>43872</v>
-      </c>
-      <c r="N7" s="9">
-        <v>44083</v>
-      </c>
-      <c r="O7" s="9">
-        <v>44891</v>
-      </c>
-      <c r="P7" s="2">
-        <v>45486</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>46081</v>
-      </c>
-      <c r="R7" s="3">
-        <v>46355</v>
-      </c>
-      <c r="S7" s="3">
-        <v>48497</v>
-      </c>
-      <c r="T7" s="2">
-        <v>46334</v>
-      </c>
-      <c r="U7" s="5">
-        <v>47012</v>
-      </c>
-      <c r="V7" s="5">
-        <v>48206</v>
-      </c>
-      <c r="W7" s="4">
-        <v>47748</v>
-      </c>
-      <c r="X7" s="10">
-        <v>48609</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>49470</v>
-      </c>
-      <c r="Z7" s="5">
-        <v>51110</v>
-      </c>
-      <c r="AA7" s="5">
-        <v>50804</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>51139</v>
-      </c>
-      <c r="AC7" s="11">
-        <v>51139</v>
-      </c>
-      <c r="AD7" s="11">
-        <v>49782</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>49648</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>50940</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>50981</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1858</v>
-      </c>
-      <c r="E8" s="9">
-        <v>1820</v>
-      </c>
-      <c r="F8" s="9">
-        <v>1783</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1789</v>
-      </c>
-      <c r="H8" s="9">
-        <v>1725</v>
-      </c>
-      <c r="I8" s="9">
-        <v>2427</v>
-      </c>
-      <c r="J8" s="9">
-        <v>2463</v>
-      </c>
-      <c r="K8" s="9">
-        <v>2517</v>
-      </c>
-      <c r="L8" s="9">
-        <v>2604</v>
-      </c>
-      <c r="M8" s="9">
-        <v>2748</v>
-      </c>
-      <c r="N8" s="9">
-        <v>2883</v>
-      </c>
-      <c r="O8" s="9">
-        <v>2960</v>
-      </c>
-      <c r="P8" s="2">
-        <v>3068</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>3176</v>
-      </c>
-      <c r="R8" s="3">
-        <v>3228</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3413</v>
-      </c>
-      <c r="T8" s="2">
-        <v>3198</v>
-      </c>
-      <c r="U8" s="5">
-        <v>3104</v>
-      </c>
-      <c r="V8" s="5">
-        <v>3157</v>
-      </c>
-      <c r="W8" s="4">
-        <v>3148</v>
-      </c>
-      <c r="X8" s="10">
-        <v>3123</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>3098</v>
-      </c>
-      <c r="Z8" s="5">
-        <v>3057</v>
-      </c>
-      <c r="AA8" s="5">
-        <v>3064</v>
-      </c>
-      <c r="AB8" s="5">
-        <v>3054</v>
-      </c>
-      <c r="AC8" s="11">
-        <v>3054</v>
-      </c>
-      <c r="AD8" s="11">
-        <v>2883</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>2866</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>2953</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>2932</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>187220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="9">
-        <v>5864</v>
-      </c>
-      <c r="E9" s="9">
-        <v>6486</v>
-      </c>
-      <c r="F9" s="9">
-        <v>7174</v>
-      </c>
-      <c r="G9" s="9">
-        <v>7150</v>
-      </c>
-      <c r="H9" s="9">
-        <v>7723</v>
-      </c>
-      <c r="I9" s="9">
-        <v>7920</v>
-      </c>
-      <c r="J9" s="9">
-        <v>8118</v>
-      </c>
-      <c r="K9" s="9">
-        <v>8397</v>
-      </c>
-      <c r="L9" s="9">
-        <v>8713</v>
-      </c>
-      <c r="M9" s="9">
-        <v>9026</v>
-      </c>
-      <c r="N9" s="9">
-        <v>9043</v>
-      </c>
-      <c r="O9" s="9">
-        <v>9368</v>
-      </c>
-      <c r="P9" s="2">
-        <v>9588</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>9808</v>
-      </c>
-      <c r="R9" s="3">
-        <v>9862</v>
-      </c>
-      <c r="S9" s="3">
-        <v>10315</v>
-      </c>
-      <c r="T9" s="2">
-        <v>9679</v>
-      </c>
-      <c r="U9" s="5">
-        <v>9112</v>
-      </c>
-      <c r="V9" s="5">
-        <v>9305</v>
-      </c>
-      <c r="W9" s="4">
-        <v>9230</v>
-      </c>
-      <c r="X9" s="10">
-        <v>9178</v>
-      </c>
-      <c r="Y9" s="10">
-        <v>9125</v>
-      </c>
-      <c r="Z9" s="5">
-        <v>9268</v>
-      </c>
-      <c r="AA9" s="5">
-        <v>9229</v>
-      </c>
-      <c r="AB9" s="5">
-        <v>9230</v>
-      </c>
-      <c r="AC9" s="11">
-        <v>9230</v>
-      </c>
-      <c r="AD9" s="11">
-        <v>11738</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>12024</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>13652</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>13660</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="9">
-        <v>71964</v>
-      </c>
-      <c r="E10" s="9">
-        <v>70213</v>
-      </c>
-      <c r="F10" s="9">
-        <v>68505</v>
-      </c>
-      <c r="G10" s="9">
-        <v>73263</v>
-      </c>
-      <c r="H10" s="9">
-        <v>74778</v>
-      </c>
-      <c r="I10" s="9">
-        <v>78638</v>
-      </c>
-      <c r="J10" s="9">
-        <v>79842</v>
-      </c>
-      <c r="K10" s="9">
-        <v>81536</v>
-      </c>
-      <c r="L10" s="9">
-        <v>83127</v>
-      </c>
-      <c r="M10" s="9">
-        <v>84418</v>
-      </c>
-      <c r="N10" s="9">
-        <v>84623</v>
-      </c>
-      <c r="O10" s="9">
-        <v>82556</v>
-      </c>
-      <c r="P10" s="2">
-        <v>81806</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>81056</v>
-      </c>
-      <c r="R10" s="3">
-        <v>81236</v>
-      </c>
-      <c r="S10" s="3">
-        <v>84677</v>
-      </c>
-      <c r="T10" s="2">
-        <v>83638</v>
-      </c>
-      <c r="U10" s="5">
-        <v>79884</v>
-      </c>
-      <c r="V10" s="5">
-        <v>81093</v>
-      </c>
-      <c r="W10" s="4">
-        <v>81479</v>
-      </c>
-      <c r="X10" s="10">
-        <v>80893</v>
-      </c>
-      <c r="Y10" s="10">
-        <v>80306</v>
-      </c>
-      <c r="Z10" s="5">
-        <v>79986</v>
-      </c>
-      <c r="AA10" s="5">
-        <v>79958</v>
-      </c>
-      <c r="AB10" s="5">
-        <v>79806</v>
-      </c>
-      <c r="AC10" s="11">
-        <v>79806</v>
-      </c>
-      <c r="AD10" s="11">
-        <v>84843</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>85364</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>92830</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>93670</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="9">
-        <v>232749</v>
-      </c>
-      <c r="E11" s="9">
-        <v>242993</v>
-      </c>
-      <c r="F11" s="9">
-        <v>253688</v>
-      </c>
-      <c r="G11" s="9">
-        <v>229817</v>
-      </c>
-      <c r="H11" s="9">
-        <v>232951</v>
+        <v>189</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="P11" s="2">
-        <v>295402</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>306716</v>
-      </c>
-      <c r="R11" s="3">
-        <v>294711</v>
-      </c>
-      <c r="S11" s="3">
-        <v>294331</v>
+        <v>18</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="W11" s="4">
-        <v>190412</v>
-      </c>
-      <c r="X11" s="10">
-        <v>198533</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>206655</v>
+        <v>18</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y11" s="15" t="s">
+        <v>18</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>229539</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>229619</v>
-      </c>
-      <c r="AC11" s="11">
-        <v>229619</v>
-      </c>
-      <c r="AD11" s="11">
-        <v>238024</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>238881</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>260076</v>
-      </c>
-      <c r="AG11" s="1">
-        <v>261335</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2189,100 +2252,103 @@
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D12" s="9">
-        <v>75862</v>
+        <v>35550</v>
       </c>
       <c r="E12" s="9">
-        <v>63740</v>
+        <v>36638</v>
       </c>
       <c r="F12" s="9">
-        <v>53555</v>
+        <v>37759</v>
       </c>
       <c r="G12" s="9">
-        <v>68500</v>
+        <v>38048</v>
       </c>
       <c r="H12" s="9">
-        <v>98599</v>
+        <v>39236</v>
       </c>
       <c r="I12" s="9">
-        <v>79484</v>
+        <v>40115</v>
       </c>
       <c r="J12" s="9">
-        <v>81327</v>
+        <v>41183</v>
       </c>
       <c r="K12" s="9">
-        <v>84612</v>
+        <v>42067</v>
       </c>
       <c r="L12" s="9">
-        <v>88943</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>39</v>
+        <v>43149</v>
+      </c>
+      <c r="M12" s="9">
+        <v>43872</v>
+      </c>
+      <c r="N12" s="9">
+        <v>44083</v>
+      </c>
+      <c r="O12" s="9">
+        <v>44891</v>
       </c>
       <c r="P12" s="2">
-        <v>200858</v>
+        <v>45486</v>
       </c>
       <c r="Q12" s="2">
-        <v>229496</v>
+        <v>46081</v>
       </c>
       <c r="R12" s="3">
-        <v>241671</v>
+        <v>46355</v>
       </c>
       <c r="S12" s="3">
-        <v>269912</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>142</v>
+        <v>48497</v>
+      </c>
+      <c r="T12" s="2">
+        <v>46334</v>
+      </c>
+      <c r="U12" s="5">
+        <v>47012</v>
+      </c>
+      <c r="V12" s="5">
+        <v>48206</v>
       </c>
       <c r="W12" s="4">
-        <v>168639</v>
+        <v>47748</v>
       </c>
       <c r="X12" s="10">
-        <v>171404</v>
+        <v>48609</v>
       </c>
       <c r="Y12" s="10">
-        <v>174170</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>179991</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>179909</v>
+        <v>49470</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>51110</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>50804</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>51139</v>
       </c>
       <c r="AC12" s="11">
-        <v>179909</v>
+        <v>51139</v>
       </c>
       <c r="AD12" s="11">
-        <v>173515</v>
+        <v>49782</v>
       </c>
       <c r="AE12" s="3">
-        <v>172888</v>
+        <v>49648</v>
       </c>
       <c r="AF12" s="3">
-        <v>179901</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>179178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+        <v>50940</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>50981</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>52216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -2290,100 +2356,103 @@
         <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D13" s="9">
-        <v>120329</v>
+        <v>1858</v>
       </c>
       <c r="E13" s="9">
-        <v>127681</v>
+        <v>1820</v>
       </c>
       <c r="F13" s="9">
-        <v>135482</v>
+        <v>1783</v>
       </c>
       <c r="G13" s="9">
-        <v>131019</v>
+        <v>1789</v>
       </c>
       <c r="H13" s="9">
-        <v>132408</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>47</v>
+        <v>1725</v>
+      </c>
+      <c r="I13" s="9">
+        <v>2427</v>
+      </c>
+      <c r="J13" s="9">
+        <v>2463</v>
+      </c>
+      <c r="K13" s="9">
+        <v>2517</v>
+      </c>
+      <c r="L13" s="9">
+        <v>2604</v>
+      </c>
+      <c r="M13" s="9">
+        <v>2748</v>
+      </c>
+      <c r="N13" s="9">
+        <v>2883</v>
+      </c>
+      <c r="O13" s="9">
+        <v>2960</v>
       </c>
       <c r="P13" s="2">
-        <v>154289</v>
+        <v>3068</v>
       </c>
       <c r="Q13" s="2">
-        <v>157676</v>
+        <v>3176</v>
       </c>
       <c r="R13" s="3">
-        <v>157087</v>
+        <v>3228</v>
       </c>
       <c r="S13" s="3">
-        <v>162791</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>143</v>
+        <v>3413</v>
+      </c>
+      <c r="T13" s="2">
+        <v>3198</v>
+      </c>
+      <c r="U13" s="5">
+        <v>3104</v>
+      </c>
+      <c r="V13" s="5">
+        <v>3157</v>
       </c>
       <c r="W13" s="4">
-        <v>146511</v>
+        <v>3148</v>
       </c>
       <c r="X13" s="10">
-        <v>148663</v>
+        <v>3123</v>
       </c>
       <c r="Y13" s="10">
-        <v>150815</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>155085</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>155321</v>
+        <v>3098</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>3057</v>
+      </c>
+      <c r="AA13" s="5">
+        <v>3064</v>
+      </c>
+      <c r="AB13" s="5">
+        <v>3054</v>
       </c>
       <c r="AC13" s="11">
-        <v>155321</v>
+        <v>3054</v>
       </c>
       <c r="AD13" s="11">
-        <v>162351</v>
+        <v>2883</v>
       </c>
       <c r="AE13" s="3">
-        <v>163071</v>
+        <v>2866</v>
       </c>
       <c r="AF13" s="3">
-        <v>171760</v>
-      </c>
-      <c r="AG13" s="1">
-        <v>172153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+        <v>2953</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>2932</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2391,1009 +2460,1039 @@
         <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D14" s="9">
-        <v>33458</v>
+        <v>5864</v>
       </c>
       <c r="E14" s="9">
-        <v>28690</v>
+        <v>6486</v>
       </c>
       <c r="F14" s="9">
-        <v>24601</v>
+        <v>7174</v>
       </c>
       <c r="G14" s="9">
-        <v>30975</v>
+        <v>7150</v>
       </c>
       <c r="H14" s="9">
-        <v>33624</v>
+        <v>7723</v>
       </c>
       <c r="I14" s="9">
-        <v>36455</v>
+        <v>7920</v>
       </c>
       <c r="J14" s="9">
-        <v>37648</v>
+        <v>8118</v>
       </c>
       <c r="K14" s="9">
-        <v>39982</v>
+        <v>8397</v>
       </c>
       <c r="L14" s="9">
-        <v>42731</v>
+        <v>8713</v>
       </c>
       <c r="M14" s="9">
-        <v>50184</v>
+        <v>9026</v>
       </c>
       <c r="N14" s="9">
-        <v>57210</v>
+        <v>9043</v>
       </c>
       <c r="O14" s="9">
-        <v>65597</v>
+        <v>9368</v>
       </c>
       <c r="P14" s="2">
-        <v>73375</v>
+        <v>9588</v>
       </c>
       <c r="Q14" s="2">
-        <v>81153</v>
+        <v>9808</v>
       </c>
       <c r="R14" s="3">
-        <v>84292</v>
+        <v>9862</v>
       </c>
       <c r="S14" s="3">
-        <v>91544</v>
+        <v>10315</v>
       </c>
       <c r="T14" s="2">
-        <v>74927</v>
+        <v>9679</v>
       </c>
       <c r="U14" s="5">
-        <v>73982</v>
+        <v>9112</v>
       </c>
       <c r="V14" s="5">
-        <v>76417</v>
+        <v>9305</v>
       </c>
       <c r="W14" s="4">
-        <v>74001</v>
+        <v>9230</v>
       </c>
       <c r="X14" s="10">
-        <v>76698</v>
+        <v>9178</v>
       </c>
       <c r="Y14" s="10">
-        <v>79396</v>
+        <v>9125</v>
       </c>
       <c r="Z14" s="5">
-        <v>88105</v>
+        <v>9268</v>
       </c>
       <c r="AA14" s="5">
-        <v>85353</v>
+        <v>9229</v>
       </c>
       <c r="AB14" s="5">
-        <v>86391</v>
+        <v>9230</v>
       </c>
       <c r="AC14" s="11">
-        <v>86391</v>
+        <v>9230</v>
       </c>
       <c r="AD14" s="11">
-        <v>91784</v>
+        <v>11738</v>
       </c>
       <c r="AE14" s="3">
-        <v>92341</v>
+        <v>12024</v>
       </c>
       <c r="AF14" s="3">
-        <v>97772</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>98441</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+        <v>13652</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>13660</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>13516</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D15" s="9">
-        <v>245157</v>
+        <v>71964</v>
       </c>
       <c r="E15" s="9">
-        <v>246726</v>
+        <v>70213</v>
       </c>
       <c r="F15" s="9">
-        <v>248305</v>
+        <v>68505</v>
       </c>
       <c r="G15" s="9">
-        <v>235711</v>
+        <v>73263</v>
       </c>
       <c r="H15" s="9">
-        <v>237839</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>57</v>
+        <v>74778</v>
+      </c>
+      <c r="I15" s="9">
+        <v>78638</v>
+      </c>
+      <c r="J15" s="9">
+        <v>79842</v>
+      </c>
+      <c r="K15" s="9">
+        <v>81536</v>
+      </c>
+      <c r="L15" s="9">
+        <v>83127</v>
+      </c>
+      <c r="M15" s="9">
+        <v>84418</v>
+      </c>
+      <c r="N15" s="9">
+        <v>84623</v>
+      </c>
+      <c r="O15" s="9">
+        <v>82556</v>
       </c>
       <c r="P15" s="2">
-        <v>296538</v>
+        <v>81806</v>
       </c>
       <c r="Q15" s="2">
-        <v>303714</v>
+        <v>81056</v>
       </c>
       <c r="R15" s="3">
-        <v>297755</v>
+        <v>81236</v>
       </c>
       <c r="S15" s="3">
-        <v>303545</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>144</v>
+        <v>84677</v>
+      </c>
+      <c r="T15" s="2">
+        <v>83638</v>
+      </c>
+      <c r="U15" s="5">
+        <v>79884</v>
+      </c>
+      <c r="V15" s="5">
+        <v>81093</v>
       </c>
       <c r="W15" s="4">
-        <v>257190</v>
+        <v>81479</v>
       </c>
       <c r="X15" s="10">
-        <v>260444</v>
+        <v>80893</v>
       </c>
       <c r="Y15" s="10">
-        <v>263698</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>269169</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>269558</v>
+        <v>80306</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>79986</v>
+      </c>
+      <c r="AA15" s="5">
+        <v>79958</v>
+      </c>
+      <c r="AB15" s="5">
+        <v>79806</v>
       </c>
       <c r="AC15" s="11">
-        <v>269558</v>
+        <v>79806</v>
       </c>
       <c r="AD15" s="11">
-        <v>311607</v>
+        <v>84843</v>
       </c>
       <c r="AE15" s="3">
-        <v>316157</v>
+        <v>85364</v>
       </c>
       <c r="AF15" s="3">
-        <v>358778</v>
-      </c>
-      <c r="AG15" s="1">
-        <v>373963</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+        <v>92830</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>93670</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>96944</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D16" s="9">
-        <v>96559</v>
+        <v>232749</v>
       </c>
       <c r="E16" s="9">
-        <v>87884</v>
+        <v>242993</v>
       </c>
       <c r="F16" s="9">
-        <v>79988</v>
+        <v>253688</v>
       </c>
       <c r="G16" s="9">
-        <v>87364</v>
+        <v>229817</v>
       </c>
       <c r="H16" s="9">
-        <v>91089</v>
+        <v>232951</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="P16" s="2">
-        <v>145783</v>
+        <v>295402</v>
       </c>
       <c r="Q16" s="2">
-        <v>152795</v>
+        <v>306716</v>
       </c>
       <c r="R16" s="3">
-        <v>148080</v>
+        <v>294711</v>
       </c>
       <c r="S16" s="3">
-        <v>149270</v>
+        <v>294331</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="W16" s="4">
-        <v>108615</v>
+        <v>190412</v>
       </c>
       <c r="X16" s="10">
-        <v>112718</v>
+        <v>198533</v>
       </c>
       <c r="Y16" s="10">
-        <v>116820</v>
+        <v>206655</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AA16" s="3">
-        <v>125689</v>
+        <v>229539</v>
       </c>
       <c r="AB16" s="3">
-        <v>126703</v>
+        <v>229619</v>
       </c>
       <c r="AC16" s="11">
-        <v>126703</v>
+        <v>229619</v>
       </c>
       <c r="AD16" s="11">
-        <v>136274</v>
+        <v>238024</v>
       </c>
       <c r="AE16" s="3">
-        <v>137270</v>
+        <v>238881</v>
       </c>
       <c r="AF16" s="3">
-        <v>159166</v>
-      </c>
-      <c r="AG16" s="1">
-        <v>170952</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+        <v>260076</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>261335</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>278364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D17" s="9">
-        <v>651237</v>
+        <v>75862</v>
       </c>
       <c r="E17" s="9">
-        <v>671360</v>
+        <v>63740</v>
       </c>
       <c r="F17" s="9">
-        <v>692105</v>
+        <v>53555</v>
       </c>
       <c r="G17" s="9">
-        <v>676705</v>
+        <v>68500</v>
       </c>
       <c r="H17" s="9">
-        <v>673347</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>70</v>
+        <v>98599</v>
+      </c>
+      <c r="I17" s="9">
+        <v>79484</v>
+      </c>
+      <c r="J17" s="9">
+        <v>81327</v>
+      </c>
+      <c r="K17" s="9">
+        <v>84612</v>
+      </c>
+      <c r="L17" s="9">
+        <v>88943</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="P17" s="2">
-        <v>648993</v>
+        <v>200858</v>
       </c>
       <c r="Q17" s="2">
-        <v>615137</v>
+        <v>229496</v>
       </c>
       <c r="R17" s="3">
-        <v>601400</v>
+        <v>241671</v>
       </c>
       <c r="S17" s="3">
-        <v>611907</v>
+        <v>269912</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="W17" s="4">
-        <v>639961</v>
+        <v>168639</v>
       </c>
       <c r="X17" s="10">
-        <v>658429</v>
+        <v>171404</v>
       </c>
       <c r="Y17" s="10">
-        <v>676897</v>
+        <v>174170</v>
       </c>
       <c r="Z17" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA17" s="3">
-        <v>705930</v>
+        <v>179991</v>
       </c>
       <c r="AB17" s="3">
-        <v>713077</v>
+        <v>179909</v>
       </c>
       <c r="AC17" s="11">
-        <v>713077</v>
+        <v>179909</v>
       </c>
       <c r="AD17" s="11">
-        <v>811831</v>
+        <v>173515</v>
       </c>
       <c r="AE17" s="3">
-        <v>822429</v>
+        <v>172888</v>
       </c>
       <c r="AF17" s="3">
-        <v>949630</v>
-      </c>
-      <c r="AG17" s="1">
-        <v>969210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+        <v>179901</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>179178</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>183441</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="9">
+        <v>120329</v>
+      </c>
+      <c r="E18" s="9">
+        <v>127681</v>
+      </c>
+      <c r="F18" s="9">
+        <v>135482</v>
+      </c>
+      <c r="G18" s="9">
+        <v>131019</v>
+      </c>
+      <c r="H18" s="9">
+        <v>132408</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="P18" s="2">
+        <v>154289</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>157676</v>
+      </c>
+      <c r="R18" s="3">
+        <v>157087</v>
+      </c>
+      <c r="S18" s="3">
+        <v>162791</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="W18" s="4">
+        <v>146511</v>
+      </c>
+      <c r="X18" s="10">
+        <v>148663</v>
+      </c>
+      <c r="Y18" s="10">
+        <v>150815</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>155085</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>155321</v>
+      </c>
+      <c r="AC18" s="11">
+        <v>155321</v>
+      </c>
+      <c r="AD18" s="11">
+        <v>162351</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>163071</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>171760</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>172153</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>178126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="9">
+        <v>33458</v>
+      </c>
+      <c r="E19" s="9">
+        <v>28690</v>
+      </c>
+      <c r="F19" s="9">
+        <v>24601</v>
+      </c>
+      <c r="G19" s="9">
+        <v>30975</v>
+      </c>
+      <c r="H19" s="9">
+        <v>33624</v>
+      </c>
+      <c r="I19" s="9">
+        <v>36455</v>
+      </c>
+      <c r="J19" s="9">
+        <v>37648</v>
+      </c>
+      <c r="K19" s="9">
+        <v>39982</v>
+      </c>
+      <c r="L19" s="9">
+        <v>42731</v>
+      </c>
+      <c r="M19" s="9">
+        <v>50184</v>
+      </c>
+      <c r="N19" s="9">
+        <v>57210</v>
+      </c>
+      <c r="O19" s="9">
+        <v>65597</v>
+      </c>
+      <c r="P19" s="2">
+        <v>73375</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>81153</v>
+      </c>
+      <c r="R19" s="3">
+        <v>84292</v>
+      </c>
+      <c r="S19" s="3">
+        <v>91544</v>
+      </c>
+      <c r="T19" s="2">
+        <v>74927</v>
+      </c>
+      <c r="U19" s="5">
+        <v>73982</v>
+      </c>
+      <c r="V19" s="5">
+        <v>76417</v>
+      </c>
+      <c r="W19" s="4">
+        <v>74001</v>
+      </c>
+      <c r="X19" s="10">
+        <v>76698</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>79396</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>88105</v>
+      </c>
+      <c r="AA19" s="5">
+        <v>85353</v>
+      </c>
+      <c r="AB19" s="5">
+        <v>86391</v>
+      </c>
+      <c r="AC19" s="11">
+        <v>86391</v>
+      </c>
+      <c r="AD19" s="11">
+        <v>91784</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>92341</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>97772</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>98441</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>101544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="9">
+        <v>245157</v>
+      </c>
+      <c r="E20" s="9">
+        <v>246726</v>
+      </c>
+      <c r="F20" s="9">
+        <v>248305</v>
+      </c>
+      <c r="G20" s="9">
+        <v>235711</v>
+      </c>
+      <c r="H20" s="9">
+        <v>237839</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="P20" s="2">
+        <v>296538</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>303714</v>
+      </c>
+      <c r="R20" s="3">
+        <v>297755</v>
+      </c>
+      <c r="S20" s="3">
+        <v>303545</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="W20" s="4">
+        <v>257190</v>
+      </c>
+      <c r="X20" s="10">
+        <v>260444</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>263698</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>269169</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>269558</v>
+      </c>
+      <c r="AC20" s="11">
+        <v>269558</v>
+      </c>
+      <c r="AD20" s="11">
+        <v>311607</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>316157</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>358778</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>373963</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>419403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="9">
+        <v>96559</v>
+      </c>
+      <c r="E21" s="9">
+        <v>87884</v>
+      </c>
+      <c r="F21" s="9">
+        <v>79988</v>
+      </c>
+      <c r="G21" s="9">
+        <v>87364</v>
+      </c>
+      <c r="H21" s="9">
+        <v>91089</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P21" s="2">
+        <v>145783</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>152795</v>
+      </c>
+      <c r="R21" s="3">
+        <v>148080</v>
+      </c>
+      <c r="S21" s="3">
+        <v>149270</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="W21" s="4">
+        <v>108615</v>
+      </c>
+      <c r="X21" s="10">
+        <v>112718</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>116820</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>125689</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>126703</v>
+      </c>
+      <c r="AC21" s="11">
+        <v>126703</v>
+      </c>
+      <c r="AD21" s="11">
+        <v>136274</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>137270</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>159166</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>170952</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>204372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="9">
+        <v>651237</v>
+      </c>
+      <c r="E22" s="9">
+        <v>671360</v>
+      </c>
+      <c r="F22" s="9">
+        <v>692105</v>
+      </c>
+      <c r="G22" s="9">
+        <v>676705</v>
+      </c>
+      <c r="H22" s="9">
+        <v>673347</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P22" s="2">
+        <v>648993</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>615137</v>
+      </c>
+      <c r="R22" s="3">
+        <v>601400</v>
+      </c>
+      <c r="S22" s="3">
+        <v>611907</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="W22" s="4">
+        <v>639961</v>
+      </c>
+      <c r="X22" s="10">
+        <v>658429</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>676897</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>705930</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>713077</v>
+      </c>
+      <c r="AC22" s="11">
+        <v>713077</v>
+      </c>
+      <c r="AD22" s="11">
+        <v>811831</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>822429</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>949630</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>969210</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>1034911</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D23" s="9">
         <v>562535</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E23" s="9">
         <v>602579</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F23" s="9">
         <v>645474</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G23" s="9">
         <v>567830</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H23" s="9">
         <v>582701</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I23" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L23" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="N23" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="O23" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P23" s="2">
         <v>859755</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q23" s="2">
         <v>912668</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R23" s="3">
         <v>902394</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S23" s="3">
         <v>930324</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="U18" s="3" t="s">
+      <c r="U23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="V18" s="3" t="s">
+      <c r="V23" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W23" s="4">
         <v>688213</v>
       </c>
-      <c r="X18" s="10">
+      <c r="X23" s="10">
         <v>694998</v>
       </c>
-      <c r="Y18" s="10">
+      <c r="Y23" s="10">
         <v>701782</v>
       </c>
-      <c r="Z18" s="3" t="s">
+      <c r="Z23" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA23" s="3">
         <v>721744</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB23" s="3">
         <v>721187</v>
       </c>
-      <c r="AC18" s="11">
+      <c r="AC23" s="11">
         <v>721187</v>
       </c>
-      <c r="AD18" s="11">
+      <c r="AD23" s="11">
         <v>773824</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AE23" s="3">
         <v>779295</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AF23" s="3">
         <v>850631</v>
       </c>
-      <c r="AG18" s="1">
+      <c r="AG23" s="3">
         <v>861488</v>
       </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="9">
-        <v>9702</v>
-      </c>
-      <c r="E19" s="9">
-        <v>11370</v>
-      </c>
-      <c r="F19" s="9">
-        <v>13325</v>
-      </c>
-      <c r="G19" s="9">
-        <v>11939</v>
-      </c>
-      <c r="H19" s="9">
-        <v>11691</v>
-      </c>
-      <c r="I19" s="9">
-        <v>11364</v>
-      </c>
-      <c r="J19" s="9">
-        <v>11487</v>
-      </c>
-      <c r="K19" s="9">
-        <v>11736</v>
-      </c>
-      <c r="L19" s="9">
-        <v>11892</v>
-      </c>
-      <c r="M19" s="9">
-        <v>12231</v>
-      </c>
-      <c r="N19" s="9">
-        <v>9795</v>
-      </c>
-      <c r="O19" s="9">
-        <v>9153</v>
-      </c>
-      <c r="P19" s="2">
-        <v>8076</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>7000</v>
-      </c>
-      <c r="R19" s="3">
-        <v>6913</v>
-      </c>
-      <c r="S19" s="3">
-        <v>6871</v>
-      </c>
-      <c r="T19" s="2">
-        <v>8349</v>
-      </c>
-      <c r="U19" s="5">
-        <v>7614</v>
-      </c>
-      <c r="V19" s="5">
-        <v>7929</v>
-      </c>
-      <c r="W19" s="4">
-        <v>8147</v>
-      </c>
-      <c r="X19" s="10">
-        <v>8076</v>
-      </c>
-      <c r="Y19" s="10">
-        <v>8006</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>7929</v>
-      </c>
-      <c r="AA19" s="5">
-        <v>7989</v>
-      </c>
-      <c r="AB19" s="5">
-        <v>7993</v>
-      </c>
-      <c r="AC19" s="11">
-        <v>7993</v>
-      </c>
-      <c r="AD19" s="11">
-        <v>7759</v>
-      </c>
-      <c r="AE19" s="3">
-        <v>7736</v>
-      </c>
-      <c r="AF19" s="3">
-        <v>8608</v>
-      </c>
-      <c r="AG19" s="1">
-        <v>8772</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1136</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1297</v>
-      </c>
-      <c r="F20" s="9">
-        <v>1481</v>
-      </c>
-      <c r="G20" s="9">
-        <v>1391</v>
-      </c>
-      <c r="H20" s="9">
-        <v>1411</v>
-      </c>
-      <c r="I20" s="9">
-        <v>1442</v>
-      </c>
-      <c r="J20" s="9">
-        <v>1446</v>
-      </c>
-      <c r="K20" s="9">
-        <v>1479</v>
-      </c>
-      <c r="L20" s="9">
-        <v>1503</v>
-      </c>
-      <c r="M20" s="9">
-        <v>1548</v>
-      </c>
-      <c r="N20" s="9">
-        <v>1423</v>
-      </c>
-      <c r="O20" s="9">
-        <v>1362</v>
-      </c>
-      <c r="P20" s="2">
-        <v>1297</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>1232</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1228</v>
-      </c>
-      <c r="S20" s="3">
-        <v>1226</v>
-      </c>
-      <c r="T20" s="2">
-        <v>1354</v>
-      </c>
-      <c r="U20" s="5">
-        <v>1221</v>
-      </c>
-      <c r="V20" s="5">
-        <v>1247</v>
-      </c>
-      <c r="W20" s="4">
-        <v>1271</v>
-      </c>
-      <c r="X20" s="10">
-        <v>1286</v>
-      </c>
-      <c r="Y20" s="10">
-        <v>1300</v>
-      </c>
-      <c r="Z20" s="5">
-        <v>1400</v>
-      </c>
-      <c r="AA20" s="5">
-        <v>1372</v>
-      </c>
-      <c r="AB20" s="5">
-        <v>1384</v>
-      </c>
-      <c r="AC20" s="11">
-        <v>1384</v>
-      </c>
-      <c r="AD20" s="11">
-        <v>1405</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1407</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1360</v>
-      </c>
-      <c r="AG20" s="1">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2169</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2540</v>
-      </c>
-      <c r="F21" s="9">
-        <v>2974</v>
-      </c>
-      <c r="G21" s="9">
-        <v>2626</v>
-      </c>
-      <c r="H21" s="9">
-        <v>2606</v>
-      </c>
-      <c r="I21" s="9">
-        <v>2458</v>
-      </c>
-      <c r="J21" s="9">
-        <v>2487</v>
-      </c>
-      <c r="K21" s="9">
-        <v>2553</v>
-      </c>
-      <c r="L21" s="9">
-        <v>2612</v>
-      </c>
-      <c r="M21" s="9">
-        <v>2701</v>
-      </c>
-      <c r="N21" s="9">
-        <v>2243</v>
-      </c>
-      <c r="O21" s="9">
-        <v>2163</v>
-      </c>
-      <c r="P21" s="2">
-        <v>1985</v>
-      </c>
-      <c r="Q21" s="2">
-        <v>1807</v>
-      </c>
-      <c r="R21" s="3">
-        <v>1767</v>
-      </c>
-      <c r="S21" s="3">
-        <v>1734</v>
-      </c>
-      <c r="T21" s="2">
-        <v>1955</v>
-      </c>
-      <c r="U21" s="5">
-        <v>1861</v>
-      </c>
-      <c r="V21" s="5">
-        <v>1905</v>
-      </c>
-      <c r="W21" s="4">
-        <v>1925</v>
-      </c>
-      <c r="X21" s="10">
-        <v>1945</v>
-      </c>
-      <c r="Y21" s="10">
-        <v>1965</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>2046</v>
-      </c>
-      <c r="AA21" s="5">
-        <v>2028</v>
-      </c>
-      <c r="AB21" s="5">
-        <v>2041</v>
-      </c>
-      <c r="AC21" s="11">
-        <v>2041</v>
-      </c>
-      <c r="AD21" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>2049</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>2202</v>
-      </c>
-      <c r="AG21" s="1">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X22" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y22" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD22" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG22" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="9">
-        <v>15665</v>
-      </c>
-      <c r="E23" s="9">
-        <v>18368</v>
-      </c>
-      <c r="F23" s="9">
-        <v>21537</v>
-      </c>
-      <c r="G23" s="9">
-        <v>20433</v>
-      </c>
-      <c r="H23" s="9">
-        <v>19944</v>
-      </c>
-      <c r="I23" s="9">
-        <v>19145</v>
-      </c>
-      <c r="J23" s="9">
-        <v>19861</v>
-      </c>
-      <c r="K23" s="9">
-        <v>20628</v>
-      </c>
-      <c r="L23" s="9">
-        <v>21301</v>
-      </c>
-      <c r="M23" s="9">
-        <v>23506</v>
-      </c>
-      <c r="N23" s="9">
-        <v>26771</v>
-      </c>
-      <c r="O23" s="9">
-        <v>28509</v>
-      </c>
-      <c r="P23" s="2">
-        <v>30834</v>
-      </c>
-      <c r="Q23" s="2">
-        <v>33159</v>
-      </c>
-      <c r="R23" s="3">
-        <v>30941</v>
-      </c>
-      <c r="S23" s="3">
-        <v>27786</v>
-      </c>
-      <c r="T23" s="2">
-        <v>21006</v>
-      </c>
-      <c r="U23" s="5">
-        <v>23487</v>
-      </c>
-      <c r="V23" s="5">
-        <v>22116</v>
-      </c>
-      <c r="W23" s="4">
-        <v>19669</v>
-      </c>
-      <c r="X23" s="10">
-        <v>19659</v>
-      </c>
-      <c r="Y23" s="10">
-        <v>19649</v>
-      </c>
-      <c r="Z23" s="5">
-        <v>20511</v>
-      </c>
-      <c r="AA23" s="5">
-        <v>19591</v>
-      </c>
-      <c r="AB23" s="5">
-        <v>19364</v>
-      </c>
-      <c r="AC23" s="11">
-        <v>19364</v>
-      </c>
-      <c r="AD23" s="11">
-        <v>18054</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>17928</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>20489</v>
-      </c>
-      <c r="AG23" s="1">
-        <v>21008</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>916118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3401,100 +3500,103 @@
         <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D24" s="9">
-        <v>138</v>
+        <v>9702</v>
       </c>
       <c r="E24" s="9">
-        <v>164</v>
+        <v>11370</v>
       </c>
       <c r="F24" s="9">
-        <v>195</v>
+        <v>13325</v>
       </c>
       <c r="G24" s="9">
-        <v>163</v>
+        <v>11939</v>
       </c>
       <c r="H24" s="9">
-        <v>137</v>
+        <v>11691</v>
       </c>
       <c r="I24" s="9">
-        <v>130</v>
+        <v>11364</v>
       </c>
       <c r="J24" s="9">
-        <v>134</v>
+        <v>11487</v>
       </c>
       <c r="K24" s="9">
-        <v>138</v>
+        <v>11736</v>
       </c>
       <c r="L24" s="9">
-        <v>141</v>
+        <v>11892</v>
       </c>
       <c r="M24" s="9">
-        <v>143</v>
+        <v>12231</v>
       </c>
       <c r="N24" s="9">
-        <v>144</v>
+        <v>9795</v>
       </c>
       <c r="O24" s="9">
-        <v>137</v>
+        <v>9153</v>
       </c>
       <c r="P24" s="2">
-        <v>134</v>
+        <v>8076</v>
       </c>
       <c r="Q24" s="2">
-        <v>131</v>
+        <v>7000</v>
       </c>
       <c r="R24" s="3">
-        <v>134</v>
+        <v>6913</v>
       </c>
       <c r="S24" s="3">
-        <v>136</v>
+        <v>6871</v>
       </c>
       <c r="T24" s="2">
-        <v>150</v>
-      </c>
-      <c r="U24" s="3">
-        <v>171</v>
-      </c>
-      <c r="V24" s="3">
-        <v>165</v>
+        <v>8349</v>
+      </c>
+      <c r="U24" s="5">
+        <v>7614</v>
+      </c>
+      <c r="V24" s="5">
+        <v>7929</v>
       </c>
       <c r="W24" s="4">
-        <v>171</v>
+        <v>8147</v>
       </c>
       <c r="X24" s="10">
-        <v>178</v>
+        <v>8076</v>
       </c>
       <c r="Y24" s="10">
-        <v>185</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>191</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>192</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>195</v>
+        <v>8006</v>
+      </c>
+      <c r="Z24" s="5">
+        <v>7929</v>
+      </c>
+      <c r="AA24" s="5">
+        <v>7989</v>
+      </c>
+      <c r="AB24" s="5">
+        <v>7993</v>
       </c>
       <c r="AC24" s="11">
-        <v>195</v>
+        <v>7993</v>
       </c>
       <c r="AD24" s="11">
-        <v>178</v>
+        <v>7759</v>
       </c>
       <c r="AE24" s="3">
-        <v>176</v>
+        <v>7736</v>
       </c>
       <c r="AF24" s="3">
-        <v>231</v>
-      </c>
-      <c r="AG24" s="1">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+        <v>8608</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>8772</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3502,1110 +3604,1143 @@
         <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D25" s="9">
-        <v>2679</v>
+        <v>1136</v>
       </c>
       <c r="E25" s="9">
-        <v>3363</v>
+        <v>1297</v>
       </c>
       <c r="F25" s="9">
-        <v>4222</v>
+        <v>1481</v>
       </c>
       <c r="G25" s="9">
-        <v>4017</v>
+        <v>1391</v>
       </c>
       <c r="H25" s="9">
-        <v>4237</v>
+        <v>1411</v>
       </c>
       <c r="I25" s="9">
-        <v>4457</v>
+        <v>1442</v>
       </c>
       <c r="J25" s="9">
-        <v>4486</v>
+        <v>1446</v>
       </c>
       <c r="K25" s="9">
-        <v>4603</v>
+        <v>1479</v>
       </c>
       <c r="L25" s="9">
-        <v>4712</v>
+        <v>1503</v>
       </c>
       <c r="M25" s="9">
-        <v>4829</v>
+        <v>1548</v>
       </c>
       <c r="N25" s="9">
-        <v>4747</v>
+        <v>1423</v>
       </c>
       <c r="O25" s="9">
-        <v>4653</v>
+        <v>1362</v>
       </c>
       <c r="P25" s="2">
-        <v>4598</v>
+        <v>1297</v>
       </c>
       <c r="Q25" s="2">
-        <v>4543</v>
+        <v>1232</v>
       </c>
       <c r="R25" s="3">
-        <v>4637</v>
+        <v>1228</v>
       </c>
       <c r="S25" s="3">
-        <v>4731</v>
+        <v>1226</v>
       </c>
       <c r="T25" s="2">
-        <v>5158</v>
+        <v>1354</v>
       </c>
       <c r="U25" s="5">
-        <v>5386</v>
+        <v>1221</v>
       </c>
       <c r="V25" s="5">
-        <v>5258</v>
+        <v>1247</v>
       </c>
       <c r="W25" s="4">
-        <v>5453</v>
+        <v>1271</v>
       </c>
       <c r="X25" s="10">
-        <v>5391</v>
+        <v>1286</v>
       </c>
       <c r="Y25" s="10">
-        <v>5330</v>
+        <v>1300</v>
       </c>
       <c r="Z25" s="5">
-        <v>4948</v>
+        <v>1400</v>
       </c>
       <c r="AA25" s="5">
-        <v>5108</v>
+        <v>1372</v>
       </c>
       <c r="AB25" s="5">
-        <v>5086</v>
+        <v>1384</v>
       </c>
       <c r="AC25" s="11">
-        <v>5086</v>
+        <v>1384</v>
       </c>
       <c r="AD25" s="11">
-        <v>5104</v>
+        <v>1405</v>
       </c>
       <c r="AE25" s="3">
-        <v>5106</v>
+        <v>1407</v>
       </c>
       <c r="AF25" s="3">
-        <v>5685</v>
-      </c>
-      <c r="AG25" s="1">
-        <v>5859</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+        <v>1360</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>1373</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D26" s="9">
-        <v>13941</v>
+        <v>2169</v>
       </c>
       <c r="E26" s="9">
-        <v>13971</v>
+        <v>2540</v>
       </c>
       <c r="F26" s="9">
-        <v>14001</v>
+        <v>2974</v>
       </c>
       <c r="G26" s="9">
-        <v>13558</v>
+        <v>2626</v>
       </c>
       <c r="H26" s="9">
-        <v>13365</v>
+        <v>2606</v>
       </c>
       <c r="I26" s="9">
-        <v>13602</v>
+        <v>2458</v>
       </c>
       <c r="J26" s="9">
-        <v>13684</v>
+        <v>2487</v>
       </c>
       <c r="K26" s="9">
-        <v>13821</v>
+        <v>2553</v>
       </c>
       <c r="L26" s="9">
-        <v>13907</v>
+        <v>2612</v>
       </c>
       <c r="M26" s="9">
-        <v>14042</v>
+        <v>2701</v>
       </c>
       <c r="N26" s="9">
-        <v>13352</v>
+        <v>2243</v>
       </c>
       <c r="O26" s="9">
-        <v>13096</v>
+        <v>2163</v>
       </c>
       <c r="P26" s="2">
-        <v>12760</v>
+        <v>1985</v>
       </c>
       <c r="Q26" s="2">
-        <v>12424</v>
+        <v>1807</v>
       </c>
       <c r="R26" s="3">
-        <v>12621</v>
+        <v>1767</v>
       </c>
       <c r="S26" s="3">
-        <v>12822</v>
+        <v>1734</v>
       </c>
       <c r="T26" s="2">
-        <v>14185</v>
+        <v>1955</v>
       </c>
       <c r="U26" s="5">
-        <v>14884</v>
+        <v>1861</v>
       </c>
       <c r="V26" s="5">
-        <v>14530</v>
+        <v>1905</v>
       </c>
       <c r="W26" s="4">
-        <v>15081</v>
+        <v>1925</v>
       </c>
       <c r="X26" s="10">
-        <v>15271</v>
+        <v>1945</v>
       </c>
       <c r="Y26" s="10">
-        <v>15462</v>
+        <v>1965</v>
       </c>
       <c r="Z26" s="5">
-        <v>15435</v>
+        <v>2046</v>
       </c>
       <c r="AA26" s="5">
-        <v>15612</v>
+        <v>2028</v>
       </c>
       <c r="AB26" s="5">
-        <v>15710</v>
+        <v>2041</v>
       </c>
       <c r="AC26" s="11">
-        <v>15710</v>
+        <v>2041</v>
       </c>
       <c r="AD26" s="11">
-        <v>15346</v>
+        <v>2048</v>
       </c>
       <c r="AE26" s="3">
-        <v>15310</v>
+        <v>2049</v>
       </c>
       <c r="AF26" s="3">
-        <v>17234</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>18090</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+        <v>2202</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>2225</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="9">
-        <v>59291</v>
-      </c>
-      <c r="E27" s="9">
-        <v>55057</v>
-      </c>
-      <c r="F27" s="9">
-        <v>51125</v>
-      </c>
-      <c r="G27" s="9">
-        <v>57250</v>
-      </c>
-      <c r="H27" s="9">
-        <v>58525</v>
-      </c>
-      <c r="I27" s="9">
-        <v>60392</v>
-      </c>
-      <c r="J27" s="9">
-        <v>60874</v>
-      </c>
-      <c r="K27" s="9">
-        <v>62412</v>
-      </c>
-      <c r="L27" s="9">
-        <v>64083</v>
-      </c>
-      <c r="M27" s="9">
-        <v>65917</v>
-      </c>
-      <c r="N27" s="9">
-        <v>57715</v>
-      </c>
-      <c r="O27" s="9">
-        <v>59112</v>
-      </c>
-      <c r="P27" s="2">
-        <v>57382</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>55652</v>
-      </c>
-      <c r="R27" s="3">
-        <v>58952</v>
-      </c>
-      <c r="S27" s="3">
-        <v>62294</v>
-      </c>
-      <c r="T27" s="2">
-        <v>76957</v>
-      </c>
-      <c r="U27" s="5">
-        <v>85406</v>
-      </c>
-      <c r="V27" s="5">
-        <v>82691</v>
-      </c>
-      <c r="W27" s="4">
-        <v>88622</v>
-      </c>
-      <c r="X27" s="10">
-        <v>91624</v>
-      </c>
-      <c r="Y27" s="10">
-        <v>94626</v>
-      </c>
-      <c r="Z27" s="5">
-        <v>95855</v>
-      </c>
-      <c r="AA27" s="5">
-        <v>97691</v>
-      </c>
-      <c r="AB27" s="5">
-        <v>99168</v>
-      </c>
-      <c r="AC27" s="11">
-        <v>99168</v>
-      </c>
-      <c r="AD27" s="11">
-        <v>99365</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>99385</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>109652</v>
-      </c>
-      <c r="AG27" s="1">
-        <v>111742</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X27" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y27" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D28" s="9">
-        <v>6994</v>
+        <v>15665</v>
       </c>
       <c r="E28" s="9">
-        <v>7529</v>
+        <v>18368</v>
       </c>
       <c r="F28" s="9">
-        <v>8105</v>
+        <v>21537</v>
       </c>
       <c r="G28" s="9">
-        <v>7252</v>
+        <v>20433</v>
       </c>
       <c r="H28" s="9">
-        <v>7021</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>18</v>
+        <v>19944</v>
+      </c>
+      <c r="I28" s="9">
+        <v>19145</v>
       </c>
       <c r="J28" s="9">
-        <v>6782</v>
+        <v>19861</v>
       </c>
       <c r="K28" s="9">
-        <v>6597</v>
+        <v>20628</v>
       </c>
       <c r="L28" s="9">
-        <v>6318</v>
+        <v>21301</v>
       </c>
       <c r="M28" s="9">
-        <v>6104</v>
+        <v>23506</v>
       </c>
       <c r="N28" s="9">
-        <v>5957</v>
+        <v>26771</v>
       </c>
       <c r="O28" s="9">
-        <v>5457</v>
+        <v>28509</v>
       </c>
       <c r="P28" s="2">
-        <v>5122</v>
+        <v>30834</v>
       </c>
       <c r="Q28" s="2">
-        <v>4787</v>
+        <v>33159</v>
       </c>
       <c r="R28" s="3">
-        <v>5120</v>
+        <v>30941</v>
       </c>
       <c r="S28" s="3">
-        <v>5460</v>
+        <v>27786</v>
       </c>
       <c r="T28" s="2">
-        <v>6994</v>
+        <v>21006</v>
       </c>
       <c r="U28" s="5">
-        <v>8644</v>
+        <v>23487</v>
       </c>
       <c r="V28" s="5">
-        <v>8255</v>
+        <v>22116</v>
       </c>
       <c r="W28" s="4">
-        <v>8878</v>
+        <v>19669</v>
       </c>
       <c r="X28" s="10">
-        <v>9076</v>
+        <v>19659</v>
       </c>
       <c r="Y28" s="10">
-        <v>9275</v>
+        <v>19649</v>
       </c>
       <c r="Z28" s="5">
-        <v>8614</v>
+        <v>20511</v>
       </c>
       <c r="AA28" s="5">
-        <v>9070</v>
+        <v>19591</v>
       </c>
       <c r="AB28" s="5">
-        <v>9151</v>
+        <v>19364</v>
       </c>
       <c r="AC28" s="11">
-        <v>9151</v>
+        <v>19364</v>
       </c>
       <c r="AD28" s="11">
-        <v>9174</v>
+        <v>18054</v>
       </c>
       <c r="AE28" s="3">
-        <v>9176</v>
+        <v>17928</v>
       </c>
       <c r="AF28" s="3">
-        <v>9110</v>
-      </c>
-      <c r="AG28" s="1">
-        <v>9112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+        <v>20489</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>21008</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>22063</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D29" s="9">
-        <v>4071</v>
+        <v>138</v>
       </c>
       <c r="E29" s="9">
-        <v>2521</v>
+        <v>164</v>
       </c>
       <c r="F29" s="9">
-        <v>1561</v>
+        <v>195</v>
       </c>
       <c r="G29" s="9">
-        <v>1664</v>
+        <v>163</v>
       </c>
       <c r="H29" s="9">
-        <v>1328</v>
+        <v>137</v>
       </c>
       <c r="I29" s="9">
-        <v>955</v>
+        <v>130</v>
       </c>
       <c r="J29" s="9">
-        <v>912</v>
+        <v>134</v>
       </c>
       <c r="K29" s="9">
-        <v>847</v>
+        <v>138</v>
       </c>
       <c r="L29" s="9">
-        <v>803</v>
+        <v>141</v>
       </c>
       <c r="M29" s="9">
-        <v>712</v>
+        <v>143</v>
       </c>
       <c r="N29" s="9">
-        <v>558</v>
+        <v>144</v>
       </c>
       <c r="O29" s="9">
-        <v>506</v>
+        <v>137</v>
       </c>
       <c r="P29" s="2">
-        <v>414</v>
+        <v>134</v>
       </c>
       <c r="Q29" s="2">
-        <v>322</v>
+        <v>131</v>
       </c>
       <c r="R29" s="3">
-        <v>326</v>
+        <v>134</v>
       </c>
       <c r="S29" s="3">
-        <v>334</v>
+        <v>136</v>
       </c>
       <c r="T29" s="2">
-        <v>448</v>
+        <v>150</v>
       </c>
       <c r="U29" s="3">
-        <v>417</v>
+        <v>171</v>
       </c>
       <c r="V29" s="3">
-        <v>428</v>
+        <v>165</v>
       </c>
       <c r="W29" s="4">
-        <v>455</v>
+        <v>171</v>
       </c>
       <c r="X29" s="10">
-        <v>1477</v>
+        <v>178</v>
       </c>
       <c r="Y29" s="10">
-        <v>2499</v>
-      </c>
-      <c r="Z29" s="5">
-        <v>5560</v>
-      </c>
-      <c r="AA29" s="5">
-        <v>1980</v>
-      </c>
-      <c r="AB29" s="5">
-        <v>760</v>
+        <v>185</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>191</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>192</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>195</v>
       </c>
       <c r="AC29" s="11">
-        <v>760</v>
+        <v>195</v>
       </c>
       <c r="AD29" s="11">
-        <v>1253</v>
+        <v>178</v>
       </c>
       <c r="AE29" s="3">
-        <v>1291</v>
+        <v>176</v>
       </c>
       <c r="AF29" s="3">
-        <v>730</v>
-      </c>
-      <c r="AG29" s="1">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>222</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D30" s="9">
-        <v>57899</v>
+        <v>2679</v>
       </c>
       <c r="E30" s="9">
-        <v>65594</v>
+        <v>3363</v>
       </c>
       <c r="F30" s="9">
-        <v>74312</v>
+        <v>4222</v>
       </c>
       <c r="G30" s="9">
-        <v>67826</v>
+        <v>4017</v>
       </c>
       <c r="H30" s="9">
-        <v>62048</v>
+        <v>4237</v>
       </c>
       <c r="I30" s="9">
-        <v>58469</v>
+        <v>4457</v>
       </c>
       <c r="J30" s="9">
-        <v>57182</v>
+        <v>4486</v>
       </c>
       <c r="K30" s="9">
-        <v>55394</v>
+        <v>4603</v>
       </c>
       <c r="L30" s="9">
-        <v>53276</v>
+        <v>4712</v>
       </c>
       <c r="M30" s="9">
-        <v>51987</v>
+        <v>4829</v>
       </c>
       <c r="N30" s="9">
-        <v>51978</v>
+        <v>4747</v>
       </c>
       <c r="O30" s="9">
-        <v>50663</v>
+        <v>4653</v>
       </c>
       <c r="P30" s="2">
-        <v>49788</v>
+        <v>4598</v>
       </c>
       <c r="Q30" s="2">
-        <v>48913</v>
+        <v>4543</v>
       </c>
       <c r="R30" s="3">
-        <v>50486</v>
+        <v>4637</v>
       </c>
       <c r="S30" s="3">
-        <v>52062</v>
+        <v>4731</v>
       </c>
       <c r="T30" s="2">
-        <v>58170</v>
+        <v>5158</v>
       </c>
       <c r="U30" s="5">
-        <v>59824</v>
+        <v>5386</v>
       </c>
       <c r="V30" s="5">
-        <v>58797</v>
+        <v>5258</v>
       </c>
       <c r="W30" s="4">
-        <v>61410</v>
+        <v>5453</v>
       </c>
       <c r="X30" s="10">
-        <v>61591</v>
+        <v>5391</v>
       </c>
       <c r="Y30" s="10">
-        <v>61772</v>
+        <v>5330</v>
       </c>
       <c r="Z30" s="5">
-        <v>60156</v>
+        <v>4948</v>
       </c>
       <c r="AA30" s="5">
-        <v>61343</v>
+        <v>5108</v>
       </c>
       <c r="AB30" s="5">
-        <v>61537</v>
+        <v>5086</v>
       </c>
       <c r="AC30" s="11">
-        <v>61537</v>
+        <v>5086</v>
       </c>
       <c r="AD30" s="11">
-        <v>66523</v>
+        <v>5104</v>
       </c>
       <c r="AE30" s="3">
-        <v>67043</v>
+        <v>5106</v>
       </c>
       <c r="AF30" s="3">
-        <v>69929</v>
-      </c>
-      <c r="AG30" s="1">
-        <v>70753</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+        <v>5685</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>5859</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>6135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D31" s="9">
-        <v>232065</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>96</v>
+        <v>13941</v>
+      </c>
+      <c r="E31" s="9">
+        <v>13971</v>
       </c>
       <c r="F31" s="9">
-        <v>229222</v>
+        <v>14001</v>
       </c>
       <c r="G31" s="9">
-        <v>214551</v>
+        <v>13558</v>
       </c>
       <c r="H31" s="9">
-        <v>220488</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>103</v>
+        <v>13365</v>
+      </c>
+      <c r="I31" s="9">
+        <v>13602</v>
+      </c>
+      <c r="J31" s="9">
+        <v>13684</v>
+      </c>
+      <c r="K31" s="9">
+        <v>13821</v>
+      </c>
+      <c r="L31" s="9">
+        <v>13907</v>
+      </c>
+      <c r="M31" s="9">
+        <v>14042</v>
+      </c>
+      <c r="N31" s="9">
+        <v>13352</v>
+      </c>
+      <c r="O31" s="9">
+        <v>13096</v>
       </c>
       <c r="P31" s="2">
-        <v>205647</v>
+        <v>12760</v>
       </c>
       <c r="Q31" s="2">
-        <v>196280</v>
+        <v>12424</v>
       </c>
       <c r="R31" s="3">
-        <v>197409</v>
+        <v>12621</v>
       </c>
       <c r="S31" s="3">
-        <v>198784</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="V31" s="3" t="s">
-        <v>148</v>
+        <v>12822</v>
+      </c>
+      <c r="T31" s="2">
+        <v>14185</v>
+      </c>
+      <c r="U31" s="5">
+        <v>14884</v>
+      </c>
+      <c r="V31" s="5">
+        <v>14530</v>
       </c>
       <c r="W31" s="4">
-        <v>233433</v>
+        <v>15081</v>
       </c>
       <c r="X31" s="10">
-        <v>236635</v>
+        <v>15271</v>
       </c>
       <c r="Y31" s="10">
-        <v>239838</v>
-      </c>
-      <c r="Z31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA31" s="3">
-        <v>241915</v>
-      </c>
-      <c r="AB31" s="3">
-        <v>242484</v>
+        <v>15462</v>
+      </c>
+      <c r="Z31" s="5">
+        <v>15435</v>
+      </c>
+      <c r="AA31" s="5">
+        <v>15612</v>
+      </c>
+      <c r="AB31" s="5">
+        <v>15710</v>
       </c>
       <c r="AC31" s="11">
-        <v>242484</v>
+        <v>15710</v>
       </c>
       <c r="AD31" s="11">
-        <v>245897</v>
+        <v>15346</v>
       </c>
       <c r="AE31" s="3">
-        <v>246241</v>
+        <v>15310</v>
       </c>
       <c r="AF31" s="3">
-        <v>276760</v>
-      </c>
-      <c r="AG31" s="1">
-        <v>283936</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+        <v>17234</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>18090</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>18731</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D32" s="9">
-        <v>43955</v>
+        <v>59291</v>
       </c>
       <c r="E32" s="9">
-        <v>43218</v>
+        <v>55057</v>
       </c>
       <c r="F32" s="9">
-        <v>42493</v>
+        <v>51125</v>
       </c>
       <c r="G32" s="9">
-        <v>36165</v>
+        <v>57250</v>
       </c>
       <c r="H32" s="9">
-        <v>37051</v>
+        <v>58525</v>
       </c>
       <c r="I32" s="9">
-        <v>37453</v>
+        <v>60392</v>
       </c>
       <c r="J32" s="9">
-        <v>37842</v>
+        <v>60874</v>
       </c>
       <c r="K32" s="9">
-        <v>38917</v>
+        <v>62412</v>
       </c>
       <c r="L32" s="9">
-        <v>39884</v>
+        <v>64083</v>
       </c>
       <c r="M32" s="9">
-        <v>41062</v>
+        <v>65917</v>
       </c>
       <c r="N32" s="9">
-        <v>37304</v>
+        <v>57715</v>
       </c>
       <c r="O32" s="9">
-        <v>36486</v>
+        <v>59112</v>
       </c>
       <c r="P32" s="2">
-        <v>35021</v>
+        <v>57382</v>
       </c>
       <c r="Q32" s="2">
-        <v>33556</v>
+        <v>55652</v>
       </c>
       <c r="R32" s="3">
-        <v>33371</v>
+        <v>58952</v>
       </c>
       <c r="S32" s="3">
-        <v>33222</v>
+        <v>62294</v>
       </c>
       <c r="T32" s="2">
-        <v>36068</v>
+        <v>76957</v>
       </c>
       <c r="U32" s="5">
-        <v>38102</v>
+        <v>85406</v>
       </c>
       <c r="V32" s="5">
-        <v>37420</v>
+        <v>82691</v>
       </c>
       <c r="W32" s="4">
-        <v>38234</v>
+        <v>88622</v>
       </c>
       <c r="X32" s="10">
-        <v>38596</v>
+        <v>91624</v>
       </c>
       <c r="Y32" s="10">
-        <v>38958</v>
+        <v>94626</v>
       </c>
       <c r="Z32" s="5">
-        <v>38599</v>
+        <v>95855</v>
       </c>
       <c r="AA32" s="5">
-        <v>38730</v>
+        <v>97691</v>
       </c>
       <c r="AB32" s="5">
-        <v>38775</v>
+        <v>99168</v>
       </c>
       <c r="AC32" s="11">
-        <v>38775</v>
+        <v>99168</v>
       </c>
       <c r="AD32" s="11">
-        <v>39782</v>
+        <v>99365</v>
       </c>
       <c r="AE32" s="3">
-        <v>39884</v>
+        <v>99385</v>
       </c>
       <c r="AF32" s="3">
-        <v>43699</v>
-      </c>
-      <c r="AG32" s="1">
-        <v>44802</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+        <v>109652</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>111742</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>120275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D33" s="9">
-        <v>1946</v>
+        <v>6994</v>
       </c>
       <c r="E33" s="9">
-        <v>2220</v>
+        <v>7529</v>
       </c>
       <c r="F33" s="9">
-        <v>2533</v>
+        <v>8105</v>
       </c>
       <c r="G33" s="9">
-        <v>2235</v>
+        <v>7252</v>
       </c>
       <c r="H33" s="9">
-        <v>2180</v>
-      </c>
-      <c r="I33" s="9">
-        <v>2057</v>
+        <v>7021</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="J33" s="9">
-        <v>2053</v>
+        <v>6782</v>
       </c>
       <c r="K33" s="9">
-        <v>2041</v>
+        <v>6597</v>
       </c>
       <c r="L33" s="9">
-        <v>2029</v>
+        <v>6318</v>
       </c>
       <c r="M33" s="9">
-        <v>2018</v>
+        <v>6104</v>
       </c>
       <c r="N33" s="9">
-        <v>2261</v>
+        <v>5957</v>
       </c>
       <c r="O33" s="9">
-        <v>2276</v>
+        <v>5457</v>
       </c>
       <c r="P33" s="2">
-        <v>2363</v>
+        <v>5122</v>
       </c>
       <c r="Q33" s="2">
-        <v>2450</v>
+        <v>4787</v>
       </c>
       <c r="R33" s="3">
-        <v>2437</v>
+        <v>5120</v>
       </c>
       <c r="S33" s="3">
-        <v>2427</v>
+        <v>5460</v>
       </c>
       <c r="T33" s="2">
-        <v>2116</v>
+        <v>6994</v>
       </c>
       <c r="U33" s="5">
-        <v>1947</v>
+        <v>8644</v>
       </c>
       <c r="V33" s="5">
-        <v>2003</v>
+        <v>8255</v>
       </c>
       <c r="W33" s="4">
-        <v>1906</v>
+        <v>8878</v>
       </c>
       <c r="X33" s="10">
-        <v>1936</v>
+        <v>9076</v>
       </c>
       <c r="Y33" s="10">
-        <v>1966</v>
+        <v>9275</v>
       </c>
       <c r="Z33" s="5">
-        <v>2196</v>
+        <v>8614</v>
       </c>
       <c r="AA33" s="5">
-        <v>2098</v>
+        <v>9070</v>
       </c>
       <c r="AB33" s="5">
-        <v>2110</v>
+        <v>9151</v>
       </c>
       <c r="AC33" s="11">
-        <v>2110</v>
+        <v>9151</v>
       </c>
       <c r="AD33" s="11">
-        <v>2129</v>
+        <v>9174</v>
       </c>
       <c r="AE33" s="3">
-        <v>2131</v>
+        <v>9176</v>
       </c>
       <c r="AF33" s="3">
-        <v>2438</v>
-      </c>
-      <c r="AG33" s="1">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+        <v>9110</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>9112</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>9077</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D34" s="9">
-        <v>128227</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>107</v>
+        <v>4071</v>
+      </c>
+      <c r="E34" s="9">
+        <v>2521</v>
       </c>
       <c r="F34" s="9">
-        <v>139951</v>
+        <v>1561</v>
       </c>
       <c r="G34" s="9">
-        <v>126867</v>
+        <v>1664</v>
       </c>
       <c r="H34" s="9">
-        <v>126785</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="N34" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="O34" s="9" t="s">
-        <v>114</v>
+        <v>1328</v>
+      </c>
+      <c r="I34" s="9">
+        <v>955</v>
+      </c>
+      <c r="J34" s="9">
+        <v>912</v>
+      </c>
+      <c r="K34" s="9">
+        <v>847</v>
+      </c>
+      <c r="L34" s="9">
+        <v>803</v>
+      </c>
+      <c r="M34" s="9">
+        <v>712</v>
+      </c>
+      <c r="N34" s="9">
+        <v>558</v>
+      </c>
+      <c r="O34" s="9">
+        <v>506</v>
       </c>
       <c r="P34" s="2">
-        <v>117790</v>
+        <v>414</v>
       </c>
       <c r="Q34" s="2">
-        <v>114206</v>
+        <v>322</v>
       </c>
       <c r="R34" s="3">
-        <v>113754</v>
+        <v>326</v>
       </c>
       <c r="S34" s="3">
-        <v>113366</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>149</v>
+        <v>334</v>
+      </c>
+      <c r="T34" s="2">
+        <v>448</v>
+      </c>
+      <c r="U34" s="3">
+        <v>417</v>
+      </c>
+      <c r="V34" s="3">
+        <v>428</v>
       </c>
       <c r="W34" s="4">
-        <v>122810</v>
+        <v>455</v>
       </c>
       <c r="X34" s="10">
-        <v>125964</v>
+        <v>1477</v>
       </c>
       <c r="Y34" s="10">
-        <v>129119</v>
-      </c>
-      <c r="Z34" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA34" s="3">
-        <v>135429</v>
-      </c>
-      <c r="AB34" s="3">
-        <v>136909</v>
+        <v>2499</v>
+      </c>
+      <c r="Z34" s="5">
+        <v>5560</v>
+      </c>
+      <c r="AA34" s="5">
+        <v>1980</v>
+      </c>
+      <c r="AB34" s="5">
+        <v>760</v>
       </c>
       <c r="AC34" s="11">
-        <v>136909</v>
+        <v>760</v>
       </c>
       <c r="AD34" s="11">
-        <v>132948</v>
+        <v>1253</v>
       </c>
       <c r="AE34" s="3">
-        <v>132558</v>
+        <v>1291</v>
       </c>
       <c r="AF34" s="3">
-        <v>142234</v>
-      </c>
-      <c r="AG34" s="1">
-        <v>142641</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>1061</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D35" s="9">
-        <v>1226</v>
+        <v>57899</v>
       </c>
       <c r="E35" s="9">
-        <v>1220</v>
+        <v>65594</v>
       </c>
       <c r="F35" s="9">
-        <v>1214</v>
+        <v>74312</v>
       </c>
       <c r="G35" s="9">
-        <v>1038</v>
+        <v>67826</v>
       </c>
       <c r="H35" s="9">
-        <v>1004</v>
+        <v>62048</v>
       </c>
       <c r="I35" s="9">
-        <v>1028</v>
+        <v>58469</v>
       </c>
       <c r="J35" s="9">
-        <v>1032</v>
+        <v>57182</v>
       </c>
       <c r="K35" s="9">
-        <v>1018</v>
+        <v>55394</v>
       </c>
       <c r="L35" s="9">
-        <v>1009</v>
+        <v>53276</v>
       </c>
       <c r="M35" s="9">
-        <v>998</v>
+        <v>51987</v>
       </c>
       <c r="N35" s="9">
-        <v>1075</v>
+        <v>51978</v>
       </c>
       <c r="O35" s="9">
-        <v>1068</v>
+        <v>50663</v>
       </c>
       <c r="P35" s="2">
-        <v>1088</v>
+        <v>49788</v>
       </c>
       <c r="Q35" s="2">
-        <v>1108</v>
+        <v>48913</v>
       </c>
       <c r="R35" s="3">
-        <v>1107</v>
+        <v>50486</v>
       </c>
       <c r="S35" s="3">
-        <v>1106</v>
+        <v>52062</v>
       </c>
       <c r="T35" s="2">
-        <v>1035</v>
+        <v>58170</v>
       </c>
       <c r="U35" s="5">
-        <v>1074</v>
+        <v>59824</v>
       </c>
       <c r="V35" s="5">
-        <v>1058</v>
+        <v>58797</v>
       </c>
       <c r="W35" s="4">
-        <v>1046</v>
+        <v>61410</v>
       </c>
       <c r="X35" s="10">
-        <v>1061</v>
+        <v>61591</v>
       </c>
       <c r="Y35" s="10">
-        <v>1076</v>
+        <v>61772</v>
       </c>
       <c r="Z35" s="5">
-        <v>1114</v>
+        <v>60156</v>
       </c>
       <c r="AA35" s="5">
-        <v>1097</v>
+        <v>61343</v>
       </c>
       <c r="AB35" s="5">
-        <v>1098</v>
+        <v>61537</v>
       </c>
       <c r="AC35" s="11">
-        <v>1098</v>
+        <v>61537</v>
       </c>
       <c r="AD35" s="11">
-        <v>1110</v>
+        <v>66523</v>
       </c>
       <c r="AE35" s="3">
-        <v>1111</v>
+        <v>67043</v>
       </c>
       <c r="AF35" s="3">
-        <v>1248</v>
-      </c>
-      <c r="AG35" s="1">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+        <v>69929</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>70753</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>70950</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4613,336 +4748,1058 @@
         <v>49</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" s="9">
+        <v>232065</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="9">
+        <v>229222</v>
+      </c>
+      <c r="G36" s="9">
+        <v>214551</v>
+      </c>
+      <c r="H36" s="9">
+        <v>220488</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="P36" s="2">
+        <v>205647</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>196280</v>
+      </c>
+      <c r="R36" s="3">
+        <v>197409</v>
+      </c>
+      <c r="S36" s="3">
+        <v>198784</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="W36" s="4">
+        <v>233433</v>
+      </c>
+      <c r="X36" s="10">
+        <v>236635</v>
+      </c>
+      <c r="Y36" s="10">
+        <v>239838</v>
+      </c>
+      <c r="Z36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>241915</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>242484</v>
+      </c>
+      <c r="AC36" s="11">
+        <v>242484</v>
+      </c>
+      <c r="AD36" s="11">
+        <v>245897</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>246241</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>276760</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>283936</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>298329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="9">
+        <v>43955</v>
+      </c>
+      <c r="E37" s="9">
+        <v>43218</v>
+      </c>
+      <c r="F37" s="9">
+        <v>42493</v>
+      </c>
+      <c r="G37" s="9">
+        <v>36165</v>
+      </c>
+      <c r="H37" s="9">
+        <v>37051</v>
+      </c>
+      <c r="I37" s="9">
+        <v>37453</v>
+      </c>
+      <c r="J37" s="9">
+        <v>37842</v>
+      </c>
+      <c r="K37" s="9">
+        <v>38917</v>
+      </c>
+      <c r="L37" s="9">
+        <v>39884</v>
+      </c>
+      <c r="M37" s="9">
+        <v>41062</v>
+      </c>
+      <c r="N37" s="9">
+        <v>37304</v>
+      </c>
+      <c r="O37" s="9">
+        <v>36486</v>
+      </c>
+      <c r="P37" s="2">
+        <v>35021</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>33556</v>
+      </c>
+      <c r="R37" s="3">
+        <v>33371</v>
+      </c>
+      <c r="S37" s="3">
+        <v>33222</v>
+      </c>
+      <c r="T37" s="2">
+        <v>36068</v>
+      </c>
+      <c r="U37" s="5">
+        <v>38102</v>
+      </c>
+      <c r="V37" s="5">
+        <v>37420</v>
+      </c>
+      <c r="W37" s="4">
+        <v>38234</v>
+      </c>
+      <c r="X37" s="10">
+        <v>38596</v>
+      </c>
+      <c r="Y37" s="10">
+        <v>38958</v>
+      </c>
+      <c r="Z37" s="5">
+        <v>38599</v>
+      </c>
+      <c r="AA37" s="5">
+        <v>38730</v>
+      </c>
+      <c r="AB37" s="5">
+        <v>38775</v>
+      </c>
+      <c r="AC37" s="11">
+        <v>38775</v>
+      </c>
+      <c r="AD37" s="11">
+        <v>39782</v>
+      </c>
+      <c r="AE37" s="3">
+        <v>39884</v>
+      </c>
+      <c r="AF37" s="3">
+        <v>43699</v>
+      </c>
+      <c r="AG37" s="3">
+        <v>44802</v>
+      </c>
+      <c r="AH37" s="3">
+        <v>47308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="9">
+        <v>1946</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2220</v>
+      </c>
+      <c r="F38" s="9">
+        <v>2533</v>
+      </c>
+      <c r="G38" s="9">
+        <v>2235</v>
+      </c>
+      <c r="H38" s="9">
+        <v>2180</v>
+      </c>
+      <c r="I38" s="9">
+        <v>2057</v>
+      </c>
+      <c r="J38" s="9">
+        <v>2053</v>
+      </c>
+      <c r="K38" s="9">
+        <v>2041</v>
+      </c>
+      <c r="L38" s="9">
+        <v>2029</v>
+      </c>
+      <c r="M38" s="9">
+        <v>2018</v>
+      </c>
+      <c r="N38" s="9">
+        <v>2261</v>
+      </c>
+      <c r="O38" s="9">
+        <v>2276</v>
+      </c>
+      <c r="P38" s="2">
+        <v>2363</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>2450</v>
+      </c>
+      <c r="R38" s="3">
+        <v>2437</v>
+      </c>
+      <c r="S38" s="3">
+        <v>2427</v>
+      </c>
+      <c r="T38" s="2">
+        <v>2116</v>
+      </c>
+      <c r="U38" s="5">
+        <v>1947</v>
+      </c>
+      <c r="V38" s="5">
+        <v>2003</v>
+      </c>
+      <c r="W38" s="4">
+        <v>1906</v>
+      </c>
+      <c r="X38" s="10">
+        <v>1936</v>
+      </c>
+      <c r="Y38" s="10">
+        <v>1966</v>
+      </c>
+      <c r="Z38" s="5">
+        <v>2196</v>
+      </c>
+      <c r="AA38" s="5">
+        <v>2098</v>
+      </c>
+      <c r="AB38" s="5">
+        <v>2110</v>
+      </c>
+      <c r="AC38" s="11">
+        <v>2110</v>
+      </c>
+      <c r="AD38" s="11">
+        <v>2129</v>
+      </c>
+      <c r="AE38" s="3">
+        <v>2131</v>
+      </c>
+      <c r="AF38" s="3">
+        <v>2438</v>
+      </c>
+      <c r="AG38" s="3">
+        <v>2510</v>
+      </c>
+      <c r="AH38" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="9">
+        <v>128227</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="9">
+        <v>139951</v>
+      </c>
+      <c r="G39" s="9">
+        <v>126867</v>
+      </c>
+      <c r="H39" s="9">
+        <v>126785</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="P39" s="2">
+        <v>117790</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>114206</v>
+      </c>
+      <c r="R39" s="3">
+        <v>113754</v>
+      </c>
+      <c r="S39" s="3">
+        <v>113366</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="U39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="W39" s="4">
+        <v>122810</v>
+      </c>
+      <c r="X39" s="10">
+        <v>125964</v>
+      </c>
+      <c r="Y39" s="10">
+        <v>129119</v>
+      </c>
+      <c r="Z39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>135429</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>136909</v>
+      </c>
+      <c r="AC39" s="11">
+        <v>136909</v>
+      </c>
+      <c r="AD39" s="11">
+        <v>132948</v>
+      </c>
+      <c r="AE39" s="3">
+        <v>132558</v>
+      </c>
+      <c r="AF39" s="3">
+        <v>142234</v>
+      </c>
+      <c r="AG39" s="3">
+        <v>142641</v>
+      </c>
+      <c r="AH39" s="3">
+        <v>145566</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1226</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1220</v>
+      </c>
+      <c r="F40" s="9">
+        <v>1214</v>
+      </c>
+      <c r="G40" s="9">
+        <v>1038</v>
+      </c>
+      <c r="H40" s="9">
+        <v>1004</v>
+      </c>
+      <c r="I40" s="9">
+        <v>1028</v>
+      </c>
+      <c r="J40" s="9">
+        <v>1032</v>
+      </c>
+      <c r="K40" s="9">
+        <v>1018</v>
+      </c>
+      <c r="L40" s="9">
+        <v>1009</v>
+      </c>
+      <c r="M40" s="9">
+        <v>998</v>
+      </c>
+      <c r="N40" s="9">
+        <v>1075</v>
+      </c>
+      <c r="O40" s="9">
+        <v>1068</v>
+      </c>
+      <c r="P40" s="2">
+        <v>1088</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>1108</v>
+      </c>
+      <c r="R40" s="3">
+        <v>1107</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1106</v>
+      </c>
+      <c r="T40" s="2">
+        <v>1035</v>
+      </c>
+      <c r="U40" s="5">
+        <v>1074</v>
+      </c>
+      <c r="V40" s="5">
+        <v>1058</v>
+      </c>
+      <c r="W40" s="4">
+        <v>1046</v>
+      </c>
+      <c r="X40" s="10">
+        <v>1061</v>
+      </c>
+      <c r="Y40" s="10">
+        <v>1076</v>
+      </c>
+      <c r="Z40" s="5">
+        <v>1114</v>
+      </c>
+      <c r="AA40" s="5">
+        <v>1097</v>
+      </c>
+      <c r="AB40" s="5">
+        <v>1098</v>
+      </c>
+      <c r="AC40" s="11">
+        <v>1098</v>
+      </c>
+      <c r="AD40" s="11">
+        <v>1110</v>
+      </c>
+      <c r="AE40" s="3">
+        <v>1111</v>
+      </c>
+      <c r="AF40" s="3">
+        <v>1248</v>
+      </c>
+      <c r="AG40" s="3">
+        <v>1266</v>
+      </c>
+      <c r="AH40" s="3">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D41" s="9">
         <v>205501</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E41" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F41" s="9">
         <v>184544</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G41" s="9">
         <v>173828</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H41" s="9">
         <v>188628</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I41" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J41" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="K41" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="L41" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="M36" s="9" t="s">
+      <c r="M41" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="N36" s="9" t="s">
+      <c r="N41" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="O36" s="9" t="s">
+      <c r="O41" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P41" s="2">
         <v>177176</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q41" s="2">
         <v>171423</v>
       </c>
-      <c r="R36" s="3">
+      <c r="R41" s="3">
         <v>172527</v>
       </c>
-      <c r="S36" s="3">
+      <c r="S41" s="3">
         <v>173740</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="U36" s="3" t="s">
+      <c r="U41" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="V36" s="3" t="s">
+      <c r="V41" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="W36" s="4">
+      <c r="W41" s="4">
         <v>207739</v>
       </c>
-      <c r="X36" s="10">
+      <c r="X41" s="10">
         <v>213357</v>
       </c>
-      <c r="Y36" s="10">
+      <c r="Y41" s="10">
         <v>218976</v>
       </c>
-      <c r="Z36" s="3" t="s">
+      <c r="Z41" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AA36" s="3">
+      <c r="AA41" s="3">
         <v>225458</v>
       </c>
-      <c r="AB36" s="3">
+      <c r="AB41" s="3">
         <v>227879</v>
       </c>
-      <c r="AC36" s="11">
+      <c r="AC41" s="11">
         <v>227879</v>
       </c>
-      <c r="AD36" s="11">
+      <c r="AD41" s="11">
         <v>242948</v>
       </c>
-      <c r="AE36" s="3">
+      <c r="AE41" s="3">
         <v>244509</v>
       </c>
-      <c r="AF36" s="3">
+      <c r="AF41" s="3">
         <v>292657</v>
       </c>
-      <c r="AG36" s="1">
+      <c r="AG41" s="3">
         <v>302625</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="AH41" s="3">
+        <v>318877</v>
+      </c>
+    </row>
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X37" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y37" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC37" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD37" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF37" s="3">
+      <c r="D42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X42" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y42" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC42" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD42" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF42" s="3">
         <v>99570</v>
       </c>
-      <c r="AG37" s="1">
+      <c r="AG42" s="3">
         <v>99469</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="AH42" s="3">
+        <v>102143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O38" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X38" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y38" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC38" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD38" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF38" s="3">
+      <c r="D43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD43" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF43" s="3">
         <v>67914</v>
       </c>
-      <c r="AG38" s="1">
+      <c r="AG43" s="3">
         <v>68080</v>
       </c>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
-      <c r="X40" s="8"/>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="X42" s="6"/>
-    </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="X46" s="6"/>
-    </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>68865</v>
+      </c>
+    </row>
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X44" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y44" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X45" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y45" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC45" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD45" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF45" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="X48" s="6"/>
-    </row>
-    <row r="49" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X49" s="6"/>
+    <row r="51" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X51" s="6"/>
+    </row>
+    <row r="52" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X52" s="6"/>
     </row>
     <row r="53" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X53" s="6"/>
     </row>
+    <row r="54" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X54" s="6"/>
+    </row>
     <row r="58" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X58" s="6"/>
     </row>
-    <row r="59" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X59" s="6"/>
-    </row>
-    <row r="60" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X60" s="6"/>
-    </row>
-    <row r="62" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X62" s="6"/>
+    <row r="63" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X63" s="6"/>
     </row>
     <row r="64" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X64" s="6"/>
@@ -4950,29 +5807,38 @@
     <row r="65" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X65" s="6"/>
     </row>
-    <row r="66" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X66" s="6"/>
-    </row>
     <row r="67" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X67" s="6"/>
     </row>
-    <row r="68" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X68" s="6"/>
-    </row>
     <row r="69" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X69" s="6"/>
     </row>
+    <row r="70" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X70" s="6"/>
+    </row>
     <row r="71" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X71" s="6"/>
     </row>
     <row r="72" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X72" s="6"/>
     </row>
+    <row r="73" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X73" s="6"/>
+    </row>
     <row r="74" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X74" s="6"/>
     </row>
+    <row r="76" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X76" s="6"/>
+    </row>
+    <row r="77" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X77" s="6"/>
+    </row>
+    <row r="79" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X79" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O36" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}"/>
+  <autoFilter ref="A1:O43" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7284D4A2-48D9-CF40-8E94-8CA1451F71FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CFC4CE-1689-774F-B97A-C66563FE527A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="194">
   <si>
     <t>Category</t>
   </si>
@@ -618,6 +618,9 @@
   </si>
   <si>
     <t>Aug26 W2</t>
+  </si>
+  <si>
+    <t>Aug26 W3</t>
   </si>
 </sst>
 </file>
@@ -628,7 +631,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -665,6 +668,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -704,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -744,6 +753,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1079,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AH79"/>
+  <dimension ref="A1:AI79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1100,7 +1110,7 @@
     <col min="34" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1203,8 +1213,11 @@
       <c r="AH1" s="13" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI1" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1307,8 +1320,11 @@
       <c r="AH2" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI2" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -1411,8 +1427,11 @@
       <c r="AH3" s="3">
         <v>22063</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI3" s="17">
+        <v>24034</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1515,8 +1534,11 @@
       <c r="AH4" s="3">
         <v>442</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI4" s="17">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1619,8 +1641,11 @@
       <c r="AH5" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI5" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1723,8 +1748,11 @@
       <c r="AH6" s="3">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI6" s="17">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1827,8 +1855,11 @@
       <c r="AH7" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1931,8 +1962,11 @@
       <c r="AH8" s="3">
         <v>187220</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="17">
+        <v>216944</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -2035,8 +2069,11 @@
       <c r="AH9" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -2139,8 +2176,11 @@
       <c r="AH10" s="3">
         <v>514</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="17">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -2243,8 +2283,11 @@
       <c r="AH11" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -2347,8 +2390,11 @@
       <c r="AH12" s="3">
         <v>52216</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="17">
+        <v>52627</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -2451,8 +2497,11 @@
       <c r="AH13" s="3">
         <v>2896</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="17">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2555,8 +2604,11 @@
       <c r="AH14" s="3">
         <v>13516</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="17">
+        <v>14167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -2659,8 +2711,11 @@
       <c r="AH15" s="3">
         <v>96944</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="17">
+        <v>101304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2763,8 +2818,11 @@
       <c r="AH16" s="3">
         <v>278364</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="17">
+        <v>286294</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2867,8 +2925,11 @@
       <c r="AH17" s="3">
         <v>183441</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="17">
+        <v>185831</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2971,8 +3032,11 @@
       <c r="AH18" s="3">
         <v>178126</v>
       </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="17">
+        <v>183055</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -3075,8 +3139,11 @@
       <c r="AH19" s="3">
         <v>101544</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="17">
+        <v>105101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -3179,8 +3246,11 @@
       <c r="AH20" s="3">
         <v>419403</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="17">
+        <v>471796</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
@@ -3283,8 +3353,11 @@
       <c r="AH21" s="3">
         <v>204372</v>
       </c>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="17">
+        <v>235028</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
@@ -3387,8 +3460,11 @@
       <c r="AH22" s="3">
         <v>1034911</v>
       </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="17">
+        <v>1090367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
@@ -3491,8 +3567,11 @@
       <c r="AH23" s="3">
         <v>916118</v>
       </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="17">
+        <v>962188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -3595,8 +3674,11 @@
       <c r="AH24" s="3">
         <v>8949</v>
       </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="17">
+        <v>8989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,8 +3781,11 @@
       <c r="AH25" s="3">
         <v>1415</v>
       </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="17">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -3803,8 +3888,11 @@
       <c r="AH26" s="3">
         <v>2255</v>
       </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="17">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -3907,8 +3995,11 @@
       <c r="AH27" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -4011,8 +4102,11 @@
       <c r="AH28" s="3">
         <v>22063</v>
       </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="17">
+        <v>24034</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -4115,8 +4209,11 @@
       <c r="AH29" s="3">
         <v>217</v>
       </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="17">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -4219,8 +4316,11 @@
       <c r="AH30" s="3">
         <v>6135</v>
       </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="17">
+        <v>6328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -4323,8 +4423,11 @@
       <c r="AH31" s="3">
         <v>18731</v>
       </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="17">
+        <v>19018</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -4427,8 +4530,11 @@
       <c r="AH32" s="3">
         <v>120275</v>
       </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="17">
+        <v>126055</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -4531,8 +4637,11 @@
       <c r="AH33" s="3">
         <v>9077</v>
       </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="17">
+        <v>9469</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -4635,8 +4744,11 @@
       <c r="AH34" s="3">
         <v>1172</v>
       </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="17">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -4739,8 +4851,11 @@
       <c r="AH35" s="3">
         <v>70950</v>
       </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="17">
+        <v>70308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -4843,8 +4958,11 @@
       <c r="AH36" s="3">
         <v>298329</v>
       </c>
-    </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI36" s="17">
+        <v>303898</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>82</v>
       </c>
@@ -4947,8 +5065,11 @@
       <c r="AH37" s="3">
         <v>47308</v>
       </c>
-    </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI37" s="17">
+        <v>48011</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>
@@ -5051,8 +5172,11 @@
       <c r="AH38" s="3">
         <v>2702</v>
       </c>
-    </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="17">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>82</v>
       </c>
@@ -5155,8 +5279,11 @@
       <c r="AH39" s="3">
         <v>145566</v>
       </c>
-    </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="17">
+        <v>144885</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>82</v>
       </c>
@@ -5259,8 +5386,11 @@
       <c r="AH40" s="3">
         <v>1327</v>
       </c>
-    </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="17">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -5363,8 +5493,11 @@
       <c r="AH41" s="3">
         <v>318877</v>
       </c>
-    </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="17">
+        <v>331208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>181</v>
       </c>
@@ -5467,8 +5600,11 @@
       <c r="AH42" s="3">
         <v>102143</v>
       </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="17">
+        <v>105567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>181</v>
       </c>
@@ -5571,8 +5707,11 @@
       <c r="AH43" s="3">
         <v>68865</v>
       </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="17">
+        <v>69733</v>
+      </c>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>181</v>
       </c>
@@ -5675,8 +5814,11 @@
       <c r="AH44" s="3">
         <v>229</v>
       </c>
-    </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="17">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>181</v>
       </c>
@@ -5779,8 +5921,11 @@
       <c r="AH45" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
       <c r="X47" s="6"/>
     </row>
     <row r="51" spans="24:24" x14ac:dyDescent="0.2">

--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CFC4CE-1689-774F-B97A-C66563FE527A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C18CAA-8015-5C46-A027-3B6B31D7252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="196">
   <si>
     <t>Category</t>
   </si>
@@ -302,9 +302,6 @@
     <t>desi popz tangy imli</t>
   </si>
   <si>
-    <t>go desi</t>
-  </si>
-  <si>
     <t>go desi pop</t>
   </si>
   <si>
@@ -621,6 +618,15 @@
   </si>
   <si>
     <t>Aug26 W3</t>
+  </si>
+  <si>
+    <t>GO DESi Candies/POPz Branded Keywords</t>
+  </si>
+  <si>
+    <t>GO DESi Sweets Branded Keywords</t>
+  </si>
+  <si>
+    <t>GO DESi Snacks Branded Keywords</t>
   </si>
 </sst>
 </file>
@@ -713,7 +719,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -740,20 +746,15 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1089,12 +1090,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}">
-  <dimension ref="A1:AI79"/>
+  <dimension ref="A1:AI77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -1120,101 +1121,101 @@
       <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="U1" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="X1" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="S1" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="U1" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="V1" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="X1" s="13" t="s">
+      <c r="Y1" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Z1" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="Z1" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB1" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AD1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AE1" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="AE1" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF1" s="13" t="s">
+      <c r="AF1" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG1" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="AG1" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AH1" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="AI1" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="AI1" s="13" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.2">
@@ -1227,100 +1228,100 @@
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI2" s="17">
+      <c r="D2" s="15">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0</v>
+      </c>
+      <c r="K2" s="15">
+        <v>0</v>
+      </c>
+      <c r="L2" s="15">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15">
+        <v>0</v>
+      </c>
+      <c r="N2" s="15">
+        <v>0</v>
+      </c>
+      <c r="O2" s="15">
+        <v>0</v>
+      </c>
+      <c r="P2" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="15">
+        <v>0</v>
+      </c>
+      <c r="R2" s="15">
+        <v>0</v>
+      </c>
+      <c r="S2" s="15">
+        <v>0</v>
+      </c>
+      <c r="T2" s="15">
+        <v>0</v>
+      </c>
+      <c r="U2" s="15">
+        <v>0</v>
+      </c>
+      <c r="V2" s="15">
+        <v>0</v>
+      </c>
+      <c r="W2" s="15">
+        <v>0</v>
+      </c>
+      <c r="X2" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="15">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="15">
         <v>0</v>
       </c>
     </row>
@@ -1332,103 +1333,103 @@
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="9">
-        <v>15665</v>
+        <v>227</v>
       </c>
       <c r="E3" s="9">
-        <v>18368</v>
+        <v>267</v>
       </c>
       <c r="F3" s="9">
-        <v>21537</v>
+        <v>314</v>
       </c>
       <c r="G3" s="9">
-        <v>20433</v>
+        <v>302</v>
       </c>
       <c r="H3" s="9">
-        <v>19944</v>
+        <v>309</v>
       </c>
       <c r="I3" s="9">
-        <v>19145</v>
+        <v>319</v>
       </c>
       <c r="J3" s="9">
-        <v>19872</v>
+        <v>323</v>
       </c>
       <c r="K3" s="9">
-        <v>20641</v>
+        <v>331</v>
       </c>
       <c r="L3" s="9">
-        <v>21287</v>
+        <v>339</v>
       </c>
       <c r="M3" s="9">
-        <v>23518</v>
+        <v>358</v>
       </c>
       <c r="N3" s="9">
-        <v>26771</v>
+        <v>398</v>
       </c>
       <c r="O3" s="9">
-        <v>28509</v>
+        <v>408</v>
       </c>
       <c r="P3" s="2">
-        <v>30834</v>
+        <v>430</v>
       </c>
       <c r="Q3" s="2">
-        <v>33159</v>
+        <v>452</v>
       </c>
       <c r="R3" s="3">
-        <v>30941</v>
+        <v>427</v>
       </c>
       <c r="S3" s="3">
-        <v>25786</v>
+        <v>403</v>
       </c>
       <c r="T3" s="2">
-        <v>21006</v>
-      </c>
-      <c r="U3" s="5">
-        <v>23487</v>
-      </c>
-      <c r="V3" s="5">
-        <v>22116</v>
+        <v>270</v>
+      </c>
+      <c r="U3" s="3">
+        <v>291</v>
+      </c>
+      <c r="V3" s="3">
+        <v>274</v>
       </c>
       <c r="W3" s="4">
-        <v>19589</v>
+        <v>237</v>
       </c>
       <c r="X3" s="10">
-        <v>19584</v>
+        <v>253</v>
       </c>
       <c r="Y3" s="10">
-        <v>19580</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>20511</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>19597</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>19386</v>
+        <v>268</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>337</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>306</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>306</v>
       </c>
       <c r="AC3" s="11">
-        <v>19386</v>
+        <v>306</v>
       </c>
       <c r="AD3" s="11">
-        <v>18054</v>
+        <v>283</v>
       </c>
       <c r="AE3" s="3">
-        <v>17926</v>
+        <v>281</v>
       </c>
       <c r="AF3" s="3">
-        <v>20489</v>
+        <v>372</v>
       </c>
       <c r="AG3" s="3">
-        <v>21008</v>
+        <v>394</v>
       </c>
       <c r="AH3" s="3">
-        <v>22063</v>
-      </c>
-      <c r="AI3" s="17">
-        <v>24034</v>
+        <v>442</v>
+      </c>
+      <c r="AI3" s="15">
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.2">
@@ -1439,103 +1440,103 @@
         <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="9">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="F4" s="9">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="G4" s="9">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="H4" s="9">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="I4" s="9">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="J4" s="9">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="K4" s="9">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="L4" s="9">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="M4" s="9">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="N4" s="9">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="O4" s="9">
-        <v>408</v>
-      </c>
-      <c r="P4" s="2">
-        <v>430</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>452</v>
-      </c>
-      <c r="R4" s="3">
-        <v>427</v>
-      </c>
-      <c r="S4" s="3">
-        <v>403</v>
-      </c>
-      <c r="T4" s="2">
-        <v>270</v>
-      </c>
-      <c r="U4" s="3">
-        <v>291</v>
-      </c>
-      <c r="V4" s="3">
-        <v>274</v>
-      </c>
-      <c r="W4" s="4">
-        <v>237</v>
-      </c>
-      <c r="X4" s="10">
-        <v>253</v>
-      </c>
-      <c r="Y4" s="10">
-        <v>268</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>337</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>306</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>306</v>
-      </c>
-      <c r="AC4" s="11">
-        <v>306</v>
-      </c>
-      <c r="AD4" s="11">
-        <v>283</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>281</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>372</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>394</v>
-      </c>
-      <c r="AH4" s="3">
-        <v>442</v>
-      </c>
-      <c r="AI4" s="17">
-        <v>510</v>
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9">
+        <v>0</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0</v>
+      </c>
+      <c r="U4" s="9">
+        <v>0</v>
+      </c>
+      <c r="V4" s="9">
+        <v>0</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.2">
@@ -1546,103 +1547,103 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI5" s="17">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="D5" s="9">
+        <v>106</v>
+      </c>
+      <c r="E5" s="9">
+        <v>106</v>
+      </c>
+      <c r="F5" s="9">
+        <v>106</v>
+      </c>
+      <c r="G5" s="9">
+        <v>106</v>
+      </c>
+      <c r="H5" s="9">
+        <v>106</v>
+      </c>
+      <c r="I5" s="9">
+        <v>106</v>
+      </c>
+      <c r="J5" s="9">
+        <v>106</v>
+      </c>
+      <c r="K5" s="9">
+        <v>106</v>
+      </c>
+      <c r="L5" s="9">
+        <v>106</v>
+      </c>
+      <c r="M5" s="9">
+        <v>106</v>
+      </c>
+      <c r="N5" s="9">
+        <v>106</v>
+      </c>
+      <c r="O5" s="9">
+        <v>106</v>
+      </c>
+      <c r="P5" s="2">
+        <v>106</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>106</v>
+      </c>
+      <c r="R5" s="3">
+        <v>106</v>
+      </c>
+      <c r="S5" s="3">
+        <v>106</v>
+      </c>
+      <c r="T5" s="2">
+        <v>106</v>
+      </c>
+      <c r="U5" s="3">
+        <v>106</v>
+      </c>
+      <c r="V5" s="3">
+        <v>106</v>
+      </c>
+      <c r="W5" s="4">
+        <v>106</v>
+      </c>
+      <c r="X5" s="10">
+        <v>106</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>106</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AC5" s="11">
+        <v>106</v>
+      </c>
+      <c r="AD5" s="11">
+        <v>106</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>106</v>
+      </c>
+      <c r="AI5" s="15">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.2">
@@ -1653,103 +1654,103 @@
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="D6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="I6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="L6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N6" s="9">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O6" s="9">
-        <v>106</v>
-      </c>
-      <c r="P6" s="2">
-        <v>106</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>106</v>
-      </c>
-      <c r="R6" s="3">
-        <v>106</v>
-      </c>
-      <c r="S6" s="3">
-        <v>106</v>
-      </c>
-      <c r="T6" s="2">
-        <v>106</v>
-      </c>
-      <c r="U6" s="3">
-        <v>106</v>
-      </c>
-      <c r="V6" s="3">
-        <v>106</v>
-      </c>
-      <c r="W6" s="4">
-        <v>106</v>
-      </c>
-      <c r="X6" s="10">
-        <v>106</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>106</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AC6" s="11">
-        <v>106</v>
-      </c>
-      <c r="AD6" s="11">
-        <v>106</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AH6" s="3">
-        <v>106</v>
-      </c>
-      <c r="AI6" s="17">
-        <v>106</v>
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9">
+        <v>0</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -1760,103 +1761,103 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI7" s="17">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9">
+        <v>0</v>
+      </c>
+      <c r="T7" s="9">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>187220</v>
+      </c>
+      <c r="AI7" s="15">
+        <v>216944</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -1866,104 +1867,104 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>187220</v>
-      </c>
-      <c r="AI8" s="17">
-        <v>216944</v>
+      <c r="C8" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
@@ -1973,104 +1974,104 @@
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI9" s="17">
-        <v>0</v>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9">
+        <v>0</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>514</v>
+      </c>
+      <c r="AI9" s="15">
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.2">
@@ -2083,101 +2084,101 @@
       <c r="C10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X10" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y10" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>514</v>
-      </c>
-      <c r="AI10" s="17">
-        <v>559</v>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9">
+        <v>0</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.2">
@@ -2185,106 +2186,106 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD11" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF11" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI11" s="17">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="D11" s="9">
+        <v>35550</v>
+      </c>
+      <c r="E11" s="9">
+        <v>36638</v>
+      </c>
+      <c r="F11" s="9">
+        <v>37759</v>
+      </c>
+      <c r="G11" s="9">
+        <v>38048</v>
+      </c>
+      <c r="H11" s="9">
+        <v>39236</v>
+      </c>
+      <c r="I11" s="9">
+        <v>40115</v>
+      </c>
+      <c r="J11" s="9">
+        <v>41183</v>
+      </c>
+      <c r="K11" s="9">
+        <v>42067</v>
+      </c>
+      <c r="L11" s="9">
+        <v>43149</v>
+      </c>
+      <c r="M11" s="9">
+        <v>43872</v>
+      </c>
+      <c r="N11" s="9">
+        <v>44083</v>
+      </c>
+      <c r="O11" s="9">
+        <v>44891</v>
+      </c>
+      <c r="P11" s="2">
+        <v>45486</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>46081</v>
+      </c>
+      <c r="R11" s="3">
+        <v>46355</v>
+      </c>
+      <c r="S11" s="3">
+        <v>48497</v>
+      </c>
+      <c r="T11" s="2">
+        <v>46334</v>
+      </c>
+      <c r="U11" s="5">
+        <v>47012</v>
+      </c>
+      <c r="V11" s="5">
+        <v>48206</v>
+      </c>
+      <c r="W11" s="4">
+        <v>47748</v>
+      </c>
+      <c r="X11" s="10">
+        <v>48609</v>
+      </c>
+      <c r="Y11" s="10">
+        <v>49470</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>51110</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>50804</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>51139</v>
+      </c>
+      <c r="AC11" s="11">
+        <v>51139</v>
+      </c>
+      <c r="AD11" s="11">
+        <v>49782</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>49648</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>50940</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>50981</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>52216</v>
+      </c>
+      <c r="AI11" s="15">
+        <v>52627</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.2">
@@ -2295,103 +2296,103 @@
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" s="9">
-        <v>35550</v>
+        <v>1858</v>
       </c>
       <c r="E12" s="9">
-        <v>36638</v>
+        <v>1820</v>
       </c>
       <c r="F12" s="9">
-        <v>37759</v>
+        <v>1783</v>
       </c>
       <c r="G12" s="9">
-        <v>38048</v>
+        <v>1789</v>
       </c>
       <c r="H12" s="9">
-        <v>39236</v>
+        <v>1725</v>
       </c>
       <c r="I12" s="9">
-        <v>40115</v>
+        <v>2427</v>
       </c>
       <c r="J12" s="9">
-        <v>41183</v>
+        <v>2463</v>
       </c>
       <c r="K12" s="9">
-        <v>42067</v>
+        <v>2517</v>
       </c>
       <c r="L12" s="9">
-        <v>43149</v>
+        <v>2604</v>
       </c>
       <c r="M12" s="9">
-        <v>43872</v>
+        <v>2748</v>
       </c>
       <c r="N12" s="9">
-        <v>44083</v>
+        <v>2883</v>
       </c>
       <c r="O12" s="9">
-        <v>44891</v>
+        <v>2960</v>
       </c>
       <c r="P12" s="2">
-        <v>45486</v>
+        <v>3068</v>
       </c>
       <c r="Q12" s="2">
-        <v>46081</v>
+        <v>3176</v>
       </c>
       <c r="R12" s="3">
-        <v>46355</v>
+        <v>3228</v>
       </c>
       <c r="S12" s="3">
-        <v>48497</v>
+        <v>3413</v>
       </c>
       <c r="T12" s="2">
-        <v>46334</v>
+        <v>3198</v>
       </c>
       <c r="U12" s="5">
-        <v>47012</v>
+        <v>3104</v>
       </c>
       <c r="V12" s="5">
-        <v>48206</v>
+        <v>3157</v>
       </c>
       <c r="W12" s="4">
-        <v>47748</v>
+        <v>3148</v>
       </c>
       <c r="X12" s="10">
-        <v>48609</v>
+        <v>3123</v>
       </c>
       <c r="Y12" s="10">
-        <v>49470</v>
+        <v>3098</v>
       </c>
       <c r="Z12" s="5">
-        <v>51110</v>
+        <v>3057</v>
       </c>
       <c r="AA12" s="5">
-        <v>50804</v>
+        <v>3064</v>
       </c>
       <c r="AB12" s="5">
-        <v>51139</v>
+        <v>3054</v>
       </c>
       <c r="AC12" s="11">
-        <v>51139</v>
+        <v>3054</v>
       </c>
       <c r="AD12" s="11">
-        <v>49782</v>
+        <v>2883</v>
       </c>
       <c r="AE12" s="3">
-        <v>49648</v>
+        <v>2866</v>
       </c>
       <c r="AF12" s="3">
-        <v>50940</v>
+        <v>2953</v>
       </c>
       <c r="AG12" s="3">
-        <v>50981</v>
+        <v>2932</v>
       </c>
       <c r="AH12" s="3">
-        <v>52216</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>52627</v>
+        <v>2896</v>
+      </c>
+      <c r="AI12" s="15">
+        <v>2940</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
@@ -2402,103 +2403,103 @@
         <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="9">
-        <v>1858</v>
+        <v>5864</v>
       </c>
       <c r="E13" s="9">
-        <v>1820</v>
+        <v>6486</v>
       </c>
       <c r="F13" s="9">
-        <v>1783</v>
+        <v>7174</v>
       </c>
       <c r="G13" s="9">
-        <v>1789</v>
+        <v>7150</v>
       </c>
       <c r="H13" s="9">
-        <v>1725</v>
+        <v>7723</v>
       </c>
       <c r="I13" s="9">
-        <v>2427</v>
+        <v>7920</v>
       </c>
       <c r="J13" s="9">
-        <v>2463</v>
+        <v>8118</v>
       </c>
       <c r="K13" s="9">
-        <v>2517</v>
+        <v>8397</v>
       </c>
       <c r="L13" s="9">
-        <v>2604</v>
+        <v>8713</v>
       </c>
       <c r="M13" s="9">
-        <v>2748</v>
+        <v>9026</v>
       </c>
       <c r="N13" s="9">
-        <v>2883</v>
+        <v>9043</v>
       </c>
       <c r="O13" s="9">
-        <v>2960</v>
+        <v>9368</v>
       </c>
       <c r="P13" s="2">
-        <v>3068</v>
+        <v>9588</v>
       </c>
       <c r="Q13" s="2">
-        <v>3176</v>
+        <v>9808</v>
       </c>
       <c r="R13" s="3">
-        <v>3228</v>
+        <v>9862</v>
       </c>
       <c r="S13" s="3">
-        <v>3413</v>
+        <v>10315</v>
       </c>
       <c r="T13" s="2">
-        <v>3198</v>
+        <v>9679</v>
       </c>
       <c r="U13" s="5">
-        <v>3104</v>
+        <v>9112</v>
       </c>
       <c r="V13" s="5">
-        <v>3157</v>
+        <v>9305</v>
       </c>
       <c r="W13" s="4">
-        <v>3148</v>
+        <v>9230</v>
       </c>
       <c r="X13" s="10">
-        <v>3123</v>
+        <v>9178</v>
       </c>
       <c r="Y13" s="10">
-        <v>3098</v>
+        <v>9125</v>
       </c>
       <c r="Z13" s="5">
-        <v>3057</v>
+        <v>9268</v>
       </c>
       <c r="AA13" s="5">
-        <v>3064</v>
+        <v>9229</v>
       </c>
       <c r="AB13" s="5">
-        <v>3054</v>
+        <v>9230</v>
       </c>
       <c r="AC13" s="11">
-        <v>3054</v>
+        <v>9230</v>
       </c>
       <c r="AD13" s="11">
-        <v>2883</v>
+        <v>11738</v>
       </c>
       <c r="AE13" s="3">
-        <v>2866</v>
+        <v>12024</v>
       </c>
       <c r="AF13" s="3">
-        <v>2953</v>
+        <v>13652</v>
       </c>
       <c r="AG13" s="3">
-        <v>2932</v>
+        <v>13660</v>
       </c>
       <c r="AH13" s="3">
-        <v>2896</v>
-      </c>
-      <c r="AI13" s="17">
-        <v>2940</v>
+        <v>13516</v>
+      </c>
+      <c r="AI13" s="15">
+        <v>14167</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.2">
@@ -2509,103 +2510,103 @@
         <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="9">
-        <v>5864</v>
+        <v>71964</v>
       </c>
       <c r="E14" s="9">
-        <v>6486</v>
+        <v>70213</v>
       </c>
       <c r="F14" s="9">
-        <v>7174</v>
+        <v>68505</v>
       </c>
       <c r="G14" s="9">
-        <v>7150</v>
+        <v>73263</v>
       </c>
       <c r="H14" s="9">
-        <v>7723</v>
+        <v>74778</v>
       </c>
       <c r="I14" s="9">
-        <v>7920</v>
+        <v>78638</v>
       </c>
       <c r="J14" s="9">
-        <v>8118</v>
+        <v>79842</v>
       </c>
       <c r="K14" s="9">
-        <v>8397</v>
+        <v>81536</v>
       </c>
       <c r="L14" s="9">
-        <v>8713</v>
+        <v>83127</v>
       </c>
       <c r="M14" s="9">
-        <v>9026</v>
+        <v>84418</v>
       </c>
       <c r="N14" s="9">
-        <v>9043</v>
+        <v>84623</v>
       </c>
       <c r="O14" s="9">
-        <v>9368</v>
+        <v>82556</v>
       </c>
       <c r="P14" s="2">
-        <v>9588</v>
+        <v>81806</v>
       </c>
       <c r="Q14" s="2">
-        <v>9808</v>
+        <v>81056</v>
       </c>
       <c r="R14" s="3">
-        <v>9862</v>
+        <v>81236</v>
       </c>
       <c r="S14" s="3">
-        <v>10315</v>
+        <v>84677</v>
       </c>
       <c r="T14" s="2">
-        <v>9679</v>
+        <v>83638</v>
       </c>
       <c r="U14" s="5">
-        <v>9112</v>
+        <v>79884</v>
       </c>
       <c r="V14" s="5">
-        <v>9305</v>
+        <v>81093</v>
       </c>
       <c r="W14" s="4">
-        <v>9230</v>
+        <v>81479</v>
       </c>
       <c r="X14" s="10">
-        <v>9178</v>
+        <v>80893</v>
       </c>
       <c r="Y14" s="10">
-        <v>9125</v>
+        <v>80306</v>
       </c>
       <c r="Z14" s="5">
-        <v>9268</v>
+        <v>79986</v>
       </c>
       <c r="AA14" s="5">
-        <v>9229</v>
+        <v>79958</v>
       </c>
       <c r="AB14" s="5">
-        <v>9230</v>
+        <v>79806</v>
       </c>
       <c r="AC14" s="11">
-        <v>9230</v>
+        <v>79806</v>
       </c>
       <c r="AD14" s="11">
-        <v>11738</v>
+        <v>84843</v>
       </c>
       <c r="AE14" s="3">
-        <v>12024</v>
+        <v>85364</v>
       </c>
       <c r="AF14" s="3">
-        <v>13652</v>
+        <v>92830</v>
       </c>
       <c r="AG14" s="3">
-        <v>13660</v>
+        <v>93670</v>
       </c>
       <c r="AH14" s="3">
-        <v>13516</v>
-      </c>
-      <c r="AI14" s="17">
-        <v>14167</v>
+        <v>96944</v>
+      </c>
+      <c r="AI14" s="15">
+        <v>101304</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.2">
@@ -2616,103 +2617,103 @@
         <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15" s="9">
-        <v>71964</v>
+        <v>232749</v>
       </c>
       <c r="E15" s="9">
-        <v>70213</v>
+        <v>242993</v>
       </c>
       <c r="F15" s="9">
-        <v>68505</v>
+        <v>253688</v>
       </c>
       <c r="G15" s="9">
-        <v>73263</v>
+        <v>229817</v>
       </c>
       <c r="H15" s="9">
-        <v>74778</v>
-      </c>
-      <c r="I15" s="9">
-        <v>78638</v>
-      </c>
-      <c r="J15" s="9">
-        <v>79842</v>
-      </c>
-      <c r="K15" s="9">
-        <v>81536</v>
-      </c>
-      <c r="L15" s="9">
-        <v>83127</v>
-      </c>
-      <c r="M15" s="9">
-        <v>84418</v>
-      </c>
-      <c r="N15" s="9">
-        <v>84623</v>
-      </c>
-      <c r="O15" s="9">
-        <v>82556</v>
+        <v>232951</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="P15" s="2">
-        <v>81806</v>
+        <v>295402</v>
       </c>
       <c r="Q15" s="2">
-        <v>81056</v>
+        <v>306716</v>
       </c>
       <c r="R15" s="3">
-        <v>81236</v>
+        <v>294711</v>
       </c>
       <c r="S15" s="3">
-        <v>84677</v>
-      </c>
-      <c r="T15" s="2">
-        <v>83638</v>
-      </c>
-      <c r="U15" s="5">
-        <v>79884</v>
-      </c>
-      <c r="V15" s="5">
-        <v>81093</v>
+        <v>294331</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="W15" s="4">
-        <v>81479</v>
+        <v>190412</v>
       </c>
       <c r="X15" s="10">
-        <v>80893</v>
+        <v>198533</v>
       </c>
       <c r="Y15" s="10">
-        <v>80306</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>79986</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>79958</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>79806</v>
+        <v>206655</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>229539</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>229619</v>
       </c>
       <c r="AC15" s="11">
-        <v>79806</v>
+        <v>229619</v>
       </c>
       <c r="AD15" s="11">
-        <v>84843</v>
+        <v>238024</v>
       </c>
       <c r="AE15" s="3">
-        <v>85364</v>
+        <v>238881</v>
       </c>
       <c r="AF15" s="3">
-        <v>92830</v>
+        <v>260076</v>
       </c>
       <c r="AG15" s="3">
-        <v>93670</v>
+        <v>261335</v>
       </c>
       <c r="AH15" s="3">
-        <v>96944</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>101304</v>
+        <v>278364</v>
+      </c>
+      <c r="AI15" s="15">
+        <v>286294</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.2">
@@ -2723,55 +2724,55 @@
         <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D16" s="9">
-        <v>232749</v>
+        <v>75862</v>
       </c>
       <c r="E16" s="9">
-        <v>242993</v>
+        <v>63740</v>
       </c>
       <c r="F16" s="9">
-        <v>253688</v>
+        <v>53555</v>
       </c>
       <c r="G16" s="9">
-        <v>229817</v>
+        <v>68500</v>
       </c>
       <c r="H16" s="9">
-        <v>232951</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>32</v>
+        <v>98599</v>
+      </c>
+      <c r="I16" s="9">
+        <v>79484</v>
+      </c>
+      <c r="J16" s="9">
+        <v>81327</v>
+      </c>
+      <c r="K16" s="9">
+        <v>84612</v>
+      </c>
+      <c r="L16" s="9">
+        <v>88943</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P16" s="2">
-        <v>295402</v>
+        <v>200858</v>
       </c>
       <c r="Q16" s="2">
-        <v>306716</v>
+        <v>229496</v>
       </c>
       <c r="R16" s="3">
-        <v>294711</v>
+        <v>241671</v>
       </c>
       <c r="S16" s="3">
-        <v>294331</v>
+        <v>269912</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>129</v>
@@ -2783,43 +2784,43 @@
         <v>141</v>
       </c>
       <c r="W16" s="4">
-        <v>190412</v>
+        <v>168639</v>
       </c>
       <c r="X16" s="10">
-        <v>198533</v>
+        <v>171404</v>
       </c>
       <c r="Y16" s="10">
-        <v>206655</v>
+        <v>174170</v>
       </c>
       <c r="Z16" s="3" t="s">
         <v>166</v>
       </c>
       <c r="AA16" s="3">
-        <v>229539</v>
+        <v>179991</v>
       </c>
       <c r="AB16" s="3">
-        <v>229619</v>
+        <v>179909</v>
       </c>
       <c r="AC16" s="11">
-        <v>229619</v>
+        <v>179909</v>
       </c>
       <c r="AD16" s="11">
-        <v>238024</v>
+        <v>173515</v>
       </c>
       <c r="AE16" s="3">
-        <v>238881</v>
+        <v>172888</v>
       </c>
       <c r="AF16" s="3">
-        <v>260076</v>
+        <v>179901</v>
       </c>
       <c r="AG16" s="3">
-        <v>261335</v>
+        <v>179178</v>
       </c>
       <c r="AH16" s="3">
-        <v>278364</v>
-      </c>
-      <c r="AI16" s="17">
-        <v>286294</v>
+        <v>183441</v>
+      </c>
+      <c r="AI16" s="15">
+        <v>185831</v>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.2">
@@ -2830,55 +2831,55 @@
         <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D17" s="9">
-        <v>75862</v>
+        <v>120329</v>
       </c>
       <c r="E17" s="9">
-        <v>63740</v>
+        <v>127681</v>
       </c>
       <c r="F17" s="9">
-        <v>53555</v>
+        <v>135482</v>
       </c>
       <c r="G17" s="9">
-        <v>68500</v>
+        <v>131019</v>
       </c>
       <c r="H17" s="9">
-        <v>98599</v>
-      </c>
-      <c r="I17" s="9">
-        <v>79484</v>
-      </c>
-      <c r="J17" s="9">
-        <v>81327</v>
-      </c>
-      <c r="K17" s="9">
-        <v>84612</v>
-      </c>
-      <c r="L17" s="9">
-        <v>88943</v>
+        <v>132408</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P17" s="2">
-        <v>200858</v>
+        <v>154289</v>
       </c>
       <c r="Q17" s="2">
-        <v>229496</v>
+        <v>157676</v>
       </c>
       <c r="R17" s="3">
-        <v>241671</v>
+        <v>157087</v>
       </c>
       <c r="S17" s="3">
-        <v>269912</v>
+        <v>162791</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>130</v>
@@ -2890,43 +2891,43 @@
         <v>142</v>
       </c>
       <c r="W17" s="4">
-        <v>168639</v>
+        <v>146511</v>
       </c>
       <c r="X17" s="10">
-        <v>171404</v>
+        <v>148663</v>
       </c>
       <c r="Y17" s="10">
-        <v>174170</v>
+        <v>150815</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>167</v>
       </c>
       <c r="AA17" s="3">
-        <v>179991</v>
+        <v>155085</v>
       </c>
       <c r="AB17" s="3">
-        <v>179909</v>
+        <v>155321</v>
       </c>
       <c r="AC17" s="11">
-        <v>179909</v>
+        <v>155321</v>
       </c>
       <c r="AD17" s="11">
-        <v>173515</v>
+        <v>162351</v>
       </c>
       <c r="AE17" s="3">
-        <v>172888</v>
+        <v>163071</v>
       </c>
       <c r="AF17" s="3">
-        <v>179901</v>
+        <v>171760</v>
       </c>
       <c r="AG17" s="3">
-        <v>179178</v>
+        <v>172153</v>
       </c>
       <c r="AH17" s="3">
-        <v>183441</v>
-      </c>
-      <c r="AI17" s="17">
-        <v>185831</v>
+        <v>178126</v>
+      </c>
+      <c r="AI17" s="15">
+        <v>183055</v>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.2">
@@ -2937,103 +2938,103 @@
         <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D18" s="9">
-        <v>120329</v>
+        <v>33458</v>
       </c>
       <c r="E18" s="9">
-        <v>127681</v>
+        <v>28690</v>
       </c>
       <c r="F18" s="9">
-        <v>135482</v>
+        <v>24601</v>
       </c>
       <c r="G18" s="9">
-        <v>131019</v>
+        <v>30975</v>
       </c>
       <c r="H18" s="9">
-        <v>132408</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O18" s="9" t="s">
-        <v>47</v>
+        <v>33624</v>
+      </c>
+      <c r="I18" s="9">
+        <v>36455</v>
+      </c>
+      <c r="J18" s="9">
+        <v>37648</v>
+      </c>
+      <c r="K18" s="9">
+        <v>39982</v>
+      </c>
+      <c r="L18" s="9">
+        <v>42731</v>
+      </c>
+      <c r="M18" s="9">
+        <v>50184</v>
+      </c>
+      <c r="N18" s="9">
+        <v>57210</v>
+      </c>
+      <c r="O18" s="9">
+        <v>65597</v>
       </c>
       <c r="P18" s="2">
-        <v>154289</v>
+        <v>73375</v>
       </c>
       <c r="Q18" s="2">
-        <v>157676</v>
+        <v>81153</v>
       </c>
       <c r="R18" s="3">
-        <v>157087</v>
+        <v>84292</v>
       </c>
       <c r="S18" s="3">
-        <v>162791</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>143</v>
+        <v>91544</v>
+      </c>
+      <c r="T18" s="2">
+        <v>74927</v>
+      </c>
+      <c r="U18" s="5">
+        <v>73982</v>
+      </c>
+      <c r="V18" s="5">
+        <v>76417</v>
       </c>
       <c r="W18" s="4">
-        <v>146511</v>
+        <v>74001</v>
       </c>
       <c r="X18" s="10">
-        <v>148663</v>
+        <v>76698</v>
       </c>
       <c r="Y18" s="10">
-        <v>150815</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>155085</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>155321</v>
+        <v>79396</v>
+      </c>
+      <c r="Z18" s="5">
+        <v>88105</v>
+      </c>
+      <c r="AA18" s="5">
+        <v>85353</v>
+      </c>
+      <c r="AB18" s="5">
+        <v>86391</v>
       </c>
       <c r="AC18" s="11">
-        <v>155321</v>
+        <v>86391</v>
       </c>
       <c r="AD18" s="11">
-        <v>162351</v>
+        <v>91784</v>
       </c>
       <c r="AE18" s="3">
-        <v>163071</v>
+        <v>92341</v>
       </c>
       <c r="AF18" s="3">
-        <v>171760</v>
+        <v>97772</v>
       </c>
       <c r="AG18" s="3">
-        <v>172153</v>
+        <v>98441</v>
       </c>
       <c r="AH18" s="3">
-        <v>178126</v>
-      </c>
-      <c r="AI18" s="17">
-        <v>183055</v>
+        <v>101544</v>
+      </c>
+      <c r="AI18" s="15">
+        <v>105101</v>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.2">
@@ -3041,106 +3042,106 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" s="9">
-        <v>33458</v>
+        <v>245157</v>
       </c>
       <c r="E19" s="9">
-        <v>28690</v>
+        <v>246726</v>
       </c>
       <c r="F19" s="9">
-        <v>24601</v>
+        <v>248305</v>
       </c>
       <c r="G19" s="9">
-        <v>30975</v>
+        <v>235711</v>
       </c>
       <c r="H19" s="9">
-        <v>33624</v>
-      </c>
-      <c r="I19" s="9">
-        <v>36455</v>
-      </c>
-      <c r="J19" s="9">
-        <v>37648</v>
-      </c>
-      <c r="K19" s="9">
-        <v>39982</v>
-      </c>
-      <c r="L19" s="9">
-        <v>42731</v>
-      </c>
-      <c r="M19" s="9">
-        <v>50184</v>
-      </c>
-      <c r="N19" s="9">
-        <v>57210</v>
-      </c>
-      <c r="O19" s="9">
-        <v>65597</v>
+        <v>237839</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="P19" s="2">
-        <v>73375</v>
+        <v>296538</v>
       </c>
       <c r="Q19" s="2">
-        <v>81153</v>
+        <v>303714</v>
       </c>
       <c r="R19" s="3">
-        <v>84292</v>
+        <v>297755</v>
       </c>
       <c r="S19" s="3">
-        <v>91544</v>
-      </c>
-      <c r="T19" s="2">
-        <v>74927</v>
-      </c>
-      <c r="U19" s="5">
-        <v>73982</v>
-      </c>
-      <c r="V19" s="5">
-        <v>76417</v>
+        <v>303545</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="W19" s="4">
-        <v>74001</v>
+        <v>257190</v>
       </c>
       <c r="X19" s="10">
-        <v>76698</v>
+        <v>260444</v>
       </c>
       <c r="Y19" s="10">
-        <v>79396</v>
-      </c>
-      <c r="Z19" s="5">
-        <v>88105</v>
-      </c>
-      <c r="AA19" s="5">
-        <v>85353</v>
-      </c>
-      <c r="AB19" s="5">
-        <v>86391</v>
+        <v>263698</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>269169</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>269558</v>
       </c>
       <c r="AC19" s="11">
-        <v>86391</v>
+        <v>269558</v>
       </c>
       <c r="AD19" s="11">
-        <v>91784</v>
+        <v>311607</v>
       </c>
       <c r="AE19" s="3">
-        <v>92341</v>
+        <v>316157</v>
       </c>
       <c r="AF19" s="3">
-        <v>97772</v>
+        <v>358778</v>
       </c>
       <c r="AG19" s="3">
-        <v>98441</v>
+        <v>373963</v>
       </c>
       <c r="AH19" s="3">
-        <v>101544</v>
-      </c>
-      <c r="AI19" s="17">
-        <v>105101</v>
+        <v>419403</v>
+      </c>
+      <c r="AI19" s="15">
+        <v>471796</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.2">
@@ -3151,55 +3152,55 @@
         <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D20" s="9">
-        <v>245157</v>
+        <v>96559</v>
       </c>
       <c r="E20" s="9">
-        <v>246726</v>
+        <v>87884</v>
       </c>
       <c r="F20" s="9">
-        <v>248305</v>
+        <v>79988</v>
       </c>
       <c r="G20" s="9">
-        <v>235711</v>
+        <v>87364</v>
       </c>
       <c r="H20" s="9">
-        <v>237839</v>
+        <v>91089</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="P20" s="2">
-        <v>296538</v>
+        <v>145783</v>
       </c>
       <c r="Q20" s="2">
-        <v>303714</v>
+        <v>152795</v>
       </c>
       <c r="R20" s="3">
-        <v>297755</v>
+        <v>148080</v>
       </c>
       <c r="S20" s="3">
-        <v>303545</v>
+        <v>149270</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>132</v>
@@ -3211,43 +3212,43 @@
         <v>144</v>
       </c>
       <c r="W20" s="4">
-        <v>257190</v>
+        <v>108615</v>
       </c>
       <c r="X20" s="10">
-        <v>260444</v>
+        <v>112718</v>
       </c>
       <c r="Y20" s="10">
-        <v>263698</v>
+        <v>116820</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>169</v>
       </c>
       <c r="AA20" s="3">
-        <v>269169</v>
+        <v>125689</v>
       </c>
       <c r="AB20" s="3">
-        <v>269558</v>
+        <v>126703</v>
       </c>
       <c r="AC20" s="11">
-        <v>269558</v>
+        <v>126703</v>
       </c>
       <c r="AD20" s="11">
-        <v>311607</v>
+        <v>136274</v>
       </c>
       <c r="AE20" s="3">
-        <v>316157</v>
+        <v>137270</v>
       </c>
       <c r="AF20" s="3">
-        <v>358778</v>
+        <v>159166</v>
       </c>
       <c r="AG20" s="3">
-        <v>373963</v>
+        <v>170952</v>
       </c>
       <c r="AH20" s="3">
-        <v>419403</v>
-      </c>
-      <c r="AI20" s="17">
-        <v>471796</v>
+        <v>204372</v>
+      </c>
+      <c r="AI20" s="15">
+        <v>235028</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.2">
@@ -3258,55 +3259,55 @@
         <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D21" s="9">
-        <v>96559</v>
+        <v>651237</v>
       </c>
       <c r="E21" s="9">
-        <v>87884</v>
+        <v>671360</v>
       </c>
       <c r="F21" s="9">
-        <v>79988</v>
+        <v>692105</v>
       </c>
       <c r="G21" s="9">
-        <v>87364</v>
+        <v>676705</v>
       </c>
       <c r="H21" s="9">
-        <v>91089</v>
+        <v>673347</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="P21" s="2">
-        <v>145783</v>
+        <v>648993</v>
       </c>
       <c r="Q21" s="2">
-        <v>152795</v>
+        <v>615137</v>
       </c>
       <c r="R21" s="3">
-        <v>148080</v>
+        <v>601400</v>
       </c>
       <c r="S21" s="3">
-        <v>149270</v>
+        <v>611907</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>133</v>
@@ -3318,43 +3319,43 @@
         <v>145</v>
       </c>
       <c r="W21" s="4">
-        <v>108615</v>
+        <v>639961</v>
       </c>
       <c r="X21" s="10">
-        <v>112718</v>
+        <v>658429</v>
       </c>
       <c r="Y21" s="10">
-        <v>116820</v>
+        <v>676897</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>170</v>
       </c>
       <c r="AA21" s="3">
-        <v>125689</v>
+        <v>705930</v>
       </c>
       <c r="AB21" s="3">
-        <v>126703</v>
+        <v>713077</v>
       </c>
       <c r="AC21" s="11">
-        <v>126703</v>
+        <v>713077</v>
       </c>
       <c r="AD21" s="11">
-        <v>136274</v>
+        <v>811831</v>
       </c>
       <c r="AE21" s="3">
-        <v>137270</v>
+        <v>822429</v>
       </c>
       <c r="AF21" s="3">
-        <v>159166</v>
+        <v>949630</v>
       </c>
       <c r="AG21" s="3">
-        <v>170952</v>
+        <v>969210</v>
       </c>
       <c r="AH21" s="3">
-        <v>204372</v>
-      </c>
-      <c r="AI21" s="17">
-        <v>235028</v>
+        <v>1034911</v>
+      </c>
+      <c r="AI21" s="15">
+        <v>1090367</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.2">
@@ -3365,55 +3366,55 @@
         <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D22" s="9">
-        <v>651237</v>
+        <v>562535</v>
       </c>
       <c r="E22" s="9">
-        <v>671360</v>
+        <v>602579</v>
       </c>
       <c r="F22" s="9">
-        <v>692105</v>
+        <v>645474</v>
       </c>
       <c r="G22" s="9">
-        <v>676705</v>
+        <v>567830</v>
       </c>
       <c r="H22" s="9">
-        <v>673347</v>
+        <v>582701</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="P22" s="2">
-        <v>648993</v>
+        <v>859755</v>
       </c>
       <c r="Q22" s="2">
-        <v>615137</v>
+        <v>912668</v>
       </c>
       <c r="R22" s="3">
-        <v>601400</v>
+        <v>902394</v>
       </c>
       <c r="S22" s="3">
-        <v>611907</v>
+        <v>930324</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>134</v>
@@ -3425,150 +3426,150 @@
         <v>146</v>
       </c>
       <c r="W22" s="4">
-        <v>639961</v>
+        <v>688213</v>
       </c>
       <c r="X22" s="10">
-        <v>658429</v>
+        <v>694998</v>
       </c>
       <c r="Y22" s="10">
-        <v>676897</v>
+        <v>701782</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>171</v>
       </c>
       <c r="AA22" s="3">
-        <v>705930</v>
+        <v>721744</v>
       </c>
       <c r="AB22" s="3">
-        <v>713077</v>
+        <v>721187</v>
       </c>
       <c r="AC22" s="11">
-        <v>713077</v>
+        <v>721187</v>
       </c>
       <c r="AD22" s="11">
-        <v>811831</v>
+        <v>773824</v>
       </c>
       <c r="AE22" s="3">
-        <v>822429</v>
+        <v>779295</v>
       </c>
       <c r="AF22" s="3">
-        <v>949630</v>
+        <v>850631</v>
       </c>
       <c r="AG22" s="3">
-        <v>969210</v>
+        <v>861488</v>
       </c>
       <c r="AH22" s="3">
-        <v>1034911</v>
-      </c>
-      <c r="AI22" s="17">
-        <v>1090367</v>
+        <v>916118</v>
+      </c>
+      <c r="AI22" s="15">
+        <v>962188</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D23" s="9">
-        <v>562535</v>
+        <v>9702</v>
       </c>
       <c r="E23" s="9">
-        <v>602579</v>
+        <v>11370</v>
       </c>
       <c r="F23" s="9">
-        <v>645474</v>
+        <v>13325</v>
       </c>
       <c r="G23" s="9">
-        <v>567830</v>
+        <v>11939</v>
       </c>
       <c r="H23" s="9">
-        <v>582701</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>81</v>
+        <v>11691</v>
+      </c>
+      <c r="I23" s="9">
+        <v>11364</v>
+      </c>
+      <c r="J23" s="9">
+        <v>11487</v>
+      </c>
+      <c r="K23" s="9">
+        <v>11736</v>
+      </c>
+      <c r="L23" s="9">
+        <v>11892</v>
+      </c>
+      <c r="M23" s="9">
+        <v>12231</v>
+      </c>
+      <c r="N23" s="9">
+        <v>9795</v>
+      </c>
+      <c r="O23" s="9">
+        <v>9153</v>
       </c>
       <c r="P23" s="2">
-        <v>859755</v>
+        <v>8076</v>
       </c>
       <c r="Q23" s="2">
-        <v>912668</v>
+        <v>7000</v>
       </c>
       <c r="R23" s="3">
-        <v>902394</v>
+        <v>6913</v>
       </c>
       <c r="S23" s="3">
-        <v>930324</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>147</v>
+        <v>6871</v>
+      </c>
+      <c r="T23" s="2">
+        <v>8349</v>
+      </c>
+      <c r="U23" s="5">
+        <v>7614</v>
+      </c>
+      <c r="V23" s="5">
+        <v>7929</v>
       </c>
       <c r="W23" s="4">
-        <v>688213</v>
+        <v>8147</v>
       </c>
       <c r="X23" s="10">
-        <v>694998</v>
+        <v>8076</v>
       </c>
       <c r="Y23" s="10">
-        <v>701782</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>721744</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>721187</v>
+        <v>8006</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>7929</v>
+      </c>
+      <c r="AA23" s="5">
+        <v>7989</v>
+      </c>
+      <c r="AB23" s="5">
+        <v>7993</v>
       </c>
       <c r="AC23" s="11">
-        <v>721187</v>
+        <v>7993</v>
       </c>
       <c r="AD23" s="11">
-        <v>773824</v>
+        <v>7759</v>
       </c>
       <c r="AE23" s="3">
-        <v>779295</v>
+        <v>7736</v>
       </c>
       <c r="AF23" s="3">
-        <v>850631</v>
+        <v>8608</v>
       </c>
       <c r="AG23" s="3">
-        <v>861488</v>
+        <v>8772</v>
       </c>
       <c r="AH23" s="3">
-        <v>916118</v>
-      </c>
-      <c r="AI23" s="17">
-        <v>962188</v>
+        <v>8949</v>
+      </c>
+      <c r="AI23" s="15">
+        <v>8989</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.2">
@@ -3579,103 +3580,103 @@
         <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D24" s="9">
-        <v>9702</v>
+        <v>1136</v>
       </c>
       <c r="E24" s="9">
-        <v>11370</v>
+        <v>1297</v>
       </c>
       <c r="F24" s="9">
-        <v>13325</v>
+        <v>1481</v>
       </c>
       <c r="G24" s="9">
-        <v>11939</v>
+        <v>1391</v>
       </c>
       <c r="H24" s="9">
-        <v>11691</v>
+        <v>1411</v>
       </c>
       <c r="I24" s="9">
-        <v>11364</v>
+        <v>1442</v>
       </c>
       <c r="J24" s="9">
-        <v>11487</v>
+        <v>1446</v>
       </c>
       <c r="K24" s="9">
-        <v>11736</v>
+        <v>1479</v>
       </c>
       <c r="L24" s="9">
-        <v>11892</v>
+        <v>1503</v>
       </c>
       <c r="M24" s="9">
-        <v>12231</v>
+        <v>1548</v>
       </c>
       <c r="N24" s="9">
-        <v>9795</v>
+        <v>1423</v>
       </c>
       <c r="O24" s="9">
-        <v>9153</v>
+        <v>1362</v>
       </c>
       <c r="P24" s="2">
-        <v>8076</v>
+        <v>1297</v>
       </c>
       <c r="Q24" s="2">
-        <v>7000</v>
+        <v>1232</v>
       </c>
       <c r="R24" s="3">
-        <v>6913</v>
+        <v>1228</v>
       </c>
       <c r="S24" s="3">
-        <v>6871</v>
+        <v>1226</v>
       </c>
       <c r="T24" s="2">
-        <v>8349</v>
+        <v>1354</v>
       </c>
       <c r="U24" s="5">
-        <v>7614</v>
+        <v>1221</v>
       </c>
       <c r="V24" s="5">
-        <v>7929</v>
+        <v>1247</v>
       </c>
       <c r="W24" s="4">
-        <v>8147</v>
+        <v>1271</v>
       </c>
       <c r="X24" s="10">
-        <v>8076</v>
+        <v>1286</v>
       </c>
       <c r="Y24" s="10">
-        <v>8006</v>
+        <v>1300</v>
       </c>
       <c r="Z24" s="5">
-        <v>7929</v>
+        <v>1400</v>
       </c>
       <c r="AA24" s="5">
-        <v>7989</v>
+        <v>1372</v>
       </c>
       <c r="AB24" s="5">
-        <v>7993</v>
+        <v>1384</v>
       </c>
       <c r="AC24" s="11">
-        <v>7993</v>
+        <v>1384</v>
       </c>
       <c r="AD24" s="11">
-        <v>7759</v>
+        <v>1405</v>
       </c>
       <c r="AE24" s="3">
-        <v>7736</v>
+        <v>1407</v>
       </c>
       <c r="AF24" s="3">
-        <v>8608</v>
+        <v>1360</v>
       </c>
       <c r="AG24" s="3">
-        <v>8772</v>
+        <v>1373</v>
       </c>
       <c r="AH24" s="3">
-        <v>8949</v>
-      </c>
-      <c r="AI24" s="17">
-        <v>8989</v>
+        <v>1415</v>
+      </c>
+      <c r="AI24" s="15">
+        <v>1483</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.2">
@@ -3686,103 +3687,103 @@
         <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="9">
-        <v>1136</v>
+        <v>2169</v>
       </c>
       <c r="E25" s="9">
-        <v>1297</v>
+        <v>2540</v>
       </c>
       <c r="F25" s="9">
-        <v>1481</v>
+        <v>2974</v>
       </c>
       <c r="G25" s="9">
-        <v>1391</v>
+        <v>2626</v>
       </c>
       <c r="H25" s="9">
-        <v>1411</v>
+        <v>2606</v>
       </c>
       <c r="I25" s="9">
-        <v>1442</v>
+        <v>2458</v>
       </c>
       <c r="J25" s="9">
-        <v>1446</v>
+        <v>2487</v>
       </c>
       <c r="K25" s="9">
-        <v>1479</v>
+        <v>2553</v>
       </c>
       <c r="L25" s="9">
-        <v>1503</v>
+        <v>2612</v>
       </c>
       <c r="M25" s="9">
-        <v>1548</v>
+        <v>2701</v>
       </c>
       <c r="N25" s="9">
-        <v>1423</v>
+        <v>2243</v>
       </c>
       <c r="O25" s="9">
-        <v>1362</v>
+        <v>2163</v>
       </c>
       <c r="P25" s="2">
-        <v>1297</v>
+        <v>1985</v>
       </c>
       <c r="Q25" s="2">
-        <v>1232</v>
+        <v>1807</v>
       </c>
       <c r="R25" s="3">
-        <v>1228</v>
+        <v>1767</v>
       </c>
       <c r="S25" s="3">
-        <v>1226</v>
+        <v>1734</v>
       </c>
       <c r="T25" s="2">
-        <v>1354</v>
+        <v>1955</v>
       </c>
       <c r="U25" s="5">
-        <v>1221</v>
+        <v>1861</v>
       </c>
       <c r="V25" s="5">
-        <v>1247</v>
+        <v>1905</v>
       </c>
       <c r="W25" s="4">
-        <v>1271</v>
+        <v>1925</v>
       </c>
       <c r="X25" s="10">
-        <v>1286</v>
+        <v>1945</v>
       </c>
       <c r="Y25" s="10">
-        <v>1300</v>
+        <v>1965</v>
       </c>
       <c r="Z25" s="5">
-        <v>1400</v>
+        <v>2046</v>
       </c>
       <c r="AA25" s="5">
-        <v>1372</v>
+        <v>2028</v>
       </c>
       <c r="AB25" s="5">
-        <v>1384</v>
+        <v>2041</v>
       </c>
       <c r="AC25" s="11">
-        <v>1384</v>
+        <v>2041</v>
       </c>
       <c r="AD25" s="11">
-        <v>1405</v>
+        <v>2048</v>
       </c>
       <c r="AE25" s="3">
-        <v>1407</v>
+        <v>2049</v>
       </c>
       <c r="AF25" s="3">
-        <v>1360</v>
+        <v>2202</v>
       </c>
       <c r="AG25" s="3">
-        <v>1373</v>
+        <v>2225</v>
       </c>
       <c r="AH25" s="3">
-        <v>1415</v>
-      </c>
-      <c r="AI25" s="17">
-        <v>1483</v>
+        <v>2255</v>
+      </c>
+      <c r="AI25" s="15">
+        <v>2314</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.2">
@@ -3793,103 +3794,103 @@
         <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D26" s="9">
-        <v>2169</v>
+        <v>0</v>
       </c>
       <c r="E26" s="9">
-        <v>2540</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9">
-        <v>2974</v>
+        <v>0</v>
       </c>
       <c r="G26" s="9">
-        <v>2626</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9">
-        <v>2606</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9">
-        <v>2458</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9">
-        <v>2487</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9">
-        <v>2553</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9">
-        <v>2612</v>
+        <v>0</v>
       </c>
       <c r="M26" s="9">
-        <v>2701</v>
+        <v>0</v>
       </c>
       <c r="N26" s="9">
-        <v>2243</v>
+        <v>0</v>
       </c>
       <c r="O26" s="9">
-        <v>2163</v>
-      </c>
-      <c r="P26" s="2">
-        <v>1985</v>
-      </c>
-      <c r="Q26" s="2">
-        <v>1807</v>
-      </c>
-      <c r="R26" s="3">
-        <v>1767</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1734</v>
-      </c>
-      <c r="T26" s="2">
-        <v>1955</v>
-      </c>
-      <c r="U26" s="5">
-        <v>1861</v>
-      </c>
-      <c r="V26" s="5">
-        <v>1905</v>
-      </c>
-      <c r="W26" s="4">
-        <v>1925</v>
-      </c>
-      <c r="X26" s="10">
-        <v>1945</v>
-      </c>
-      <c r="Y26" s="10">
-        <v>1965</v>
-      </c>
-      <c r="Z26" s="5">
-        <v>2046</v>
-      </c>
-      <c r="AA26" s="5">
-        <v>2028</v>
-      </c>
-      <c r="AB26" s="5">
-        <v>2041</v>
-      </c>
-      <c r="AC26" s="11">
-        <v>2041</v>
-      </c>
-      <c r="AD26" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>2049</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>2202</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>2225</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>2255</v>
-      </c>
-      <c r="AI26" s="17">
-        <v>2314</v>
+        <v>0</v>
+      </c>
+      <c r="P26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>0</v>
+      </c>
+      <c r="R26" s="9">
+        <v>0</v>
+      </c>
+      <c r="S26" s="9">
+        <v>0</v>
+      </c>
+      <c r="T26" s="9">
+        <v>0</v>
+      </c>
+      <c r="U26" s="9">
+        <v>0</v>
+      </c>
+      <c r="V26" s="9">
+        <v>0</v>
+      </c>
+      <c r="W26" s="9">
+        <v>0</v>
+      </c>
+      <c r="X26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.2">
@@ -3900,103 +3901,103 @@
         <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X27" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y27" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD27" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI27" s="17">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="D27" s="9">
+        <v>138</v>
+      </c>
+      <c r="E27" s="9">
+        <v>164</v>
+      </c>
+      <c r="F27" s="9">
+        <v>195</v>
+      </c>
+      <c r="G27" s="9">
+        <v>163</v>
+      </c>
+      <c r="H27" s="9">
+        <v>137</v>
+      </c>
+      <c r="I27" s="9">
+        <v>130</v>
+      </c>
+      <c r="J27" s="9">
+        <v>134</v>
+      </c>
+      <c r="K27" s="9">
+        <v>138</v>
+      </c>
+      <c r="L27" s="9">
+        <v>141</v>
+      </c>
+      <c r="M27" s="9">
+        <v>143</v>
+      </c>
+      <c r="N27" s="9">
+        <v>144</v>
+      </c>
+      <c r="O27" s="9">
+        <v>137</v>
+      </c>
+      <c r="P27" s="2">
+        <v>134</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>131</v>
+      </c>
+      <c r="R27" s="3">
+        <v>134</v>
+      </c>
+      <c r="S27" s="3">
+        <v>136</v>
+      </c>
+      <c r="T27" s="2">
+        <v>150</v>
+      </c>
+      <c r="U27" s="3">
+        <v>171</v>
+      </c>
+      <c r="V27" s="3">
+        <v>165</v>
+      </c>
+      <c r="W27" s="4">
+        <v>171</v>
+      </c>
+      <c r="X27" s="10">
+        <v>178</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>185</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>191</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>192</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>195</v>
+      </c>
+      <c r="AC27" s="11">
+        <v>195</v>
+      </c>
+      <c r="AD27" s="11">
+        <v>178</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>176</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>231</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>222</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>217</v>
+      </c>
+      <c r="AI27" s="15">
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.2">
@@ -4007,103 +4008,103 @@
         <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D28" s="9">
-        <v>15665</v>
+        <v>2679</v>
       </c>
       <c r="E28" s="9">
-        <v>18368</v>
+        <v>3363</v>
       </c>
       <c r="F28" s="9">
-        <v>21537</v>
+        <v>4222</v>
       </c>
       <c r="G28" s="9">
-        <v>20433</v>
+        <v>4017</v>
       </c>
       <c r="H28" s="9">
-        <v>19944</v>
+        <v>4237</v>
       </c>
       <c r="I28" s="9">
-        <v>19145</v>
+        <v>4457</v>
       </c>
       <c r="J28" s="9">
-        <v>19861</v>
+        <v>4486</v>
       </c>
       <c r="K28" s="9">
-        <v>20628</v>
+        <v>4603</v>
       </c>
       <c r="L28" s="9">
-        <v>21301</v>
+        <v>4712</v>
       </c>
       <c r="M28" s="9">
-        <v>23506</v>
+        <v>4829</v>
       </c>
       <c r="N28" s="9">
-        <v>26771</v>
+        <v>4747</v>
       </c>
       <c r="O28" s="9">
-        <v>28509</v>
+        <v>4653</v>
       </c>
       <c r="P28" s="2">
-        <v>30834</v>
+        <v>4598</v>
       </c>
       <c r="Q28" s="2">
-        <v>33159</v>
+        <v>4543</v>
       </c>
       <c r="R28" s="3">
-        <v>30941</v>
+        <v>4637</v>
       </c>
       <c r="S28" s="3">
-        <v>27786</v>
+        <v>4731</v>
       </c>
       <c r="T28" s="2">
-        <v>21006</v>
+        <v>5158</v>
       </c>
       <c r="U28" s="5">
-        <v>23487</v>
+        <v>5386</v>
       </c>
       <c r="V28" s="5">
-        <v>22116</v>
+        <v>5258</v>
       </c>
       <c r="W28" s="4">
-        <v>19669</v>
+        <v>5453</v>
       </c>
       <c r="X28" s="10">
-        <v>19659</v>
+        <v>5391</v>
       </c>
       <c r="Y28" s="10">
-        <v>19649</v>
+        <v>5330</v>
       </c>
       <c r="Z28" s="5">
-        <v>20511</v>
+        <v>4948</v>
       </c>
       <c r="AA28" s="5">
-        <v>19591</v>
+        <v>5108</v>
       </c>
       <c r="AB28" s="5">
-        <v>19364</v>
+        <v>5086</v>
       </c>
       <c r="AC28" s="11">
-        <v>19364</v>
+        <v>5086</v>
       </c>
       <c r="AD28" s="11">
-        <v>18054</v>
+        <v>5104</v>
       </c>
       <c r="AE28" s="3">
-        <v>17928</v>
+        <v>5106</v>
       </c>
       <c r="AF28" s="3">
-        <v>20489</v>
+        <v>5685</v>
       </c>
       <c r="AG28" s="3">
-        <v>21008</v>
+        <v>5859</v>
       </c>
       <c r="AH28" s="3">
-        <v>22063</v>
-      </c>
-      <c r="AI28" s="17">
-        <v>24034</v>
+        <v>6135</v>
+      </c>
+      <c r="AI28" s="15">
+        <v>6328</v>
       </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.2">
@@ -4111,106 +4112,106 @@
         <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="9">
-        <v>138</v>
+        <v>13941</v>
       </c>
       <c r="E29" s="9">
-        <v>164</v>
+        <v>13971</v>
       </c>
       <c r="F29" s="9">
-        <v>195</v>
+        <v>14001</v>
       </c>
       <c r="G29" s="9">
-        <v>163</v>
+        <v>13558</v>
       </c>
       <c r="H29" s="9">
-        <v>137</v>
+        <v>13365</v>
       </c>
       <c r="I29" s="9">
-        <v>130</v>
+        <v>13602</v>
       </c>
       <c r="J29" s="9">
-        <v>134</v>
+        <v>13684</v>
       </c>
       <c r="K29" s="9">
-        <v>138</v>
+        <v>13821</v>
       </c>
       <c r="L29" s="9">
-        <v>141</v>
+        <v>13907</v>
       </c>
       <c r="M29" s="9">
-        <v>143</v>
+        <v>14042</v>
       </c>
       <c r="N29" s="9">
-        <v>144</v>
+        <v>13352</v>
       </c>
       <c r="O29" s="9">
-        <v>137</v>
+        <v>13096</v>
       </c>
       <c r="P29" s="2">
-        <v>134</v>
+        <v>12760</v>
       </c>
       <c r="Q29" s="2">
-        <v>131</v>
+        <v>12424</v>
       </c>
       <c r="R29" s="3">
-        <v>134</v>
+        <v>12621</v>
       </c>
       <c r="S29" s="3">
-        <v>136</v>
+        <v>12822</v>
       </c>
       <c r="T29" s="2">
-        <v>150</v>
-      </c>
-      <c r="U29" s="3">
-        <v>171</v>
-      </c>
-      <c r="V29" s="3">
-        <v>165</v>
+        <v>14185</v>
+      </c>
+      <c r="U29" s="5">
+        <v>14884</v>
+      </c>
+      <c r="V29" s="5">
+        <v>14530</v>
       </c>
       <c r="W29" s="4">
-        <v>171</v>
+        <v>15081</v>
       </c>
       <c r="X29" s="10">
-        <v>178</v>
+        <v>15271</v>
       </c>
       <c r="Y29" s="10">
-        <v>185</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>191</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>192</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>195</v>
+        <v>15462</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>15435</v>
+      </c>
+      <c r="AA29" s="5">
+        <v>15612</v>
+      </c>
+      <c r="AB29" s="5">
+        <v>15710</v>
       </c>
       <c r="AC29" s="11">
-        <v>195</v>
+        <v>15710</v>
       </c>
       <c r="AD29" s="11">
-        <v>178</v>
+        <v>15346</v>
       </c>
       <c r="AE29" s="3">
-        <v>176</v>
+        <v>15310</v>
       </c>
       <c r="AF29" s="3">
-        <v>231</v>
+        <v>17234</v>
       </c>
       <c r="AG29" s="3">
-        <v>222</v>
+        <v>18090</v>
       </c>
       <c r="AH29" s="3">
-        <v>217</v>
-      </c>
-      <c r="AI29" s="17">
-        <v>226</v>
+        <v>18731</v>
+      </c>
+      <c r="AI29" s="15">
+        <v>19018</v>
       </c>
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.2">
@@ -4218,106 +4219,106 @@
         <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30" s="9">
-        <v>2679</v>
+        <v>59291</v>
       </c>
       <c r="E30" s="9">
-        <v>3363</v>
+        <v>55057</v>
       </c>
       <c r="F30" s="9">
-        <v>4222</v>
+        <v>51125</v>
       </c>
       <c r="G30" s="9">
-        <v>4017</v>
+        <v>57250</v>
       </c>
       <c r="H30" s="9">
-        <v>4237</v>
+        <v>58525</v>
       </c>
       <c r="I30" s="9">
-        <v>4457</v>
+        <v>60392</v>
       </c>
       <c r="J30" s="9">
-        <v>4486</v>
+        <v>60874</v>
       </c>
       <c r="K30" s="9">
-        <v>4603</v>
+        <v>62412</v>
       </c>
       <c r="L30" s="9">
-        <v>4712</v>
+        <v>64083</v>
       </c>
       <c r="M30" s="9">
-        <v>4829</v>
+        <v>65917</v>
       </c>
       <c r="N30" s="9">
-        <v>4747</v>
+        <v>57715</v>
       </c>
       <c r="O30" s="9">
-        <v>4653</v>
+        <v>59112</v>
       </c>
       <c r="P30" s="2">
-        <v>4598</v>
+        <v>57382</v>
       </c>
       <c r="Q30" s="2">
-        <v>4543</v>
+        <v>55652</v>
       </c>
       <c r="R30" s="3">
-        <v>4637</v>
+        <v>58952</v>
       </c>
       <c r="S30" s="3">
-        <v>4731</v>
+        <v>62294</v>
       </c>
       <c r="T30" s="2">
-        <v>5158</v>
+        <v>76957</v>
       </c>
       <c r="U30" s="5">
-        <v>5386</v>
+        <v>85406</v>
       </c>
       <c r="V30" s="5">
-        <v>5258</v>
+        <v>82691</v>
       </c>
       <c r="W30" s="4">
-        <v>5453</v>
+        <v>88622</v>
       </c>
       <c r="X30" s="10">
-        <v>5391</v>
+        <v>91624</v>
       </c>
       <c r="Y30" s="10">
-        <v>5330</v>
+        <v>94626</v>
       </c>
       <c r="Z30" s="5">
-        <v>4948</v>
+        <v>95855</v>
       </c>
       <c r="AA30" s="5">
-        <v>5108</v>
+        <v>97691</v>
       </c>
       <c r="AB30" s="5">
-        <v>5086</v>
+        <v>99168</v>
       </c>
       <c r="AC30" s="11">
-        <v>5086</v>
+        <v>99168</v>
       </c>
       <c r="AD30" s="11">
-        <v>5104</v>
+        <v>99365</v>
       </c>
       <c r="AE30" s="3">
-        <v>5106</v>
+        <v>99385</v>
       </c>
       <c r="AF30" s="3">
-        <v>5685</v>
+        <v>109652</v>
       </c>
       <c r="AG30" s="3">
-        <v>5859</v>
+        <v>111742</v>
       </c>
       <c r="AH30" s="3">
-        <v>6135</v>
-      </c>
-      <c r="AI30" s="17">
-        <v>6328</v>
+        <v>120275</v>
+      </c>
+      <c r="AI30" s="15">
+        <v>126055</v>
       </c>
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.2">
@@ -4328,103 +4329,103 @@
         <v>23</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="9">
-        <v>13941</v>
+        <v>6994</v>
       </c>
       <c r="E31" s="9">
-        <v>13971</v>
+        <v>7529</v>
       </c>
       <c r="F31" s="9">
-        <v>14001</v>
+        <v>8105</v>
       </c>
       <c r="G31" s="9">
-        <v>13558</v>
+        <v>7252</v>
       </c>
       <c r="H31" s="9">
-        <v>13365</v>
-      </c>
-      <c r="I31" s="9">
-        <v>13602</v>
+        <v>7021</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="J31" s="9">
-        <v>13684</v>
+        <v>6782</v>
       </c>
       <c r="K31" s="9">
-        <v>13821</v>
+        <v>6597</v>
       </c>
       <c r="L31" s="9">
-        <v>13907</v>
+        <v>6318</v>
       </c>
       <c r="M31" s="9">
-        <v>14042</v>
+        <v>6104</v>
       </c>
       <c r="N31" s="9">
-        <v>13352</v>
+        <v>5957</v>
       </c>
       <c r="O31" s="9">
-        <v>13096</v>
+        <v>5457</v>
       </c>
       <c r="P31" s="2">
-        <v>12760</v>
+        <v>5122</v>
       </c>
       <c r="Q31" s="2">
-        <v>12424</v>
+        <v>4787</v>
       </c>
       <c r="R31" s="3">
-        <v>12621</v>
+        <v>5120</v>
       </c>
       <c r="S31" s="3">
-        <v>12822</v>
+        <v>5460</v>
       </c>
       <c r="T31" s="2">
-        <v>14185</v>
+        <v>6994</v>
       </c>
       <c r="U31" s="5">
-        <v>14884</v>
+        <v>8644</v>
       </c>
       <c r="V31" s="5">
-        <v>14530</v>
+        <v>8255</v>
       </c>
       <c r="W31" s="4">
-        <v>15081</v>
+        <v>8878</v>
       </c>
       <c r="X31" s="10">
-        <v>15271</v>
+        <v>9076</v>
       </c>
       <c r="Y31" s="10">
-        <v>15462</v>
+        <v>9275</v>
       </c>
       <c r="Z31" s="5">
-        <v>15435</v>
+        <v>8614</v>
       </c>
       <c r="AA31" s="5">
-        <v>15612</v>
+        <v>9070</v>
       </c>
       <c r="AB31" s="5">
-        <v>15710</v>
+        <v>9151</v>
       </c>
       <c r="AC31" s="11">
-        <v>15710</v>
+        <v>9151</v>
       </c>
       <c r="AD31" s="11">
-        <v>15346</v>
+        <v>9174</v>
       </c>
       <c r="AE31" s="3">
-        <v>15310</v>
+        <v>9176</v>
       </c>
       <c r="AF31" s="3">
-        <v>17234</v>
+        <v>9110</v>
       </c>
       <c r="AG31" s="3">
-        <v>18090</v>
+        <v>9112</v>
       </c>
       <c r="AH31" s="3">
-        <v>18731</v>
-      </c>
-      <c r="AI31" s="17">
-        <v>19018</v>
+        <v>9077</v>
+      </c>
+      <c r="AI31" s="15">
+        <v>9469</v>
       </c>
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.2">
@@ -4435,103 +4436,103 @@
         <v>23</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" s="9">
-        <v>59291</v>
+        <v>4071</v>
       </c>
       <c r="E32" s="9">
-        <v>55057</v>
+        <v>2521</v>
       </c>
       <c r="F32" s="9">
-        <v>51125</v>
+        <v>1561</v>
       </c>
       <c r="G32" s="9">
-        <v>57250</v>
+        <v>1664</v>
       </c>
       <c r="H32" s="9">
-        <v>58525</v>
+        <v>1328</v>
       </c>
       <c r="I32" s="9">
-        <v>60392</v>
+        <v>955</v>
       </c>
       <c r="J32" s="9">
-        <v>60874</v>
+        <v>912</v>
       </c>
       <c r="K32" s="9">
-        <v>62412</v>
+        <v>847</v>
       </c>
       <c r="L32" s="9">
-        <v>64083</v>
+        <v>803</v>
       </c>
       <c r="M32" s="9">
-        <v>65917</v>
+        <v>712</v>
       </c>
       <c r="N32" s="9">
-        <v>57715</v>
+        <v>558</v>
       </c>
       <c r="O32" s="9">
-        <v>59112</v>
+        <v>506</v>
       </c>
       <c r="P32" s="2">
-        <v>57382</v>
+        <v>414</v>
       </c>
       <c r="Q32" s="2">
-        <v>55652</v>
+        <v>322</v>
       </c>
       <c r="R32" s="3">
-        <v>58952</v>
+        <v>326</v>
       </c>
       <c r="S32" s="3">
-        <v>62294</v>
+        <v>334</v>
       </c>
       <c r="T32" s="2">
-        <v>76957</v>
-      </c>
-      <c r="U32" s="5">
-        <v>85406</v>
-      </c>
-      <c r="V32" s="5">
-        <v>82691</v>
+        <v>448</v>
+      </c>
+      <c r="U32" s="3">
+        <v>417</v>
+      </c>
+      <c r="V32" s="3">
+        <v>428</v>
       </c>
       <c r="W32" s="4">
-        <v>88622</v>
+        <v>455</v>
       </c>
       <c r="X32" s="10">
-        <v>91624</v>
+        <v>1477</v>
       </c>
       <c r="Y32" s="10">
-        <v>94626</v>
+        <v>2499</v>
       </c>
       <c r="Z32" s="5">
-        <v>95855</v>
+        <v>5560</v>
       </c>
       <c r="AA32" s="5">
-        <v>97691</v>
+        <v>1980</v>
       </c>
       <c r="AB32" s="5">
-        <v>99168</v>
+        <v>760</v>
       </c>
       <c r="AC32" s="11">
-        <v>99168</v>
+        <v>760</v>
       </c>
       <c r="AD32" s="11">
-        <v>99365</v>
+        <v>1253</v>
       </c>
       <c r="AE32" s="3">
-        <v>99385</v>
+        <v>1291</v>
       </c>
       <c r="AF32" s="3">
-        <v>109652</v>
+        <v>730</v>
       </c>
       <c r="AG32" s="3">
-        <v>111742</v>
+        <v>1061</v>
       </c>
       <c r="AH32" s="3">
-        <v>120275</v>
-      </c>
-      <c r="AI32" s="17">
-        <v>126055</v>
+        <v>1172</v>
+      </c>
+      <c r="AI32" s="15">
+        <v>1180</v>
       </c>
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.2">
@@ -4542,103 +4543,103 @@
         <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="9">
-        <v>6994</v>
+        <v>57899</v>
       </c>
       <c r="E33" s="9">
-        <v>7529</v>
+        <v>65594</v>
       </c>
       <c r="F33" s="9">
-        <v>8105</v>
+        <v>74312</v>
       </c>
       <c r="G33" s="9">
-        <v>7252</v>
+        <v>67826</v>
       </c>
       <c r="H33" s="9">
-        <v>7021</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>18</v>
+        <v>62048</v>
+      </c>
+      <c r="I33" s="9">
+        <v>58469</v>
       </c>
       <c r="J33" s="9">
-        <v>6782</v>
+        <v>57182</v>
       </c>
       <c r="K33" s="9">
-        <v>6597</v>
+        <v>55394</v>
       </c>
       <c r="L33" s="9">
-        <v>6318</v>
+        <v>53276</v>
       </c>
       <c r="M33" s="9">
-        <v>6104</v>
+        <v>51987</v>
       </c>
       <c r="N33" s="9">
-        <v>5957</v>
+        <v>51978</v>
       </c>
       <c r="O33" s="9">
-        <v>5457</v>
+        <v>50663</v>
       </c>
       <c r="P33" s="2">
-        <v>5122</v>
+        <v>49788</v>
       </c>
       <c r="Q33" s="2">
-        <v>4787</v>
+        <v>48913</v>
       </c>
       <c r="R33" s="3">
-        <v>5120</v>
+        <v>50486</v>
       </c>
       <c r="S33" s="3">
-        <v>5460</v>
+        <v>52062</v>
       </c>
       <c r="T33" s="2">
-        <v>6994</v>
+        <v>58170</v>
       </c>
       <c r="U33" s="5">
-        <v>8644</v>
+        <v>59824</v>
       </c>
       <c r="V33" s="5">
-        <v>8255</v>
+        <v>58797</v>
       </c>
       <c r="W33" s="4">
-        <v>8878</v>
+        <v>61410</v>
       </c>
       <c r="X33" s="10">
-        <v>9076</v>
+        <v>61591</v>
       </c>
       <c r="Y33" s="10">
-        <v>9275</v>
+        <v>61772</v>
       </c>
       <c r="Z33" s="5">
-        <v>8614</v>
+        <v>60156</v>
       </c>
       <c r="AA33" s="5">
-        <v>9070</v>
+        <v>61343</v>
       </c>
       <c r="AB33" s="5">
-        <v>9151</v>
+        <v>61537</v>
       </c>
       <c r="AC33" s="11">
-        <v>9151</v>
+        <v>61537</v>
       </c>
       <c r="AD33" s="11">
-        <v>9174</v>
+        <v>66523</v>
       </c>
       <c r="AE33" s="3">
-        <v>9176</v>
+        <v>67043</v>
       </c>
       <c r="AF33" s="3">
-        <v>9110</v>
+        <v>69929</v>
       </c>
       <c r="AG33" s="3">
-        <v>9112</v>
+        <v>70753</v>
       </c>
       <c r="AH33" s="3">
-        <v>9077</v>
-      </c>
-      <c r="AI33" s="17">
-        <v>9469</v>
+        <v>70950</v>
+      </c>
+      <c r="AI33" s="15">
+        <v>70308</v>
       </c>
     </row>
     <row r="34" spans="1:35" x14ac:dyDescent="0.2">
@@ -4646,106 +4647,106 @@
         <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D34" s="9">
-        <v>4071</v>
-      </c>
-      <c r="E34" s="9">
-        <v>2521</v>
+        <v>232065</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="F34" s="9">
-        <v>1561</v>
+        <v>229222</v>
       </c>
       <c r="G34" s="9">
-        <v>1664</v>
+        <v>214551</v>
       </c>
       <c r="H34" s="9">
-        <v>1328</v>
-      </c>
-      <c r="I34" s="9">
-        <v>955</v>
-      </c>
-      <c r="J34" s="9">
-        <v>912</v>
-      </c>
-      <c r="K34" s="9">
-        <v>847</v>
-      </c>
-      <c r="L34" s="9">
-        <v>803</v>
-      </c>
-      <c r="M34" s="9">
-        <v>712</v>
-      </c>
-      <c r="N34" s="9">
-        <v>558</v>
-      </c>
-      <c r="O34" s="9">
-        <v>506</v>
+        <v>220488</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="P34" s="2">
-        <v>414</v>
+        <v>205647</v>
       </c>
       <c r="Q34" s="2">
-        <v>322</v>
+        <v>196280</v>
       </c>
       <c r="R34" s="3">
-        <v>326</v>
+        <v>197409</v>
       </c>
       <c r="S34" s="3">
-        <v>334</v>
-      </c>
-      <c r="T34" s="2">
-        <v>448</v>
-      </c>
-      <c r="U34" s="3">
-        <v>417</v>
-      </c>
-      <c r="V34" s="3">
-        <v>428</v>
+        <v>198784</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="W34" s="4">
-        <v>455</v>
+        <v>233433</v>
       </c>
       <c r="X34" s="10">
-        <v>1477</v>
+        <v>236635</v>
       </c>
       <c r="Y34" s="10">
-        <v>2499</v>
-      </c>
-      <c r="Z34" s="5">
-        <v>5560</v>
-      </c>
-      <c r="AA34" s="5">
-        <v>1980</v>
-      </c>
-      <c r="AB34" s="5">
-        <v>760</v>
+        <v>239838</v>
+      </c>
+      <c r="Z34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>241915</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>242484</v>
       </c>
       <c r="AC34" s="11">
-        <v>760</v>
+        <v>242484</v>
       </c>
       <c r="AD34" s="11">
-        <v>1253</v>
+        <v>245897</v>
       </c>
       <c r="AE34" s="3">
-        <v>1291</v>
+        <v>246241</v>
       </c>
       <c r="AF34" s="3">
-        <v>730</v>
+        <v>276760</v>
       </c>
       <c r="AG34" s="3">
-        <v>1061</v>
+        <v>283936</v>
       </c>
       <c r="AH34" s="3">
-        <v>1172</v>
-      </c>
-      <c r="AI34" s="17">
-        <v>1180</v>
+        <v>298329</v>
+      </c>
+      <c r="AI34" s="15">
+        <v>303898</v>
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.2">
@@ -4753,106 +4754,106 @@
         <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D35" s="9">
-        <v>57899</v>
+        <v>43955</v>
       </c>
       <c r="E35" s="9">
-        <v>65594</v>
+        <v>43218</v>
       </c>
       <c r="F35" s="9">
-        <v>74312</v>
+        <v>42493</v>
       </c>
       <c r="G35" s="9">
-        <v>67826</v>
+        <v>36165</v>
       </c>
       <c r="H35" s="9">
-        <v>62048</v>
+        <v>37051</v>
       </c>
       <c r="I35" s="9">
-        <v>58469</v>
+        <v>37453</v>
       </c>
       <c r="J35" s="9">
-        <v>57182</v>
+        <v>37842</v>
       </c>
       <c r="K35" s="9">
-        <v>55394</v>
+        <v>38917</v>
       </c>
       <c r="L35" s="9">
-        <v>53276</v>
+        <v>39884</v>
       </c>
       <c r="M35" s="9">
-        <v>51987</v>
+        <v>41062</v>
       </c>
       <c r="N35" s="9">
-        <v>51978</v>
+        <v>37304</v>
       </c>
       <c r="O35" s="9">
-        <v>50663</v>
+        <v>36486</v>
       </c>
       <c r="P35" s="2">
-        <v>49788</v>
+        <v>35021</v>
       </c>
       <c r="Q35" s="2">
-        <v>48913</v>
+        <v>33556</v>
       </c>
       <c r="R35" s="3">
-        <v>50486</v>
+        <v>33371</v>
       </c>
       <c r="S35" s="3">
-        <v>52062</v>
+        <v>33222</v>
       </c>
       <c r="T35" s="2">
-        <v>58170</v>
+        <v>36068</v>
       </c>
       <c r="U35" s="5">
-        <v>59824</v>
+        <v>38102</v>
       </c>
       <c r="V35" s="5">
-        <v>58797</v>
+        <v>37420</v>
       </c>
       <c r="W35" s="4">
-        <v>61410</v>
+        <v>38234</v>
       </c>
       <c r="X35" s="10">
-        <v>61591</v>
+        <v>38596</v>
       </c>
       <c r="Y35" s="10">
-        <v>61772</v>
+        <v>38958</v>
       </c>
       <c r="Z35" s="5">
-        <v>60156</v>
+        <v>38599</v>
       </c>
       <c r="AA35" s="5">
-        <v>61343</v>
+        <v>38730</v>
       </c>
       <c r="AB35" s="5">
-        <v>61537</v>
+        <v>38775</v>
       </c>
       <c r="AC35" s="11">
-        <v>61537</v>
+        <v>38775</v>
       </c>
       <c r="AD35" s="11">
-        <v>66523</v>
+        <v>39782</v>
       </c>
       <c r="AE35" s="3">
-        <v>67043</v>
+        <v>39884</v>
       </c>
       <c r="AF35" s="3">
-        <v>69929</v>
+        <v>43699</v>
       </c>
       <c r="AG35" s="3">
-        <v>70753</v>
+        <v>44802</v>
       </c>
       <c r="AH35" s="3">
-        <v>70950</v>
-      </c>
-      <c r="AI35" s="17">
-        <v>70308</v>
+        <v>47308</v>
+      </c>
+      <c r="AI35" s="15">
+        <v>48011</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.2">
@@ -4863,103 +4864,103 @@
         <v>49</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D36" s="9">
-        <v>232065</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>96</v>
+        <v>1946</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2220</v>
       </c>
       <c r="F36" s="9">
-        <v>229222</v>
+        <v>2533</v>
       </c>
       <c r="G36" s="9">
-        <v>214551</v>
+        <v>2235</v>
       </c>
       <c r="H36" s="9">
-        <v>220488</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="N36" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>103</v>
+        <v>2180</v>
+      </c>
+      <c r="I36" s="9">
+        <v>2057</v>
+      </c>
+      <c r="J36" s="9">
+        <v>2053</v>
+      </c>
+      <c r="K36" s="9">
+        <v>2041</v>
+      </c>
+      <c r="L36" s="9">
+        <v>2029</v>
+      </c>
+      <c r="M36" s="9">
+        <v>2018</v>
+      </c>
+      <c r="N36" s="9">
+        <v>2261</v>
+      </c>
+      <c r="O36" s="9">
+        <v>2276</v>
       </c>
       <c r="P36" s="2">
-        <v>205647</v>
+        <v>2363</v>
       </c>
       <c r="Q36" s="2">
-        <v>196280</v>
+        <v>2450</v>
       </c>
       <c r="R36" s="3">
-        <v>197409</v>
+        <v>2437</v>
       </c>
       <c r="S36" s="3">
-        <v>198784</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>148</v>
+        <v>2427</v>
+      </c>
+      <c r="T36" s="2">
+        <v>2116</v>
+      </c>
+      <c r="U36" s="5">
+        <v>1947</v>
+      </c>
+      <c r="V36" s="5">
+        <v>2003</v>
       </c>
       <c r="W36" s="4">
-        <v>233433</v>
+        <v>1906</v>
       </c>
       <c r="X36" s="10">
-        <v>236635</v>
+        <v>1936</v>
       </c>
       <c r="Y36" s="10">
-        <v>239838</v>
-      </c>
-      <c r="Z36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA36" s="3">
-        <v>241915</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>242484</v>
+        <v>1966</v>
+      </c>
+      <c r="Z36" s="5">
+        <v>2196</v>
+      </c>
+      <c r="AA36" s="5">
+        <v>2098</v>
+      </c>
+      <c r="AB36" s="5">
+        <v>2110</v>
       </c>
       <c r="AC36" s="11">
-        <v>242484</v>
+        <v>2110</v>
       </c>
       <c r="AD36" s="11">
-        <v>245897</v>
+        <v>2129</v>
       </c>
       <c r="AE36" s="3">
-        <v>246241</v>
+        <v>2131</v>
       </c>
       <c r="AF36" s="3">
-        <v>276760</v>
+        <v>2438</v>
       </c>
       <c r="AG36" s="3">
-        <v>283936</v>
+        <v>2510</v>
       </c>
       <c r="AH36" s="3">
-        <v>298329</v>
-      </c>
-      <c r="AI36" s="17">
-        <v>303898</v>
+        <v>2702</v>
+      </c>
+      <c r="AI36" s="15">
+        <v>2771</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.2">
@@ -4970,103 +4971,103 @@
         <v>49</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D37" s="9">
-        <v>43955</v>
-      </c>
-      <c r="E37" s="9">
-        <v>43218</v>
+        <v>128227</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="F37" s="9">
-        <v>42493</v>
+        <v>139951</v>
       </c>
       <c r="G37" s="9">
-        <v>36165</v>
+        <v>126867</v>
       </c>
       <c r="H37" s="9">
-        <v>37051</v>
-      </c>
-      <c r="I37" s="9">
-        <v>37453</v>
-      </c>
-      <c r="J37" s="9">
-        <v>37842</v>
-      </c>
-      <c r="K37" s="9">
-        <v>38917</v>
-      </c>
-      <c r="L37" s="9">
-        <v>39884</v>
-      </c>
-      <c r="M37" s="9">
-        <v>41062</v>
-      </c>
-      <c r="N37" s="9">
-        <v>37304</v>
-      </c>
-      <c r="O37" s="9">
-        <v>36486</v>
+        <v>126785</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="P37" s="2">
-        <v>35021</v>
+        <v>117790</v>
       </c>
       <c r="Q37" s="2">
-        <v>33556</v>
+        <v>114206</v>
       </c>
       <c r="R37" s="3">
-        <v>33371</v>
+        <v>113754</v>
       </c>
       <c r="S37" s="3">
-        <v>33222</v>
-      </c>
-      <c r="T37" s="2">
-        <v>36068</v>
-      </c>
-      <c r="U37" s="5">
-        <v>38102</v>
-      </c>
-      <c r="V37" s="5">
-        <v>37420</v>
+        <v>113366</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="W37" s="4">
-        <v>38234</v>
+        <v>122810</v>
       </c>
       <c r="X37" s="10">
-        <v>38596</v>
+        <v>125964</v>
       </c>
       <c r="Y37" s="10">
-        <v>38958</v>
-      </c>
-      <c r="Z37" s="5">
-        <v>38599</v>
-      </c>
-      <c r="AA37" s="5">
-        <v>38730</v>
-      </c>
-      <c r="AB37" s="5">
-        <v>38775</v>
+        <v>129119</v>
+      </c>
+      <c r="Z37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>135429</v>
+      </c>
+      <c r="AB37" s="3">
+        <v>136909</v>
       </c>
       <c r="AC37" s="11">
-        <v>38775</v>
+        <v>136909</v>
       </c>
       <c r="AD37" s="11">
-        <v>39782</v>
+        <v>132948</v>
       </c>
       <c r="AE37" s="3">
-        <v>39884</v>
+        <v>132558</v>
       </c>
       <c r="AF37" s="3">
-        <v>43699</v>
+        <v>142234</v>
       </c>
       <c r="AG37" s="3">
-        <v>44802</v>
+        <v>142641</v>
       </c>
       <c r="AH37" s="3">
-        <v>47308</v>
-      </c>
-      <c r="AI37" s="17">
-        <v>48011</v>
+        <v>145566</v>
+      </c>
+      <c r="AI37" s="15">
+        <v>144885</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.2">
@@ -5077,103 +5078,103 @@
         <v>49</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D38" s="9">
-        <v>1946</v>
+        <v>1226</v>
       </c>
       <c r="E38" s="9">
-        <v>2220</v>
+        <v>1220</v>
       </c>
       <c r="F38" s="9">
-        <v>2533</v>
+        <v>1214</v>
       </c>
       <c r="G38" s="9">
-        <v>2235</v>
+        <v>1038</v>
       </c>
       <c r="H38" s="9">
-        <v>2180</v>
+        <v>1004</v>
       </c>
       <c r="I38" s="9">
-        <v>2057</v>
+        <v>1028</v>
       </c>
       <c r="J38" s="9">
-        <v>2053</v>
+        <v>1032</v>
       </c>
       <c r="K38" s="9">
-        <v>2041</v>
+        <v>1018</v>
       </c>
       <c r="L38" s="9">
-        <v>2029</v>
+        <v>1009</v>
       </c>
       <c r="M38" s="9">
-        <v>2018</v>
+        <v>998</v>
       </c>
       <c r="N38" s="9">
-        <v>2261</v>
+        <v>1075</v>
       </c>
       <c r="O38" s="9">
-        <v>2276</v>
+        <v>1068</v>
       </c>
       <c r="P38" s="2">
-        <v>2363</v>
+        <v>1088</v>
       </c>
       <c r="Q38" s="2">
-        <v>2450</v>
+        <v>1108</v>
       </c>
       <c r="R38" s="3">
-        <v>2437</v>
+        <v>1107</v>
       </c>
       <c r="S38" s="3">
-        <v>2427</v>
+        <v>1106</v>
       </c>
       <c r="T38" s="2">
-        <v>2116</v>
+        <v>1035</v>
       </c>
       <c r="U38" s="5">
-        <v>1947</v>
+        <v>1074</v>
       </c>
       <c r="V38" s="5">
-        <v>2003</v>
+        <v>1058</v>
       </c>
       <c r="W38" s="4">
-        <v>1906</v>
+        <v>1046</v>
       </c>
       <c r="X38" s="10">
-        <v>1936</v>
+        <v>1061</v>
       </c>
       <c r="Y38" s="10">
-        <v>1966</v>
+        <v>1076</v>
       </c>
       <c r="Z38" s="5">
-        <v>2196</v>
+        <v>1114</v>
       </c>
       <c r="AA38" s="5">
-        <v>2098</v>
+        <v>1097</v>
       </c>
       <c r="AB38" s="5">
-        <v>2110</v>
+        <v>1098</v>
       </c>
       <c r="AC38" s="11">
-        <v>2110</v>
+        <v>1098</v>
       </c>
       <c r="AD38" s="11">
-        <v>2129</v>
+        <v>1110</v>
       </c>
       <c r="AE38" s="3">
-        <v>2131</v>
+        <v>1111</v>
       </c>
       <c r="AF38" s="3">
-        <v>2438</v>
+        <v>1248</v>
       </c>
       <c r="AG38" s="3">
-        <v>2510</v>
+        <v>1266</v>
       </c>
       <c r="AH38" s="3">
-        <v>2702</v>
-      </c>
-      <c r="AI38" s="17">
-        <v>2771</v>
+        <v>1327</v>
+      </c>
+      <c r="AI38" s="15">
+        <v>1332</v>
       </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.2">
@@ -5184,55 +5185,55 @@
         <v>49</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D39" s="9">
-        <v>128227</v>
+        <v>205501</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F39" s="9">
-        <v>139951</v>
+        <v>184544</v>
       </c>
       <c r="G39" s="9">
-        <v>126867</v>
+        <v>173828</v>
       </c>
       <c r="H39" s="9">
-        <v>126785</v>
+        <v>188628</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="P39" s="2">
-        <v>117790</v>
+        <v>177176</v>
       </c>
       <c r="Q39" s="2">
-        <v>114206</v>
+        <v>171423</v>
       </c>
       <c r="R39" s="3">
-        <v>113754</v>
+        <v>172527</v>
       </c>
       <c r="S39" s="3">
-        <v>113366</v>
+        <v>173740</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>137</v>
@@ -5244,689 +5245,1002 @@
         <v>149</v>
       </c>
       <c r="W39" s="4">
-        <v>122810</v>
+        <v>207739</v>
       </c>
       <c r="X39" s="10">
-        <v>125964</v>
+        <v>213357</v>
       </c>
       <c r="Y39" s="10">
-        <v>129119</v>
+        <v>218976</v>
       </c>
       <c r="Z39" s="3" t="s">
         <v>174</v>
       </c>
       <c r="AA39" s="3">
-        <v>135429</v>
+        <v>225458</v>
       </c>
       <c r="AB39" s="3">
-        <v>136909</v>
+        <v>227879</v>
       </c>
       <c r="AC39" s="11">
-        <v>136909</v>
+        <v>227879</v>
       </c>
       <c r="AD39" s="11">
-        <v>132948</v>
+        <v>242948</v>
       </c>
       <c r="AE39" s="3">
-        <v>132558</v>
+        <v>244509</v>
       </c>
       <c r="AF39" s="3">
-        <v>142234</v>
+        <v>292657</v>
       </c>
       <c r="AG39" s="3">
-        <v>142641</v>
+        <v>302625</v>
       </c>
       <c r="AH39" s="3">
-        <v>145566</v>
-      </c>
-      <c r="AI39" s="17">
-        <v>144885</v>
+        <v>318877</v>
+      </c>
+      <c r="AI39" s="15">
+        <v>331208</v>
       </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="9">
-        <v>1226</v>
-      </c>
-      <c r="E40" s="9">
-        <v>1220</v>
-      </c>
-      <c r="F40" s="9">
-        <v>1214</v>
-      </c>
-      <c r="G40" s="9">
-        <v>1038</v>
-      </c>
-      <c r="H40" s="9">
-        <v>1004</v>
-      </c>
-      <c r="I40" s="9">
-        <v>1028</v>
-      </c>
-      <c r="J40" s="9">
-        <v>1032</v>
-      </c>
-      <c r="K40" s="9">
-        <v>1018</v>
-      </c>
-      <c r="L40" s="9">
-        <v>1009</v>
-      </c>
-      <c r="M40" s="9">
-        <v>998</v>
-      </c>
-      <c r="N40" s="9">
-        <v>1075</v>
-      </c>
-      <c r="O40" s="9">
-        <v>1068</v>
-      </c>
-      <c r="P40" s="2">
-        <v>1088</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>1108</v>
-      </c>
-      <c r="R40" s="3">
-        <v>1107</v>
-      </c>
-      <c r="S40" s="3">
-        <v>1106</v>
-      </c>
-      <c r="T40" s="2">
-        <v>1035</v>
-      </c>
-      <c r="U40" s="5">
-        <v>1074</v>
-      </c>
-      <c r="V40" s="5">
-        <v>1058</v>
-      </c>
-      <c r="W40" s="4">
-        <v>1046</v>
-      </c>
-      <c r="X40" s="10">
-        <v>1061</v>
-      </c>
-      <c r="Y40" s="10">
-        <v>1076</v>
-      </c>
-      <c r="Z40" s="5">
-        <v>1114</v>
-      </c>
-      <c r="AA40" s="5">
-        <v>1097</v>
-      </c>
-      <c r="AB40" s="5">
-        <v>1098</v>
-      </c>
-      <c r="AC40" s="11">
-        <v>1098</v>
-      </c>
-      <c r="AD40" s="11">
-        <v>1110</v>
-      </c>
-      <c r="AE40" s="3">
-        <v>1111</v>
+        <v>182</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15">
+        <v>0</v>
+      </c>
+      <c r="F40" s="15">
+        <v>0</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0</v>
+      </c>
+      <c r="H40" s="15">
+        <v>0</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0</v>
+      </c>
+      <c r="L40" s="15">
+        <v>0</v>
+      </c>
+      <c r="M40" s="15">
+        <v>0</v>
+      </c>
+      <c r="N40" s="15">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15">
+        <v>0</v>
+      </c>
+      <c r="P40" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="15">
+        <v>0</v>
+      </c>
+      <c r="R40" s="15">
+        <v>0</v>
+      </c>
+      <c r="S40" s="15">
+        <v>0</v>
+      </c>
+      <c r="T40" s="15">
+        <v>0</v>
+      </c>
+      <c r="U40" s="15">
+        <v>0</v>
+      </c>
+      <c r="V40" s="15">
+        <v>0</v>
+      </c>
+      <c r="W40" s="15">
+        <v>0</v>
+      </c>
+      <c r="X40" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="15">
+        <v>0</v>
       </c>
       <c r="AF40" s="3">
-        <v>1248</v>
+        <v>99570</v>
       </c>
       <c r="AG40" s="3">
-        <v>1266</v>
+        <v>99469</v>
       </c>
       <c r="AH40" s="3">
-        <v>1327</v>
-      </c>
-      <c r="AI40" s="17">
-        <v>1332</v>
+        <v>102143</v>
+      </c>
+      <c r="AI40" s="15">
+        <v>105567</v>
       </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" s="9">
-        <v>205501</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="9">
-        <v>184544</v>
-      </c>
-      <c r="G41" s="9">
-        <v>173828</v>
-      </c>
-      <c r="H41" s="9">
-        <v>188628</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="P41" s="2">
-        <v>177176</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>171423</v>
-      </c>
-      <c r="R41" s="3">
-        <v>172527</v>
-      </c>
-      <c r="S41" s="3">
-        <v>173740</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="W41" s="4">
-        <v>207739</v>
-      </c>
-      <c r="X41" s="10">
-        <v>213357</v>
-      </c>
-      <c r="Y41" s="10">
-        <v>218976</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>225458</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>227879</v>
-      </c>
-      <c r="AC41" s="11">
-        <v>227879</v>
-      </c>
-      <c r="AD41" s="11">
-        <v>242948</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>244509</v>
+        <v>181</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15">
+        <v>0</v>
+      </c>
+      <c r="G41" s="15">
+        <v>0</v>
+      </c>
+      <c r="H41" s="15">
+        <v>0</v>
+      </c>
+      <c r="I41" s="15">
+        <v>0</v>
+      </c>
+      <c r="J41" s="15">
+        <v>0</v>
+      </c>
+      <c r="K41" s="15">
+        <v>0</v>
+      </c>
+      <c r="L41" s="15">
+        <v>0</v>
+      </c>
+      <c r="M41" s="15">
+        <v>0</v>
+      </c>
+      <c r="N41" s="15">
+        <v>0</v>
+      </c>
+      <c r="O41" s="15">
+        <v>0</v>
+      </c>
+      <c r="P41" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="15">
+        <v>0</v>
+      </c>
+      <c r="R41" s="15">
+        <v>0</v>
+      </c>
+      <c r="S41" s="15">
+        <v>0</v>
+      </c>
+      <c r="T41" s="15">
+        <v>0</v>
+      </c>
+      <c r="U41" s="15">
+        <v>0</v>
+      </c>
+      <c r="V41" s="15">
+        <v>0</v>
+      </c>
+      <c r="W41" s="15">
+        <v>0</v>
+      </c>
+      <c r="X41" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="15">
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
-        <v>292657</v>
+        <v>67914</v>
       </c>
       <c r="AG41" s="3">
-        <v>302625</v>
+        <v>68080</v>
       </c>
       <c r="AH41" s="3">
-        <v>318877</v>
-      </c>
-      <c r="AI41" s="17">
-        <v>331208</v>
+        <v>68865</v>
+      </c>
+      <c r="AI41" s="15">
+        <v>69733</v>
       </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X42" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y42" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC42" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD42" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>99570</v>
-      </c>
-      <c r="AG42" s="3">
-        <v>99469</v>
+        <v>189</v>
+      </c>
+      <c r="D42" s="15">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0</v>
+      </c>
+      <c r="F42" s="15">
+        <v>0</v>
+      </c>
+      <c r="G42" s="15">
+        <v>0</v>
+      </c>
+      <c r="H42" s="15">
+        <v>0</v>
+      </c>
+      <c r="I42" s="15">
+        <v>0</v>
+      </c>
+      <c r="J42" s="15">
+        <v>0</v>
+      </c>
+      <c r="K42" s="15">
+        <v>0</v>
+      </c>
+      <c r="L42" s="15">
+        <v>0</v>
+      </c>
+      <c r="M42" s="15">
+        <v>0</v>
+      </c>
+      <c r="N42" s="15">
+        <v>0</v>
+      </c>
+      <c r="O42" s="15">
+        <v>0</v>
+      </c>
+      <c r="P42" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="15">
+        <v>0</v>
+      </c>
+      <c r="R42" s="15">
+        <v>0</v>
+      </c>
+      <c r="S42" s="15">
+        <v>0</v>
+      </c>
+      <c r="T42" s="15">
+        <v>0</v>
+      </c>
+      <c r="U42" s="15">
+        <v>0</v>
+      </c>
+      <c r="V42" s="15">
+        <v>0</v>
+      </c>
+      <c r="W42" s="15">
+        <v>0</v>
+      </c>
+      <c r="X42" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="15">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="15">
+        <v>0</v>
       </c>
       <c r="AH42" s="3">
-        <v>102143</v>
-      </c>
-      <c r="AI42" s="17">
-        <v>105567</v>
+        <v>229</v>
+      </c>
+      <c r="AI42" s="15">
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X43" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y43" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC43" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD43" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>67914</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>68080</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>68865</v>
-      </c>
-      <c r="AI43" s="17">
-        <v>69733</v>
+        <v>190</v>
+      </c>
+      <c r="D43" s="15">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15">
+        <v>0</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0</v>
+      </c>
+      <c r="H43" s="15">
+        <v>0</v>
+      </c>
+      <c r="I43" s="15">
+        <v>0</v>
+      </c>
+      <c r="J43" s="15">
+        <v>0</v>
+      </c>
+      <c r="K43" s="15">
+        <v>0</v>
+      </c>
+      <c r="L43" s="15">
+        <v>0</v>
+      </c>
+      <c r="M43" s="15">
+        <v>0</v>
+      </c>
+      <c r="N43" s="15">
+        <v>0</v>
+      </c>
+      <c r="O43" s="15">
+        <v>0</v>
+      </c>
+      <c r="P43" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="15">
+        <v>0</v>
+      </c>
+      <c r="R43" s="15">
+        <v>0</v>
+      </c>
+      <c r="S43" s="15">
+        <v>0</v>
+      </c>
+      <c r="T43" s="15">
+        <v>0</v>
+      </c>
+      <c r="U43" s="15">
+        <v>0</v>
+      </c>
+      <c r="V43" s="15">
+        <v>0</v>
+      </c>
+      <c r="W43" s="15">
+        <v>0</v>
+      </c>
+      <c r="X43" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="15">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="15">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X44" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y44" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC44" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD44" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF44" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="C44" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="16">
+        <f>(D23+D24+D25+D26+D27)</f>
+        <v>13145</v>
+      </c>
+      <c r="E44" s="16">
+        <f>(E23+E24+E25+E26+E27)</f>
+        <v>15371</v>
+      </c>
+      <c r="F44" s="16">
+        <f>(F23+F24+F25+F26+F27)</f>
+        <v>17975</v>
+      </c>
+      <c r="G44" s="16">
+        <f>(G23+G24+G25+G26+G27)</f>
+        <v>16119</v>
+      </c>
+      <c r="H44" s="16">
+        <f>(H23+H24+H25+H26+H27)</f>
+        <v>15845</v>
+      </c>
+      <c r="I44" s="16">
+        <f>(I23+I24+I25+I26+I27)</f>
+        <v>15394</v>
+      </c>
+      <c r="J44" s="16">
+        <f>(J23+J24+J25+J26+J27)</f>
+        <v>15554</v>
+      </c>
+      <c r="K44" s="16">
+        <f>(K23+K24+K25+K26+K27)</f>
+        <v>15906</v>
+      </c>
+      <c r="L44" s="16">
+        <f>(L23+L24+L25+L26+L27)</f>
+        <v>16148</v>
+      </c>
+      <c r="M44" s="16">
+        <f>(M23+M24+M25+M26+M27)</f>
+        <v>16623</v>
+      </c>
+      <c r="N44" s="16">
+        <f>(N23+N24+N25+N26+N27)</f>
+        <v>13605</v>
+      </c>
+      <c r="O44" s="16">
+        <f>(O23+O24+O25+O26+O27)</f>
+        <v>12815</v>
+      </c>
+      <c r="P44" s="16">
+        <f>(P23+P24+P25+P26+P27)</f>
+        <v>11492</v>
+      </c>
+      <c r="Q44" s="16">
+        <f>(Q23+Q24+Q25+Q26+Q27)</f>
+        <v>10170</v>
+      </c>
+      <c r="R44" s="16">
+        <f>(R23+R24+R25+R26+R27)</f>
+        <v>10042</v>
+      </c>
+      <c r="S44" s="16">
+        <f>(S23+S24+S25+S26+S27)</f>
+        <v>9967</v>
+      </c>
+      <c r="T44" s="16">
+        <f>(T23+T24+T25+T26+T27)</f>
+        <v>11808</v>
+      </c>
+      <c r="U44" s="16">
+        <f>(U23+U24+U25+U26+U27)</f>
+        <v>10867</v>
+      </c>
+      <c r="V44" s="16">
+        <f>(V23+V24+V25+V26+V27)</f>
+        <v>11246</v>
+      </c>
+      <c r="W44" s="16">
+        <f>(W23+W24+W25+W26+W27)</f>
+        <v>11514</v>
+      </c>
+      <c r="X44" s="16">
+        <f>(X23+X24+X25+X26+X27)</f>
+        <v>11485</v>
+      </c>
+      <c r="Y44" s="16">
+        <f>(Y23+Y24+Y25+Y26+Y27)</f>
+        <v>11456</v>
+      </c>
+      <c r="Z44" s="16">
+        <f>(Z23+Z24+Z25+Z26+Z27)</f>
+        <v>11566</v>
+      </c>
+      <c r="AA44" s="16">
+        <f>(AA23+AA24+AA25+AA26+AA27)</f>
+        <v>11581</v>
+      </c>
+      <c r="AB44" s="16">
+        <f>(AB23+AB24+AB25+AB26+AB27)</f>
+        <v>11613</v>
+      </c>
+      <c r="AC44" s="16">
+        <f>(AC23+AC24+AC25+AC26+AC27)</f>
+        <v>11613</v>
+      </c>
+      <c r="AD44" s="16">
+        <f>(AD23+AD24+AD25+AD26+AD27)</f>
+        <v>11390</v>
+      </c>
+      <c r="AE44" s="16">
+        <f>(AE23+AE24+AE25+AE26+AE27)</f>
+        <v>11368</v>
+      </c>
+      <c r="AF44" s="16">
+        <f>(AF23+AF24+AF25+AF26+AF27)</f>
+        <v>12401</v>
+      </c>
+      <c r="AG44" s="16">
+        <f>(AG23+AG24+AG25+AG26+AG27)</f>
+        <v>12592</v>
+      </c>
+      <c r="AH44" s="16">
+        <f>(AH23+AH24+AH25+AH26+AH27)</f>
+        <v>12836</v>
+      </c>
+      <c r="AI44" s="16">
+        <f>(AI23+AI24+AI25+AI26+AI27)</f>
+        <v>13012</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" s="16">
+        <f>D2+D3+D4+D5+D6+D8+D9+D10</f>
+        <v>333</v>
+      </c>
+      <c r="E45" s="16">
+        <f>E2+E3+E4+E5+E6+E8+E9+E10</f>
+        <v>373</v>
+      </c>
+      <c r="F45" s="16">
+        <f>F2+F3+F4+F5+F6+F8+F9+F10</f>
+        <v>420</v>
+      </c>
+      <c r="G45" s="16">
+        <f>G2+G3+G4+G5+G6+G8+G9+G10</f>
+        <v>408</v>
+      </c>
+      <c r="H45" s="16">
+        <f>H2+H3+H4+H5+H6+H8+H9+H10</f>
+        <v>415</v>
+      </c>
+      <c r="I45" s="16">
+        <f>I2+I3+I4+I5+I6+I8+I9+I10</f>
+        <v>425</v>
+      </c>
+      <c r="J45" s="16">
+        <f>J2+J3+J4+J5+J6+J8+J9+J10</f>
+        <v>429</v>
+      </c>
+      <c r="K45" s="16">
+        <f>K2+K3+K4+K5+K6+K8+K9+K10</f>
+        <v>437</v>
+      </c>
+      <c r="L45" s="16">
+        <f>L2+L3+L4+L5+L6+L8+L9+L10</f>
+        <v>445</v>
+      </c>
+      <c r="M45" s="16">
+        <f>M2+M3+M4+M5+M6+M8+M9+M10</f>
+        <v>464</v>
+      </c>
+      <c r="N45" s="16">
+        <f>N2+N3+N4+N5+N6+N8+N9+N10</f>
+        <v>504</v>
+      </c>
+      <c r="O45" s="16">
+        <f>O2+O3+O4+O5+O6+O8+O9+O10</f>
+        <v>514</v>
+      </c>
+      <c r="P45" s="16">
+        <f>P2+P3+P4+P5+P6+P8+P9+P10</f>
+        <v>536</v>
+      </c>
+      <c r="Q45" s="16">
+        <f>Q2+Q3+Q4+Q5+Q6+Q8+Q9+Q10</f>
+        <v>558</v>
+      </c>
+      <c r="R45" s="16">
+        <f>R2+R3+R4+R5+R6+R8+R9+R10</f>
+        <v>533</v>
+      </c>
+      <c r="S45" s="16">
+        <f>S2+S3+S4+S5+S6+S8+S9+S10</f>
+        <v>509</v>
+      </c>
+      <c r="T45" s="16">
+        <f>T2+T3+T4+T5+T6+T8+T9+T10</f>
+        <v>376</v>
+      </c>
+      <c r="U45" s="16">
+        <f>U2+U3+U4+U5+U6+U8+U9+U10</f>
+        <v>397</v>
+      </c>
+      <c r="V45" s="16">
+        <f>V2+V3+V4+V5+V6+V8+V9+V10</f>
+        <v>380</v>
+      </c>
+      <c r="W45" s="16">
+        <f>W2+W3+W4+W5+W6+W8+W9+W10</f>
+        <v>343</v>
+      </c>
+      <c r="X45" s="16">
+        <f>X2+X3+X4+X5+X6+X8+X9+X10</f>
+        <v>359</v>
+      </c>
+      <c r="Y45" s="16">
+        <f>Y2+Y3+Y4+Y5+Y6+Y8+Y9+Y10</f>
+        <v>374</v>
+      </c>
+      <c r="Z45" s="16">
+        <f>Z2+Z3+Z4+Z5+Z6+Z8+Z9+Z10</f>
+        <v>443</v>
+      </c>
+      <c r="AA45" s="16">
+        <f>AA2+AA3+AA4+AA5+AA6+AA8+AA9+AA10</f>
+        <v>412</v>
+      </c>
+      <c r="AB45" s="16">
+        <f>AB2+AB3+AB4+AB5+AB6+AB8+AB9+AB10</f>
+        <v>412</v>
+      </c>
+      <c r="AC45" s="16">
+        <f>AC2+AC3+AC4+AC5+AC6+AC8+AC9+AC10</f>
+        <v>412</v>
+      </c>
+      <c r="AD45" s="16">
+        <f>AD2+AD3+AD4+AD5+AD6+AD8+AD9+AD10</f>
+        <v>389</v>
+      </c>
+      <c r="AE45" s="16">
+        <f>AE2+AE3+AE4+AE5+AE6+AE8+AE9+AE10</f>
+        <v>387</v>
+      </c>
+      <c r="AF45" s="16">
+        <f>AF2+AF3+AF4+AF5+AF6+AF8+AF9+AF10</f>
+        <v>478</v>
+      </c>
+      <c r="AG45" s="16">
+        <f>AG2+AG3+AG4+AG5+AG6+AG8+AG9+AG10</f>
+        <v>500</v>
+      </c>
+      <c r="AH45" s="16">
+        <f>AH2+AH3+AH4+AH5+AH6+AH8+AH9+AH10</f>
+        <v>1062</v>
+      </c>
+      <c r="AI45" s="16">
+        <f>AI2+AI3+AI4+AI5+AI6+AI8+AI9+AI10</f>
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A46" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" s="1">
+        <f>D42+D43</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" ref="E46:AI46" si="0">E42+E43</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG46" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH46" s="1">
+        <f t="shared" si="0"/>
         <v>229</v>
       </c>
-      <c r="AI44" s="17">
+      <c r="AI46" s="1">
+        <f t="shared" si="0"/>
         <v>236</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B45" s="1" t="s">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="W45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="X45" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y45" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC45" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD45" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF45" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH45" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI45" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="X47" s="6"/>
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="9">
+        <v>15665</v>
+      </c>
+      <c r="E47" s="9">
+        <v>18368</v>
+      </c>
+      <c r="F47" s="9">
+        <v>21537</v>
+      </c>
+      <c r="G47" s="9">
+        <v>20433</v>
+      </c>
+      <c r="H47" s="9">
+        <v>19944</v>
+      </c>
+      <c r="I47" s="9">
+        <v>19145</v>
+      </c>
+      <c r="J47" s="9">
+        <v>19872</v>
+      </c>
+      <c r="K47" s="9">
+        <v>20641</v>
+      </c>
+      <c r="L47" s="9">
+        <v>21287</v>
+      </c>
+      <c r="M47" s="9">
+        <v>23518</v>
+      </c>
+      <c r="N47" s="9">
+        <v>26771</v>
+      </c>
+      <c r="O47" s="9">
+        <v>28509</v>
+      </c>
+      <c r="P47" s="2">
+        <v>30834</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>33159</v>
+      </c>
+      <c r="R47" s="3">
+        <v>30941</v>
+      </c>
+      <c r="S47" s="3">
+        <v>25786</v>
+      </c>
+      <c r="T47" s="2">
+        <v>21006</v>
+      </c>
+      <c r="U47" s="5">
+        <v>23487</v>
+      </c>
+      <c r="V47" s="5">
+        <v>22116</v>
+      </c>
+      <c r="W47" s="4">
+        <v>19589</v>
+      </c>
+      <c r="X47" s="10">
+        <v>19584</v>
+      </c>
+      <c r="Y47" s="10">
+        <v>19580</v>
+      </c>
+      <c r="Z47" s="5">
+        <v>20511</v>
+      </c>
+      <c r="AA47" s="5">
+        <v>19597</v>
+      </c>
+      <c r="AB47" s="5">
+        <v>19386</v>
+      </c>
+      <c r="AC47" s="11">
+        <v>19386</v>
+      </c>
+      <c r="AD47" s="11">
+        <v>18054</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>17926</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>20489</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>21008</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>22063</v>
+      </c>
+      <c r="AI47" s="15">
+        <v>24034</v>
+      </c>
+    </row>
+    <row r="49" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X49" s="6"/>
+    </row>
+    <row r="50" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X50" s="6"/>
     </row>
     <row r="51" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X51" s="6"/>
@@ -5934,27 +6248,27 @@
     <row r="52" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X52" s="6"/>
     </row>
-    <row r="53" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X53" s="6"/>
-    </row>
-    <row r="54" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X54" s="6"/>
-    </row>
-    <row r="58" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X58" s="6"/>
+    <row r="56" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X56" s="6"/>
+    </row>
+    <row r="61" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X61" s="6"/>
+    </row>
+    <row r="62" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X62" s="6"/>
     </row>
     <row r="63" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X63" s="6"/>
     </row>
-    <row r="64" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X64" s="6"/>
-    </row>
     <row r="65" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X65" s="6"/>
     </row>
     <row r="67" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X67" s="6"/>
     </row>
+    <row r="68" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X68" s="6"/>
+    </row>
     <row r="69" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X69" s="6"/>
     </row>
@@ -5967,23 +6281,17 @@
     <row r="72" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X72" s="6"/>
     </row>
-    <row r="73" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X73" s="6"/>
-    </row>
     <row r="74" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X74" s="6"/>
     </row>
-    <row r="76" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X76" s="6"/>
+    <row r="75" spans="24:24" x14ac:dyDescent="0.2">
+      <c r="X75" s="6"/>
     </row>
     <row r="77" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X77" s="6"/>
     </row>
-    <row r="79" spans="24:24" x14ac:dyDescent="0.2">
-      <c r="X79" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O43" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}"/>
+  <autoFilter ref="A1:O41" xr:uid="{5C3387D6-5B82-9F44-A171-AF60F746D3C2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_raw/BlinkitVS.xlsx
+++ b/data_raw/BlinkitVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/advik/Desktop/SOV Brand Comparison/data_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C18CAA-8015-5C46-A027-3B6B31D7252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E8632D-89BF-7B4B-8E8E-37AF7D46F6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" xr2:uid="{55DD27FB-5AD4-E64A-A544-907DCE296DF6}"/>
   </bookViews>
@@ -1758,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
